--- a/ScratchData/data.xlsx
+++ b/ScratchData/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="27729"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="16980" yWindow="0" windowWidth="17740" windowHeight="19200" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="5080" yWindow="8200" windowWidth="27380" windowHeight="20100" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/ScratchData/data.xlsx
+++ b/ScratchData/data.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="27729"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="28028"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="5080" yWindow="8200" windowWidth="27380" windowHeight="20100" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="-20" yWindow="0" windowWidth="30520" windowHeight="16020" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="time" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="140000" concurrentCalc="0"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="294">
   <si>
     <t>Done in 748</t>
   </si>
@@ -830,6 +831,78 @@
   </si>
   <si>
     <t>D = 9 pred</t>
+  </si>
+  <si>
+    <t>BaloonFactory</t>
+  </si>
+  <si>
+    <t>Class</t>
+  </si>
+  <si>
+    <t>Method name</t>
+  </si>
+  <si>
+    <t>Method id</t>
+  </si>
+  <si>
+    <t>getLines</t>
+  </si>
+  <si>
+    <t>Path</t>
+  </si>
+  <si>
+    <t>Full time</t>
+  </si>
+  <si>
+    <t>getTextBounds</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>unsats</t>
+  </si>
+  <si>
+    <t>addPadding</t>
+  </si>
+  <si>
+    <t>no branches</t>
+  </si>
+  <si>
+    <t>correctHorizontaly</t>
+  </si>
+  <si>
+    <t>no good branches</t>
+  </si>
+  <si>
+    <t>correctVericaly</t>
+  </si>
+  <si>
+    <t>isInsideBounds</t>
+  </si>
+  <si>
+    <t>without loop</t>
+  </si>
+  <si>
+    <t>run time without loops</t>
+  </si>
+  <si>
+    <t>7000?</t>
+  </si>
+  <si>
+    <t>getCirlcePath</t>
+  </si>
+  <si>
+    <t>less</t>
+  </si>
+  <si>
+    <t>0 unsats without loops</t>
+  </si>
+  <si>
+    <t>getNormalPath</t>
   </si>
 </sst>
 </file>
@@ -4775,4 +4848,202 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <cols>
+    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G1" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1" t="s">
+        <v>287</v>
+      </c>
+      <c r="J1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>16</v>
+      </c>
+      <c r="E2">
+        <v>7590</v>
+      </c>
+      <c r="F2">
+        <v>4698</v>
+      </c>
+      <c r="G2">
+        <v>1295</v>
+      </c>
+      <c r="H2">
+        <v>11</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="B3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>15</v>
+      </c>
+      <c r="E3">
+        <v>1029</v>
+      </c>
+      <c r="F3">
+        <v>986</v>
+      </c>
+      <c r="G3">
+        <v>338</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="B4" t="s">
+        <v>281</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="B5" t="s">
+        <v>283</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6" t="s">
+        <v>285</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" t="s">
+        <v>286</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>752</v>
+      </c>
+      <c r="F7">
+        <v>700</v>
+      </c>
+      <c r="G7">
+        <v>91</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" t="s">
+        <v>290</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+      <c r="D8">
+        <v>20736</v>
+      </c>
+      <c r="E8">
+        <v>4486</v>
+      </c>
+      <c r="F8">
+        <v>4300</v>
+      </c>
+      <c r="G8">
+        <v>4100</v>
+      </c>
+      <c r="I8" t="s">
+        <v>291</v>
+      </c>
+      <c r="J8" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="B9" t="s">
+        <v>293</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>282</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
+</worksheet>
 </file>
--- a/ScratchData/data.xlsx
+++ b/ScratchData/data.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="28028"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="0" windowWidth="30520" windowHeight="16020" tabRatio="500" activeTab="2"/>
+    <workbookView xWindow="-20" yWindow="0" windowWidth="31020" windowHeight="16020" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="time" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="140000" concurrentCalc="0"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="318">
   <si>
     <t>Done in 748</t>
   </si>
@@ -899,10 +900,82 @@
     <t>less</t>
   </si>
   <si>
+    <t>0 unsats</t>
+  </si>
+  <si>
     <t>0 unsats without loops</t>
   </si>
   <si>
     <t>getNormalPath</t>
+  </si>
+  <si>
+    <t>getArrow</t>
+  </si>
+  <si>
+    <t>1f,2t,3f</t>
+  </si>
+  <si>
+    <t>1f,2f</t>
+  </si>
+  <si>
+    <t>1t,5t,7f,8t,9t,10t,11t</t>
+  </si>
+  <si>
+    <t>1t,5f,6f</t>
+  </si>
+  <si>
+    <t>1t,5t,7f,8t,9t,10t,11f</t>
+  </si>
+  <si>
+    <t>1f,2t,3t,4f</t>
+  </si>
+  <si>
+    <t>1t,5t,7t</t>
+  </si>
+  <si>
+    <t>1t,5t,7f,8f,10t,11f</t>
+  </si>
+  <si>
+    <t>1t,5t,7f,8t,9t,10f</t>
+  </si>
+  <si>
+    <t>1t,5t,7f,8f,10f</t>
+  </si>
+  <si>
+    <t>1t,5t,7f,8t,9f,10t,11f</t>
+  </si>
+  <si>
+    <t>1t,5f,6t</t>
+  </si>
+  <si>
+    <t>1t,5t,7f,8t,9f,10f</t>
+  </si>
+  <si>
+    <t>1t,5t,7f,8f,10t,11t</t>
+  </si>
+  <si>
+    <t>1f,2t,3t,4t</t>
+  </si>
+  <si>
+    <t>1t,5t,7f,8t,9f,10t,11t</t>
+  </si>
+  <si>
+    <t>Base64</t>
+  </si>
+  <si>
+    <t>getBytes</t>
+  </si>
+  <si>
+    <t>encode</t>
+  </si>
+  <si>
+    <t>fillElementWithBigIteger</t>
+  </si>
+  <si>
+    <t>decode</t>
+  </si>
+  <si>
+    <t>isWhite</t>
   </si>
 </sst>
 </file>
@@ -934,12 +1007,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -990,8 +1069,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="37">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -4852,7 +4932,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
     <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -5024,18 +5104,111 @@
         <v>291</v>
       </c>
       <c r="J8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C9">
         <v>8</v>
       </c>
       <c r="D9" t="s">
         <v>282</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" t="s">
+        <v>295</v>
+      </c>
+      <c r="C10">
+        <v>9</v>
+      </c>
+      <c r="D10">
+        <v>10</v>
+      </c>
+      <c r="E10">
+        <v>1997</v>
+      </c>
+      <c r="F10">
+        <v>700</v>
+      </c>
+      <c r="G10">
+        <v>18</v>
+      </c>
+      <c r="I10" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>312</v>
+      </c>
+      <c r="B11" t="s">
+        <v>313</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>4</v>
+      </c>
+      <c r="E11">
+        <v>1144</v>
+      </c>
+      <c r="F11">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" t="s">
+        <v>314</v>
+      </c>
+      <c r="C12">
+        <v>4</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12">
+        <v>1151</v>
+      </c>
+      <c r="F12">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" t="s">
+        <v>315</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" t="s">
+        <v>316</v>
+      </c>
+      <c r="C14">
+        <v>8</v>
+      </c>
+      <c r="D14" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" t="s">
+        <v>317</v>
+      </c>
+      <c r="C15">
+        <v>13</v>
+      </c>
+      <c r="D15">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5046,4 +5219,105 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <cols>
+    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>302</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="A1:A16">
+    <sortCondition ref="A1"/>
+  </sortState>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
+</worksheet>
 </file>
--- a/ScratchData/data.xlsx
+++ b/ScratchData/data.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="28028"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="28125"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="0" windowWidth="31020" windowHeight="16020" tabRatio="500" activeTab="2"/>
+    <workbookView xWindow="800" yWindow="0" windowWidth="19720" windowHeight="16320" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="430">
   <si>
     <t>Done in 748</t>
   </si>
@@ -976,13 +976,349 @@
   </si>
   <si>
     <t>isWhite</t>
+  </si>
+  <si>
+    <t>IsPad</t>
+  </si>
+  <si>
+    <t>small</t>
+  </si>
+  <si>
+    <t>decodeInternal</t>
+  </si>
+  <si>
+    <t>but more likely thre is no paritions inside the loop</t>
+  </si>
+  <si>
+    <t>removeWhiteSpacd</t>
+  </si>
+  <si>
+    <t>decdoe</t>
+  </si>
+  <si>
+    <t>Class11</t>
+  </si>
+  <si>
+    <t>method210</t>
+  </si>
+  <si>
+    <t>method211</t>
+  </si>
+  <si>
+    <t>has branches but not if-else parts</t>
+  </si>
+  <si>
+    <t>method212</t>
+  </si>
+  <si>
+    <t>if cond on counter which is init 0</t>
+  </si>
+  <si>
+    <t>there are loops</t>
+  </si>
+  <si>
+    <t>method 213</t>
+  </si>
+  <si>
+    <t>method215</t>
+  </si>
+  <si>
+    <t>method216</t>
+  </si>
+  <si>
+    <t>method217</t>
+  </si>
+  <si>
+    <t>per of code 10, diff 5 and no loops</t>
+  </si>
+  <si>
+    <t>method218</t>
+  </si>
+  <si>
+    <t>method219</t>
+  </si>
+  <si>
+    <t>method220</t>
+  </si>
+  <si>
+    <t>per of code 5, diff 3</t>
+  </si>
+  <si>
+    <t>method 221</t>
+  </si>
+  <si>
+    <t>per of code 10, diff 5 and no loops, with 8 per of code -&gt; 703, did those still hight, so it also about the paths theseves</t>
+  </si>
+  <si>
+    <t>Class13</t>
+  </si>
+  <si>
+    <t>method226</t>
+  </si>
+  <si>
+    <t>method232</t>
+  </si>
+  <si>
+    <t>mainly nested loops</t>
+  </si>
+  <si>
+    <t>client</t>
+  </si>
+  <si>
+    <t>processMenuClick</t>
+  </si>
+  <si>
+    <t>calcCameraPos</t>
+  </si>
+  <si>
+    <t>method85</t>
+  </si>
+  <si>
+    <t>method108</t>
+  </si>
+  <si>
+    <t>determineMenuSize</t>
+  </si>
+  <si>
+    <t>method120</t>
+  </si>
+  <si>
+    <t>methdo142</t>
+  </si>
+  <si>
+    <t>throws an stack overflow - this is because had or in the loop's conditions, removed or, but now goes into inf loop</t>
+  </si>
+  <si>
+    <t>prec 7, bracnDiff 5, some paths are not reachable - they have exceptions that makes 3 outgoing trans on not 2, so remed try/catch</t>
+  </si>
+  <si>
+    <t>GeoEngine</t>
+  </si>
+  <si>
+    <t>GeoData</t>
+  </si>
+  <si>
+    <t>getZ</t>
+  </si>
+  <si>
+    <t>moveCheck</t>
+  </si>
+  <si>
+    <t>prec 7, diff 5</t>
+  </si>
+  <si>
+    <t>getRegionOffse</t>
+  </si>
+  <si>
+    <t>getBlock</t>
+  </si>
+  <si>
+    <t>getCell</t>
+  </si>
+  <si>
+    <t>prec 3, diff 10</t>
+  </si>
+  <si>
+    <t>nCanMoveNext</t>
+  </si>
+  <si>
+    <t>nLOS</t>
+  </si>
+  <si>
+    <t>nGetNSWE</t>
+  </si>
+  <si>
+    <t>checkNSWE</t>
+  </si>
+  <si>
+    <t>FastBlurFilter</t>
+  </si>
+  <si>
+    <t>blur</t>
+  </si>
+  <si>
+    <t>ImageData</t>
+  </si>
+  <si>
+    <t>getPixel</t>
+  </si>
+  <si>
+    <t>getPixels</t>
+  </si>
+  <si>
+    <t>setAlpha</t>
+  </si>
+  <si>
+    <t>setAlphas</t>
+  </si>
+  <si>
+    <t>setPixel</t>
+  </si>
+  <si>
+    <t>setPixels</t>
+  </si>
+  <si>
+    <t>getMSBOffset</t>
+  </si>
+  <si>
+    <t>only has paths when loop is not skipped</t>
+  </si>
+  <si>
+    <t>prec 3, diff 21</t>
+  </si>
+  <si>
+    <t>closestMatch</t>
+  </si>
+  <si>
+    <t>convertPad</t>
+  </si>
+  <si>
+    <t>blit</t>
+  </si>
+  <si>
+    <t>all blits have tablshitch</t>
+  </si>
+  <si>
+    <t>runs too long</t>
+  </si>
+  <si>
+    <t>getChannelShift</t>
+  </si>
+  <si>
+    <t>getChannelWidth</t>
+  </si>
+  <si>
+    <t>buildPreciseGradientChannel</t>
+  </si>
+  <si>
+    <t>buildDitheredGradientChannel</t>
+  </si>
+  <si>
+    <t>InfBlocks</t>
+  </si>
+  <si>
+    <t>InfCodes</t>
+  </si>
+  <si>
+    <t>InfTree</t>
+  </si>
+  <si>
+    <t>MapViewer</t>
+  </si>
+  <si>
+    <t>QRCodeDataBlockReader</t>
+  </si>
+  <si>
+    <t>StructurePanel</t>
+  </si>
+  <si>
+    <t>TileRenderor</t>
+  </si>
+  <si>
+    <t>WorldController</t>
+  </si>
+  <si>
+    <t>proc</t>
+  </si>
+  <si>
+    <t>has switch table - stack overflow</t>
+  </si>
+  <si>
+    <t>huft_build</t>
+  </si>
+  <si>
+    <t>no good branches outside of loops</t>
+  </si>
+  <si>
+    <t>stack overflow - two return conditions from loops?</t>
+  </si>
+  <si>
+    <t>paintRoutes</t>
+  </si>
+  <si>
+    <t>paint</t>
+  </si>
+  <si>
+    <t>init</t>
+  </si>
+  <si>
+    <t>really small method</t>
+  </si>
+  <si>
+    <t>getNextBits</t>
+  </si>
+  <si>
+    <t>prec 3, diff 100</t>
+  </si>
+  <si>
+    <t>no good branches even inside loops</t>
+  </si>
+  <si>
+    <t>getKanjiString</t>
+  </si>
+  <si>
+    <t>calculateTranslateConstant</t>
+  </si>
+  <si>
+    <t>has table switch, no path when loops is skipped</t>
+  </si>
+  <si>
+    <t>drawRoute</t>
+  </si>
+  <si>
+    <t>drawTile</t>
+  </si>
+  <si>
+    <t>not good cond lots of table switches - rewirte?</t>
+  </si>
+  <si>
+    <t>method324</t>
+  </si>
+  <si>
+    <t>TIFFaxEncoder</t>
+  </si>
+  <si>
+    <t>decode2D</t>
+  </si>
+  <si>
+    <t>7 with loops</t>
+  </si>
+  <si>
+    <t>TIFFFaxDecoder</t>
+  </si>
+  <si>
+    <t>4 unsat and 6 stmt</t>
+  </si>
+  <si>
+    <t>decodeT6</t>
+  </si>
+  <si>
+    <t>only has paths when loops is not skipped, 4 unsats with 5 paths</t>
+  </si>
+  <si>
+    <t>setToBlack</t>
+  </si>
+  <si>
+    <t>decodeBlackCodeWord</t>
+  </si>
+  <si>
+    <t>readEOL</t>
+  </si>
+  <si>
+    <t>getNextChangingElement</t>
+  </si>
+  <si>
+    <t>prec 3, diff 60</t>
+  </si>
+  <si>
+    <t>nextNBits</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1006,8 +1342,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1017,6 +1360,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1030,7 +1379,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="37">
+  <cellStyleXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1068,12 +1417,37 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="37">
+  <cellStyles count="59">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
@@ -1092,6 +1466,17 @@
     <cellStyle name="Followed Hyperlink" xfId="32" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="34" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="36" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="38" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="40" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="44" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="46" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="48" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="50" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="52" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="54" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="56" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="58" builtinId="9" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
@@ -1110,6 +1495,17 @@
     <cellStyle name="Hyperlink" xfId="31" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="33" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="35" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="37" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="39" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="41" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="43" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="45" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="47" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="49" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="51" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="53" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="55" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="57" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4932,10 +5328,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:L105"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
-    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -5175,7 +5571,7 @@
         <v>1151</v>
       </c>
       <c r="F12">
-        <v>1090</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -5210,9 +5606,1573 @@
       <c r="D15">
         <v>5</v>
       </c>
+      <c r="E15">
+        <v>369</v>
+      </c>
+      <c r="F15">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" t="s">
+        <v>318</v>
+      </c>
+      <c r="C16">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="B17" t="s">
+        <v>314</v>
+      </c>
+      <c r="C17">
+        <v>16</v>
+      </c>
+      <c r="D17">
+        <v>12</v>
+      </c>
+      <c r="E17">
+        <v>20633</v>
+      </c>
+      <c r="F17">
+        <v>19600</v>
+      </c>
+      <c r="I17" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="B18" t="s">
+        <v>320</v>
+      </c>
+      <c r="C18">
+        <v>18</v>
+      </c>
+      <c r="D18">
+        <v>15</v>
+      </c>
+      <c r="E18">
+        <v>10064</v>
+      </c>
+      <c r="F18">
+        <v>9829</v>
+      </c>
+      <c r="G18">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="B19" t="s">
+        <v>316</v>
+      </c>
+      <c r="C19">
+        <v>19</v>
+      </c>
+      <c r="D19">
+        <v>15</v>
+      </c>
+      <c r="E19">
+        <v>8729</v>
+      </c>
+      <c r="F19">
+        <v>7975</v>
+      </c>
+      <c r="G19">
+        <v>239</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="B20" t="s">
+        <v>322</v>
+      </c>
+      <c r="C20">
+        <v>21</v>
+      </c>
+      <c r="D20" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="B21" t="s">
+        <v>323</v>
+      </c>
+      <c r="C21">
+        <v>20</v>
+      </c>
+      <c r="D21">
+        <v>11</v>
+      </c>
+      <c r="E21">
+        <v>6269</v>
+      </c>
+      <c r="F21">
+        <v>7224</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>324</v>
+      </c>
+      <c r="B22" t="s">
+        <v>325</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>5</v>
+      </c>
+      <c r="E22">
+        <v>6471</v>
+      </c>
+      <c r="F22">
+        <v>4429</v>
+      </c>
+      <c r="H22">
+        <v>2</v>
+      </c>
+      <c r="I22" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="B23" t="s">
+        <v>326</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="B24" t="s">
+        <v>328</v>
+      </c>
+      <c r="C24">
+        <v>3</v>
+      </c>
+      <c r="D24">
+        <v>4</v>
+      </c>
+      <c r="E24">
+        <v>1928</v>
+      </c>
+      <c r="F24">
+        <v>1924</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="B25" t="s">
+        <v>331</v>
+      </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="B26" t="s">
+        <v>332</v>
+      </c>
+      <c r="C26">
+        <v>6</v>
+      </c>
+      <c r="D26" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="B27" t="s">
+        <v>333</v>
+      </c>
+      <c r="C27">
+        <v>7</v>
+      </c>
+      <c r="D27">
+        <v>4</v>
+      </c>
+      <c r="E27">
+        <v>1845</v>
+      </c>
+      <c r="F27">
+        <v>1863</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="B28" t="s">
+        <v>334</v>
+      </c>
+      <c r="C28">
+        <v>8</v>
+      </c>
+      <c r="D28" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="B29" t="s">
+        <v>336</v>
+      </c>
+      <c r="C29">
+        <v>9</v>
+      </c>
+      <c r="D29" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="B30" t="s">
+        <v>337</v>
+      </c>
+      <c r="C30">
+        <v>10</v>
+      </c>
+      <c r="D30">
+        <v>24</v>
+      </c>
+      <c r="E30">
+        <v>16891</v>
+      </c>
+      <c r="F30">
+        <v>6877</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="B31" t="s">
+        <v>338</v>
+      </c>
+      <c r="C31">
+        <v>11</v>
+      </c>
+      <c r="D31">
+        <v>19</v>
+      </c>
+      <c r="E31">
+        <v>7407</v>
+      </c>
+      <c r="F31">
+        <v>7151</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="B32" t="s">
+        <v>340</v>
+      </c>
+      <c r="C32">
+        <v>12</v>
+      </c>
+      <c r="D32">
+        <v>25</v>
+      </c>
+      <c r="E32">
+        <v>4790</v>
+      </c>
+      <c r="F32">
+        <v>4667</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>342</v>
+      </c>
+      <c r="B33" t="s">
+        <v>343</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>7</v>
+      </c>
+      <c r="E33">
+        <v>3381</v>
+      </c>
+      <c r="F33">
+        <v>3615</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="B34" t="s">
+        <v>344</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="D34" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>346</v>
+      </c>
+      <c r="B35" t="s">
+        <v>347</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>10</v>
+      </c>
+      <c r="E35">
+        <v>16006</v>
+      </c>
+      <c r="F35">
+        <v>15514</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="B36" t="s">
+        <v>348</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+      <c r="D36" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="B37" t="s">
+        <v>349</v>
+      </c>
+      <c r="C37">
+        <v>3</v>
+      </c>
+      <c r="D37" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="B38" t="s">
+        <v>350</v>
+      </c>
+      <c r="C38">
+        <v>4</v>
+      </c>
+      <c r="D38">
+        <v>32</v>
+      </c>
+      <c r="E38">
+        <v>4859</v>
+      </c>
+      <c r="F38">
+        <v>4499</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="B39" t="s">
+        <v>351</v>
+      </c>
+      <c r="C39">
+        <v>5</v>
+      </c>
+      <c r="D39" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="B40" t="s">
+        <v>352</v>
+      </c>
+      <c r="C40">
+        <v>6</v>
+      </c>
+      <c r="D40">
+        <v>34</v>
+      </c>
+      <c r="E40">
+        <v>7696</v>
+      </c>
+      <c r="F40">
+        <v>6430</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="B41" t="s">
+        <v>353</v>
+      </c>
+      <c r="C41">
+        <v>7</v>
+      </c>
+      <c r="D41" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>357</v>
+      </c>
+      <c r="B42" t="s">
+        <v>358</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" t="s">
+        <v>356</v>
+      </c>
+      <c r="B43" t="s">
+        <v>359</v>
+      </c>
+      <c r="C43">
+        <v>3</v>
+      </c>
+      <c r="D43">
+        <v>3</v>
+      </c>
+      <c r="E43">
+        <v>6341</v>
+      </c>
+      <c r="F43">
+        <v>4056</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="B44" t="s">
+        <v>361</v>
+      </c>
+      <c r="C44">
+        <v>4</v>
+      </c>
+      <c r="D44" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="B45" t="s">
+        <v>362</v>
+      </c>
+      <c r="C45">
+        <v>5</v>
+      </c>
+      <c r="D45" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="B46" t="s">
+        <v>363</v>
+      </c>
+      <c r="C46">
+        <v>6</v>
+      </c>
+      <c r="D46" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="B47" t="s">
+        <v>365</v>
+      </c>
+      <c r="C47">
+        <v>7</v>
+      </c>
+      <c r="D47">
+        <v>16</v>
+      </c>
+      <c r="E47">
+        <v>5794</v>
+      </c>
+      <c r="F47">
+        <v>5761</v>
+      </c>
+      <c r="I47" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="B48" t="s">
+        <v>366</v>
+      </c>
+      <c r="C48">
+        <v>8</v>
+      </c>
+      <c r="D48">
+        <v>12</v>
+      </c>
+      <c r="E48">
+        <v>3936</v>
+      </c>
+      <c r="F48">
+        <v>3494</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="B49" t="s">
+        <v>367</v>
+      </c>
+      <c r="C49">
+        <v>9</v>
+      </c>
+      <c r="D49">
+        <v>5</v>
+      </c>
+      <c r="E49">
+        <v>2535</v>
+      </c>
+      <c r="F49">
+        <v>2509</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="B50" t="s">
+        <v>368</v>
+      </c>
+      <c r="C50">
+        <v>10</v>
+      </c>
+      <c r="D50">
+        <v>25</v>
+      </c>
+      <c r="E50">
+        <v>1242</v>
+      </c>
+      <c r="F50">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" t="s">
+        <v>369</v>
+      </c>
+      <c r="B51" t="s">
+        <v>370</v>
+      </c>
+      <c r="C51">
+        <v>3</v>
+      </c>
+      <c r="D51">
+        <v>2</v>
+      </c>
+      <c r="E51" s="3">
+        <v>41974</v>
+      </c>
+      <c r="F51">
+        <v>47350</v>
+      </c>
+      <c r="G51">
+        <v>40714</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" t="s">
+        <v>371</v>
+      </c>
+      <c r="B52" t="s">
+        <v>372</v>
+      </c>
+      <c r="C52">
+        <v>2</v>
+      </c>
+      <c r="D52">
+        <v>14</v>
+      </c>
+      <c r="E52">
+        <v>4089</v>
+      </c>
+      <c r="F52">
+        <v>1683</v>
+      </c>
+      <c r="G52">
+        <v>708</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="B53" t="s">
+        <v>373</v>
+      </c>
+      <c r="C53">
+        <v>3</v>
+      </c>
+      <c r="D53">
+        <v>12</v>
+      </c>
+      <c r="E53">
+        <v>12187</v>
+      </c>
+      <c r="F53">
+        <v>5898</v>
+      </c>
+      <c r="G53">
+        <v>132</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="B54" t="s">
+        <v>373</v>
+      </c>
+      <c r="C54">
+        <v>4</v>
+      </c>
+      <c r="D54">
+        <v>8</v>
+      </c>
+      <c r="E54">
+        <v>31459</v>
+      </c>
+      <c r="F54">
+        <v>8474</v>
+      </c>
+      <c r="G54">
+        <v>2511</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="B55" t="s">
+        <v>374</v>
+      </c>
+      <c r="C55">
+        <v>5</v>
+      </c>
+      <c r="D55">
+        <v>6</v>
+      </c>
+      <c r="E55">
+        <v>1165</v>
+      </c>
+      <c r="F55">
+        <v>1017</v>
+      </c>
+      <c r="G55">
+        <v>457</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="B56" t="s">
+        <v>375</v>
+      </c>
+      <c r="C56">
+        <v>6</v>
+      </c>
+      <c r="D56">
+        <v>5</v>
+      </c>
+      <c r="E56">
+        <v>1229</v>
+      </c>
+      <c r="F56">
+        <v>1043</v>
+      </c>
+      <c r="G56">
+        <v>398</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="B57" t="s">
+        <v>376</v>
+      </c>
+      <c r="C57">
+        <v>7</v>
+      </c>
+      <c r="D57">
+        <v>9</v>
+      </c>
+      <c r="E57">
+        <v>4187</v>
+      </c>
+      <c r="F57">
+        <v>3560</v>
+      </c>
+      <c r="G57">
+        <v>1056</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="B58" t="s">
+        <v>377</v>
+      </c>
+      <c r="C58">
+        <v>8</v>
+      </c>
+      <c r="D58">
+        <v>12</v>
+      </c>
+      <c r="E58">
+        <v>13469</v>
+      </c>
+      <c r="F58">
+        <v>6100</v>
+      </c>
+      <c r="G58">
+        <v>747</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="B59" t="s">
+        <v>377</v>
+      </c>
+      <c r="C59">
+        <v>9</v>
+      </c>
+      <c r="D59">
+        <v>8</v>
+      </c>
+      <c r="E59">
+        <v>33821</v>
+      </c>
+      <c r="F59">
+        <v>9503</v>
+      </c>
+      <c r="G59">
+        <v>903</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="B60" t="s">
+        <v>378</v>
+      </c>
+      <c r="C60">
+        <v>10</v>
+      </c>
+      <c r="D60">
+        <v>2</v>
+      </c>
+      <c r="E60">
+        <v>1224</v>
+      </c>
+      <c r="F60">
+        <v>1166</v>
+      </c>
+      <c r="G60">
+        <v>202</v>
+      </c>
+      <c r="H60">
+        <v>1</v>
+      </c>
+      <c r="I60" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="B61" t="s">
+        <v>381</v>
+      </c>
+      <c r="C61">
+        <v>11</v>
+      </c>
+      <c r="D61">
+        <v>2</v>
+      </c>
+      <c r="E61">
+        <v>10849</v>
+      </c>
+      <c r="F61">
+        <v>8615</v>
+      </c>
+      <c r="G61">
+        <v>403</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="B62" t="s">
+        <v>382</v>
+      </c>
+      <c r="C62">
+        <v>12</v>
+      </c>
+      <c r="D62" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="B63" t="s">
+        <v>383</v>
+      </c>
+      <c r="C63">
+        <v>13</v>
+      </c>
+      <c r="D63">
+        <v>4</v>
+      </c>
+      <c r="E63">
+        <v>28623</v>
+      </c>
+      <c r="F63">
+        <v>26569</v>
+      </c>
+      <c r="G63">
+        <v>1104</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="B64" t="s">
+        <v>383</v>
+      </c>
+      <c r="C64">
+        <v>14</v>
+      </c>
+      <c r="D64">
+        <v>11</v>
+      </c>
+      <c r="E64">
+        <v>77024</v>
+      </c>
+      <c r="F64">
+        <v>58614</v>
+      </c>
+      <c r="G64">
+        <v>1050</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="B65" t="s">
+        <v>383</v>
+      </c>
+      <c r="C65">
+        <v>15</v>
+      </c>
+      <c r="D65">
+        <v>6</v>
+      </c>
+      <c r="E65">
+        <v>21196</v>
+      </c>
+      <c r="F65">
+        <v>19422</v>
+      </c>
+      <c r="G65">
+        <v>396</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="B66" t="s">
+        <v>383</v>
+      </c>
+      <c r="C66">
+        <v>16</v>
+      </c>
+      <c r="I66" s="4" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="B67" t="s">
+        <v>386</v>
+      </c>
+      <c r="C67">
+        <v>17</v>
+      </c>
+      <c r="D67" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="B68" t="s">
+        <v>387</v>
+      </c>
+      <c r="C68">
+        <v>18</v>
+      </c>
+      <c r="D68" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="B69" t="s">
+        <v>388</v>
+      </c>
+      <c r="C69">
+        <v>20</v>
+      </c>
+      <c r="D69">
+        <v>2</v>
+      </c>
+      <c r="E69">
+        <v>4302</v>
+      </c>
+      <c r="F69">
+        <v>2369</v>
+      </c>
+      <c r="G69">
+        <v>2276</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="B70" t="s">
+        <v>389</v>
+      </c>
+      <c r="C70">
+        <v>21</v>
+      </c>
+      <c r="D70">
+        <v>2</v>
+      </c>
+      <c r="E70">
+        <v>18483</v>
+      </c>
+      <c r="F70">
+        <v>8678</v>
+      </c>
+      <c r="G70">
+        <v>8444</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" t="s">
+        <v>390</v>
+      </c>
+      <c r="B71" t="s">
+        <v>398</v>
+      </c>
+      <c r="C71">
+        <v>2</v>
+      </c>
+      <c r="I71" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" t="s">
+        <v>391</v>
+      </c>
+      <c r="B72" t="s">
+        <v>398</v>
+      </c>
+      <c r="C72">
+        <v>2</v>
+      </c>
+      <c r="I72" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73" t="s">
+        <v>392</v>
+      </c>
+      <c r="B73" t="s">
+        <v>400</v>
+      </c>
+      <c r="C73">
+        <v>2</v>
+      </c>
+      <c r="D73" t="s">
+        <v>401</v>
+      </c>
+      <c r="I73" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" t="s">
+        <v>393</v>
+      </c>
+      <c r="B74" t="s">
+        <v>404</v>
+      </c>
+      <c r="C74">
+        <v>2</v>
+      </c>
+      <c r="D74">
+        <v>2</v>
+      </c>
+      <c r="E74">
+        <v>17673</v>
+      </c>
+      <c r="F74">
+        <v>15388</v>
+      </c>
+      <c r="G74">
+        <v>10348</v>
+      </c>
+      <c r="H74">
+        <v>2</v>
+      </c>
+      <c r="I74" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="B75" t="s">
+        <v>403</v>
+      </c>
+      <c r="C75">
+        <v>3</v>
+      </c>
+      <c r="D75">
+        <v>6</v>
+      </c>
+      <c r="E75">
+        <v>421238</v>
+      </c>
+      <c r="F75">
+        <v>38609</v>
+      </c>
+      <c r="G75">
+        <v>1315</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76" t="s">
+        <v>394</v>
+      </c>
+      <c r="B76" t="s">
+        <v>405</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76">
+        <v>4</v>
+      </c>
+      <c r="E76">
+        <v>184</v>
+      </c>
+      <c r="F76">
+        <v>182</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="B77" t="s">
+        <v>407</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="D77">
+        <v>4</v>
+      </c>
+      <c r="E77">
+        <v>10593</v>
+      </c>
+      <c r="F77">
+        <v>6632</v>
+      </c>
+      <c r="G77">
+        <v>938</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="B78" t="s">
+        <v>410</v>
+      </c>
+      <c r="C78">
+        <v>2</v>
+      </c>
+      <c r="D78" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79" t="s">
+        <v>395</v>
+      </c>
+      <c r="B79" t="s">
+        <v>411</v>
+      </c>
+      <c r="C79">
+        <v>1</v>
+      </c>
+      <c r="D79">
+        <v>8</v>
+      </c>
+      <c r="E79">
+        <v>3602</v>
+      </c>
+      <c r="F79">
+        <v>979</v>
+      </c>
+      <c r="G79">
+        <v>738</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" t="s">
+        <v>396</v>
+      </c>
+      <c r="B80" t="s">
+        <v>405</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
+      </c>
+      <c r="D80" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12">
+      <c r="B81" t="s">
+        <v>414</v>
+      </c>
+      <c r="C81">
+        <v>3</v>
+      </c>
+      <c r="D81">
+        <v>2</v>
+      </c>
+      <c r="E81">
+        <v>62456</v>
+      </c>
+      <c r="F81">
+        <v>52298</v>
+      </c>
+      <c r="G81">
+        <v>49719</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="I81" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12">
+      <c r="B82" t="s">
+        <v>413</v>
+      </c>
+      <c r="C82">
+        <v>4</v>
+      </c>
+      <c r="I82" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12">
+      <c r="C83">
+        <v>5</v>
+      </c>
+      <c r="D83" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12">
+      <c r="A84" t="s">
+        <v>397</v>
+      </c>
+      <c r="B84" t="s">
+        <v>416</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
+      <c r="D84">
+        <v>5</v>
+      </c>
+      <c r="E84">
+        <v>32925</v>
+      </c>
+      <c r="F84">
+        <v>9169</v>
+      </c>
+      <c r="G84">
+        <v>7057</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="A85" t="s">
+        <v>420</v>
+      </c>
+      <c r="B85" t="s">
+        <v>405</v>
+      </c>
+      <c r="C85">
+        <v>2</v>
+      </c>
+      <c r="D85" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12">
+      <c r="B86" t="s">
+        <v>418</v>
+      </c>
+      <c r="C86">
+        <v>4</v>
+      </c>
+      <c r="D86">
+        <v>2</v>
+      </c>
+      <c r="E86">
+        <v>18636</v>
+      </c>
+      <c r="F86">
+        <v>18960</v>
+      </c>
+      <c r="G86">
+        <v>216</v>
+      </c>
+      <c r="I86" t="s">
+        <v>419</v>
+      </c>
+      <c r="J86">
+        <v>14366</v>
+      </c>
+      <c r="K86">
+        <v>160</v>
+      </c>
+      <c r="L86" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12">
+      <c r="B87" t="s">
+        <v>422</v>
+      </c>
+      <c r="C87">
+        <v>5</v>
+      </c>
+      <c r="D87">
+        <v>8</v>
+      </c>
+      <c r="E87">
+        <v>31833</v>
+      </c>
+      <c r="F87">
+        <v>19552</v>
+      </c>
+      <c r="G87">
+        <v>6084</v>
+      </c>
+      <c r="H87">
+        <v>4</v>
+      </c>
+      <c r="I87" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12">
+      <c r="B88" t="s">
+        <v>424</v>
+      </c>
+      <c r="C88">
+        <v>6</v>
+      </c>
+      <c r="D88" t="s">
+        <v>282</v>
+      </c>
+      <c r="I88" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12">
+      <c r="C89">
+        <v>7</v>
+      </c>
+      <c r="D89">
+        <v>4</v>
+      </c>
+      <c r="E89">
+        <v>1105</v>
+      </c>
+      <c r="F89">
+        <v>938</v>
+      </c>
+      <c r="G89">
+        <v>268</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12">
+      <c r="B90" t="s">
+        <v>425</v>
+      </c>
+      <c r="C90">
+        <v>8</v>
+      </c>
+      <c r="D90">
+        <v>5</v>
+      </c>
+      <c r="E90">
+        <v>1375</v>
+      </c>
+      <c r="F90">
+        <v>896</v>
+      </c>
+      <c r="G90">
+        <v>462</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+      <c r="I90" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12">
+      <c r="B91" t="s">
+        <v>426</v>
+      </c>
+      <c r="C91">
+        <v>9</v>
+      </c>
+      <c r="D91">
+        <v>18</v>
+      </c>
+      <c r="E91">
+        <v>1158</v>
+      </c>
+      <c r="F91">
+        <v>795</v>
+      </c>
+      <c r="G91">
+        <v>289</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12">
+      <c r="B92" t="s">
+        <v>427</v>
+      </c>
+      <c r="C92">
+        <v>10</v>
+      </c>
+      <c r="D92">
+        <v>4</v>
+      </c>
+      <c r="E92">
+        <v>1298</v>
+      </c>
+      <c r="F92">
+        <v>1264</v>
+      </c>
+      <c r="G92">
+        <v>1155</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12">
+      <c r="B93" t="s">
+        <v>429</v>
+      </c>
+      <c r="C93">
+        <v>11</v>
+      </c>
+      <c r="D93">
+        <v>19</v>
+      </c>
+      <c r="E93">
+        <v>2362</v>
+      </c>
+      <c r="F93">
+        <v>1324</v>
+      </c>
+      <c r="G93">
+        <v>217</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12">
+      <c r="C94">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12">
+      <c r="C95">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12">
+      <c r="C96">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" t="s">
+        <v>417</v>
+      </c>
+      <c r="C97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="C98">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="C99">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="C100">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="C101">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="C102">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="C103">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="C104">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="C105">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
       <mx:PLV Mode="0" OnePage="0" WScale="0"/>

--- a/ScratchData/data.xlsx
+++ b/ScratchData/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="28125"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="800" yWindow="0" windowWidth="19720" windowHeight="16320" tabRatio="500" activeTab="2"/>
+    <workbookView xWindow="2880" yWindow="0" windowWidth="19700" windowHeight="16320" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="448">
   <si>
     <t>Done in 748</t>
   </si>
@@ -1312,6 +1312,60 @@
   </si>
   <si>
     <t>nextNBits</t>
+  </si>
+  <si>
+    <t>prec 3, diff 6</t>
+  </si>
+  <si>
+    <t>nextLesser than 8 bits</t>
+  </si>
+  <si>
+    <t>small method</t>
+  </si>
+  <si>
+    <t>nextState</t>
+  </si>
+  <si>
+    <t>nexState</t>
+  </si>
+  <si>
+    <t>add1DBits</t>
+  </si>
+  <si>
+    <t>add2Bits</t>
+  </si>
+  <si>
+    <t>addEOL</t>
+  </si>
+  <si>
+    <t>addEOFB</t>
+  </si>
+  <si>
+    <t>encode1D</t>
+  </si>
+  <si>
+    <t>encodeRLE</t>
+  </si>
+  <si>
+    <t>encodeT4</t>
+  </si>
+  <si>
+    <t>no good cond outside of loop, with loops has stack overflow because two cond statements for the loops exit</t>
+  </si>
+  <si>
+    <t>encodeT6</t>
+  </si>
+  <si>
+    <t>no good branches outside of loop, with loops have self-ref to node 8 - my code cannot handle an arbitry exit from the program, only when it is the only one cond stmt -- need to work on it. orec 10, diff 6, prec 6 had 24 paths and some were quite fast</t>
+  </si>
+  <si>
+    <t>%Diff</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>methods</t>
   </si>
 </sst>
 </file>
@@ -1379,7 +1433,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="59">
+  <cellStyleXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1439,15 +1493,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="59">
+  <cellStyles count="61">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
@@ -1477,6 +1534,7 @@
     <cellStyle name="Followed Hyperlink" xfId="54" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="56" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="58" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="60" builtinId="9" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
@@ -1506,6 +1564,7 @@
     <cellStyle name="Hyperlink" xfId="53" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="55" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="57" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="59" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -5328,13 +5387,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L105"/>
+  <dimension ref="A1:M109"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
     <col min="2" max="2" width="22.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>271</v>
       </c>
@@ -5351,22 +5410,25 @@
         <v>276</v>
       </c>
       <c r="F1" t="s">
+        <v>445</v>
+      </c>
+      <c r="G1" t="s">
         <v>278</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>279</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>280</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>287</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>270</v>
       </c>
@@ -5382,23 +5444,27 @@
       <c r="E2">
         <v>7590</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="5">
+        <f>(E2-G2)/E2</f>
+        <v>0.38102766798418974</v>
+      </c>
+      <c r="G2">
         <v>4698</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>1295</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>11</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>0</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="B3" t="s">
         <v>277</v>
       </c>
@@ -5411,17 +5477,21 @@
       <c r="E3">
         <v>1029</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="5">
+        <f>(E3-G3)/E3</f>
+        <v>4.1788143828960157E-2</v>
+      </c>
+      <c r="G3">
         <v>986</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>338</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:11">
       <c r="B4" t="s">
         <v>281</v>
       </c>
@@ -5431,8 +5501,11 @@
       <c r="D4" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="F4" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="B5" t="s">
         <v>283</v>
       </c>
@@ -5442,8 +5515,11 @@
       <c r="D5" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="F5" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="B6" t="s">
         <v>285</v>
       </c>
@@ -5453,8 +5529,11 @@
       <c r="D6" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="F6" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="B7" t="s">
         <v>286</v>
       </c>
@@ -5467,17 +5546,21 @@
       <c r="E7">
         <v>752</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="5">
+        <f t="shared" ref="F4:F67" si="0">(E7-G7)/E7</f>
+        <v>6.9148936170212769E-2</v>
+      </c>
+      <c r="G7">
         <v>700</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>91</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:11">
       <c r="B8" t="s">
         <v>290</v>
       </c>
@@ -5490,20 +5573,24 @@
       <c r="E8">
         <v>4486</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="5">
+        <f t="shared" si="0"/>
+        <v>4.1462327240303166E-2</v>
+      </c>
+      <c r="G8">
         <v>4300</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>4100</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>291</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:11">
       <c r="B9" t="s">
         <v>294</v>
       </c>
@@ -5513,8 +5600,11 @@
       <c r="D9" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="F9" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="B10" t="s">
         <v>295</v>
       </c>
@@ -5527,17 +5617,21 @@
       <c r="E10">
         <v>1997</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.64947421131697547</v>
+      </c>
+      <c r="G10">
         <v>700</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>18</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>312</v>
       </c>
@@ -5553,11 +5647,15 @@
       <c r="E11">
         <v>1144</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="5">
+        <f t="shared" si="0"/>
+        <v>4.5454545454545456E-2</v>
+      </c>
+      <c r="G11">
         <v>1092</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:11">
       <c r="B12" t="s">
         <v>314</v>
       </c>
@@ -5570,11 +5668,15 @@
       <c r="E12">
         <v>1151</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="5">
+        <f t="shared" si="0"/>
+        <v>3.4752389226759342E-2</v>
+      </c>
+      <c r="G12">
         <v>1111</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:11">
       <c r="B13" t="s">
         <v>315</v>
       </c>
@@ -5584,8 +5686,11 @@
       <c r="D13" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="F13" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="B14" t="s">
         <v>316</v>
       </c>
@@ -5595,8 +5700,11 @@
       <c r="D14" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="F14" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="B15" t="s">
         <v>317</v>
       </c>
@@ -5609,11 +5717,15 @@
       <c r="E15">
         <v>369</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="5">
+        <f t="shared" si="0"/>
+        <v>-5.9620596205962058E-2</v>
+      </c>
+      <c r="G15">
         <v>391</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:11">
       <c r="B16" t="s">
         <v>318</v>
       </c>
@@ -5623,8 +5735,11 @@
       <c r="D16" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="F16" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="B17" t="s">
         <v>314</v>
       </c>
@@ -5637,14 +5752,18 @@
       <c r="E17">
         <v>20633</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="5">
+        <f t="shared" si="0"/>
+        <v>5.0065429166868611E-2</v>
+      </c>
+      <c r="G17">
         <v>19600</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:10">
       <c r="B18" t="s">
         <v>320</v>
       </c>
@@ -5657,14 +5776,18 @@
       <c r="E18">
         <v>10064</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="5">
+        <f t="shared" si="0"/>
+        <v>2.3350556438791734E-2</v>
+      </c>
+      <c r="G18">
         <v>9829</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>798</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:10">
       <c r="B19" t="s">
         <v>316</v>
       </c>
@@ -5677,20 +5800,24 @@
       <c r="E19">
         <v>8729</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="5">
+        <f t="shared" si="0"/>
+        <v>8.6378737541528236E-2</v>
+      </c>
+      <c r="G19">
         <v>7975</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>239</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>0</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:10">
       <c r="B20" t="s">
         <v>322</v>
       </c>
@@ -5700,8 +5827,11 @@
       <c r="D20" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="F20" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="B21" t="s">
         <v>323</v>
       </c>
@@ -5714,14 +5844,18 @@
       <c r="E21">
         <v>6269</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="5">
+        <f t="shared" si="0"/>
+        <v>-0.15233689583665658</v>
+      </c>
+      <c r="G21">
         <v>7224</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>324</v>
       </c>
@@ -5737,17 +5871,21 @@
       <c r="E22">
         <v>6471</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.31556173698037399</v>
+      </c>
+      <c r="G22">
         <v>4429</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>2</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:10">
       <c r="B23" t="s">
         <v>326</v>
       </c>
@@ -5757,8 +5895,11 @@
       <c r="D23" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="24" spans="1:9">
+      <c r="F23" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="B24" t="s">
         <v>328</v>
       </c>
@@ -5771,17 +5912,21 @@
       <c r="E24">
         <v>1928</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="5">
+        <f t="shared" si="0"/>
+        <v>2.0746887966804979E-3</v>
+      </c>
+      <c r="G24">
         <v>1924</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>0</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:10">
       <c r="B25" t="s">
         <v>331</v>
       </c>
@@ -5791,8 +5936,11 @@
       <c r="D25" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="26" spans="1:9">
+      <c r="F25" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="B26" t="s">
         <v>332</v>
       </c>
@@ -5802,8 +5950,11 @@
       <c r="D26" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="27" spans="1:9">
+      <c r="F26" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="B27" t="s">
         <v>333</v>
       </c>
@@ -5816,17 +5967,21 @@
       <c r="E27">
         <v>1845</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="5">
+        <f t="shared" si="0"/>
+        <v>-9.7560975609756097E-3</v>
+      </c>
+      <c r="G27">
         <v>1863</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>0</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:10">
       <c r="B28" t="s">
         <v>334</v>
       </c>
@@ -5836,8 +5991,11 @@
       <c r="D28" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="29" spans="1:9">
+      <c r="F28" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="B29" t="s">
         <v>336</v>
       </c>
@@ -5847,8 +6005,11 @@
       <c r="D29" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="30" spans="1:9">
+      <c r="F29" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="B30" t="s">
         <v>337</v>
       </c>
@@ -5861,17 +6022,21 @@
       <c r="E30">
         <v>16891</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.59286010301343905</v>
+      </c>
+      <c r="G30">
         <v>6877</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>0</v>
       </c>
-      <c r="I30" t="s">
+      <c r="J30" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:10">
       <c r="B31" t="s">
         <v>338</v>
       </c>
@@ -5884,17 +6049,21 @@
       <c r="E31">
         <v>7407</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="5">
+        <f t="shared" si="0"/>
+        <v>3.4561900904549747E-2</v>
+      </c>
+      <c r="G31">
         <v>7151</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>0</v>
       </c>
-      <c r="I31" t="s">
+      <c r="J31" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:10">
       <c r="B32" t="s">
         <v>340</v>
       </c>
@@ -5907,11 +6076,15 @@
       <c r="E32">
         <v>4790</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="5">
+        <f t="shared" si="0"/>
+        <v>2.5678496868475991E-2</v>
+      </c>
+      <c r="G32">
         <v>4667</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>342</v>
       </c>
@@ -5927,11 +6100,15 @@
       <c r="E33">
         <v>3381</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="5">
+        <f t="shared" si="0"/>
+        <v>-6.9210292812777283E-2</v>
+      </c>
+      <c r="G33">
         <v>3615</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:10">
       <c r="B34" t="s">
         <v>344</v>
       </c>
@@ -5941,8 +6118,11 @@
       <c r="D34" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="35" spans="1:9">
+      <c r="F34" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>346</v>
       </c>
@@ -5958,14 +6138,18 @@
       <c r="E35">
         <v>16006</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="5">
+        <f t="shared" si="0"/>
+        <v>3.0738473072597777E-2</v>
+      </c>
+      <c r="G35">
         <v>15514</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:10">
       <c r="B36" t="s">
         <v>348</v>
       </c>
@@ -5975,8 +6159,11 @@
       <c r="D36" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="37" spans="1:9">
+      <c r="F36" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="B37" t="s">
         <v>349</v>
       </c>
@@ -5986,8 +6173,11 @@
       <c r="D37" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="38" spans="1:9">
+      <c r="F37" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="B38" t="s">
         <v>350</v>
       </c>
@@ -6000,17 +6190,21 @@
       <c r="E38">
         <v>4859</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="5">
+        <f t="shared" si="0"/>
+        <v>7.4089318789874459E-2</v>
+      </c>
+      <c r="G38">
         <v>4499</v>
       </c>
-      <c r="H38">
+      <c r="I38">
         <v>0</v>
       </c>
-      <c r="I38" t="s">
+      <c r="J38" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:10">
       <c r="B39" t="s">
         <v>351</v>
       </c>
@@ -6020,8 +6214,11 @@
       <c r="D39" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="40" spans="1:9">
+      <c r="F39" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="B40" t="s">
         <v>352</v>
       </c>
@@ -6034,14 +6231,18 @@
       <c r="E40">
         <v>7696</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="5">
+        <f t="shared" si="0"/>
+        <v>0.1645010395010395</v>
+      </c>
+      <c r="G40">
         <v>6430</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:10">
       <c r="B41" t="s">
         <v>353</v>
       </c>
@@ -6051,8 +6252,11 @@
       <c r="D41" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="42" spans="1:9">
+      <c r="F41" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" t="s">
         <v>357</v>
       </c>
@@ -6065,8 +6269,11 @@
       <c r="D42" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="43" spans="1:9">
+      <c r="F42" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" t="s">
         <v>356</v>
       </c>
@@ -6082,17 +6289,21 @@
       <c r="E43">
         <v>6341</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="5">
+        <f t="shared" si="0"/>
+        <v>0.36035325658413497</v>
+      </c>
+      <c r="G43">
         <v>4056</v>
       </c>
-      <c r="H43">
+      <c r="I43">
         <v>0</v>
       </c>
-      <c r="I43" s="2" t="s">
+      <c r="J43" s="2" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:10">
       <c r="B44" t="s">
         <v>361</v>
       </c>
@@ -6102,8 +6313,11 @@
       <c r="D44" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="45" spans="1:9">
+      <c r="F44" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
       <c r="B45" t="s">
         <v>362</v>
       </c>
@@ -6113,8 +6327,11 @@
       <c r="D45" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="46" spans="1:9">
+      <c r="F45" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
       <c r="B46" t="s">
         <v>363</v>
       </c>
@@ -6124,8 +6341,11 @@
       <c r="D46" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="47" spans="1:9">
+      <c r="F46" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
       <c r="B47" t="s">
         <v>365</v>
       </c>
@@ -6138,14 +6358,18 @@
       <c r="E47">
         <v>5794</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="5">
+        <f t="shared" si="0"/>
+        <v>5.695547117707974E-3</v>
+      </c>
+      <c r="G47">
         <v>5761</v>
       </c>
-      <c r="I47" t="s">
+      <c r="J47" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:10">
       <c r="B48" t="s">
         <v>366</v>
       </c>
@@ -6158,17 +6382,21 @@
       <c r="E48">
         <v>3936</v>
       </c>
-      <c r="F48">
+      <c r="F48" s="5">
+        <f t="shared" si="0"/>
+        <v>0.11229674796747967</v>
+      </c>
+      <c r="G48">
         <v>3494</v>
       </c>
-      <c r="H48">
+      <c r="I48">
         <v>0</v>
       </c>
-      <c r="I48" t="s">
+      <c r="J48" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:10">
       <c r="B49" t="s">
         <v>367</v>
       </c>
@@ -6181,11 +6409,15 @@
       <c r="E49">
         <v>2535</v>
       </c>
-      <c r="F49">
+      <c r="F49" s="5">
+        <f t="shared" si="0"/>
+        <v>1.0256410256410256E-2</v>
+      </c>
+      <c r="G49">
         <v>2509</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:10">
       <c r="B50" t="s">
         <v>368</v>
       </c>
@@ -6198,11 +6430,15 @@
       <c r="E50">
         <v>1242</v>
       </c>
-      <c r="F50">
+      <c r="F50" s="5">
+        <f t="shared" si="0"/>
+        <v>5.7165861513687598E-2</v>
+      </c>
+      <c r="G50">
         <v>1171</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:10">
       <c r="A51" t="s">
         <v>369</v>
       </c>
@@ -6218,17 +6454,21 @@
       <c r="E51" s="3">
         <v>41974</v>
       </c>
-      <c r="F51">
+      <c r="F51" s="5">
+        <f t="shared" si="0"/>
+        <v>-0.12807928717777672</v>
+      </c>
+      <c r="G51">
         <v>47350</v>
       </c>
-      <c r="G51">
+      <c r="H51">
         <v>40714</v>
       </c>
-      <c r="H51">
+      <c r="I51">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:10">
       <c r="A52" t="s">
         <v>371</v>
       </c>
@@ -6244,17 +6484,21 @@
       <c r="E52">
         <v>4089</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="5">
+        <f t="shared" si="0"/>
+        <v>0.58840792369772565</v>
+      </c>
+      <c r="G52">
         <v>1683</v>
       </c>
-      <c r="G52">
+      <c r="H52">
         <v>708</v>
       </c>
-      <c r="H52">
+      <c r="I52">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:10">
       <c r="B53" t="s">
         <v>373</v>
       </c>
@@ -6267,17 +6511,21 @@
       <c r="E53">
         <v>12187</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="5">
+        <f t="shared" si="0"/>
+        <v>0.51604168376138504</v>
+      </c>
+      <c r="G53">
         <v>5898</v>
       </c>
-      <c r="G53">
+      <c r="H53">
         <v>132</v>
       </c>
-      <c r="H53">
+      <c r="I53">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:10">
       <c r="B54" t="s">
         <v>373</v>
       </c>
@@ -6290,17 +6538,21 @@
       <c r="E54">
         <v>31459</v>
       </c>
-      <c r="F54">
+      <c r="F54" s="5">
+        <f t="shared" si="0"/>
+        <v>0.73063352299818807</v>
+      </c>
+      <c r="G54">
         <v>8474</v>
       </c>
-      <c r="G54">
+      <c r="H54">
         <v>2511</v>
       </c>
-      <c r="H54">
+      <c r="I54">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:10">
       <c r="B55" t="s">
         <v>374</v>
       </c>
@@ -6313,17 +6565,21 @@
       <c r="E55">
         <v>1165</v>
       </c>
-      <c r="F55">
+      <c r="F55" s="5">
+        <f t="shared" si="0"/>
+        <v>0.12703862660944207</v>
+      </c>
+      <c r="G55">
         <v>1017</v>
       </c>
-      <c r="G55">
+      <c r="H55">
         <v>457</v>
       </c>
-      <c r="H55">
+      <c r="I55">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:10">
       <c r="B56" t="s">
         <v>375</v>
       </c>
@@ -6336,17 +6592,21 @@
       <c r="E56">
         <v>1229</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="5">
+        <f t="shared" si="0"/>
+        <v>0.15134255492270138</v>
+      </c>
+      <c r="G56">
         <v>1043</v>
       </c>
-      <c r="G56">
+      <c r="H56">
         <v>398</v>
       </c>
-      <c r="H56">
+      <c r="I56">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:10">
       <c r="B57" t="s">
         <v>376</v>
       </c>
@@ -6359,17 +6619,21 @@
       <c r="E57">
         <v>4187</v>
       </c>
-      <c r="F57">
+      <c r="F57" s="5">
+        <f t="shared" si="0"/>
+        <v>0.14974922378791497</v>
+      </c>
+      <c r="G57">
         <v>3560</v>
       </c>
-      <c r="G57">
+      <c r="H57">
         <v>1056</v>
       </c>
-      <c r="H57">
+      <c r="I57">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:10">
       <c r="B58" t="s">
         <v>377</v>
       </c>
@@ -6382,17 +6646,21 @@
       <c r="E58">
         <v>13469</v>
       </c>
-      <c r="F58">
+      <c r="F58" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5471081743262306</v>
+      </c>
+      <c r="G58">
         <v>6100</v>
       </c>
-      <c r="G58">
+      <c r="H58">
         <v>747</v>
       </c>
-      <c r="H58">
+      <c r="I58">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:10">
       <c r="B59" t="s">
         <v>377</v>
       </c>
@@ -6405,17 +6673,21 @@
       <c r="E59">
         <v>33821</v>
       </c>
-      <c r="F59">
+      <c r="F59" s="5">
+        <f t="shared" si="0"/>
+        <v>0.71902072676739304</v>
+      </c>
+      <c r="G59">
         <v>9503</v>
       </c>
-      <c r="G59">
+      <c r="H59">
         <v>903</v>
       </c>
-      <c r="H59">
+      <c r="I59">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:10">
       <c r="B60" t="s">
         <v>378</v>
       </c>
@@ -6428,20 +6700,24 @@
       <c r="E60">
         <v>1224</v>
       </c>
-      <c r="F60">
+      <c r="F60" s="5">
+        <f t="shared" si="0"/>
+        <v>4.7385620915032678E-2</v>
+      </c>
+      <c r="G60">
         <v>1166</v>
       </c>
-      <c r="G60">
+      <c r="H60">
         <v>202</v>
       </c>
-      <c r="H60">
+      <c r="I60">
         <v>1</v>
       </c>
-      <c r="I60" t="s">
+      <c r="J60" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:10">
       <c r="B61" t="s">
         <v>381</v>
       </c>
@@ -6454,20 +6730,24 @@
       <c r="E61">
         <v>10849</v>
       </c>
-      <c r="F61">
+      <c r="F61" s="5">
+        <f t="shared" si="0"/>
+        <v>0.20591759609180571</v>
+      </c>
+      <c r="G61">
         <v>8615</v>
       </c>
-      <c r="G61">
+      <c r="H61">
         <v>403</v>
       </c>
-      <c r="H61">
+      <c r="I61">
         <v>0</v>
       </c>
-      <c r="I61" t="s">
+      <c r="J61" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:10">
       <c r="B62" t="s">
         <v>382</v>
       </c>
@@ -6477,8 +6757,11 @@
       <c r="D62" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="63" spans="1:9">
+      <c r="F62" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
       <c r="B63" t="s">
         <v>383</v>
       </c>
@@ -6491,20 +6774,24 @@
       <c r="E63">
         <v>28623</v>
       </c>
-      <c r="F63">
+      <c r="F63" s="5">
+        <f t="shared" si="0"/>
+        <v>7.1760472347412924E-2</v>
+      </c>
+      <c r="G63">
         <v>26569</v>
       </c>
-      <c r="G63">
+      <c r="H63">
         <v>1104</v>
       </c>
-      <c r="H63">
+      <c r="I63">
         <v>0</v>
       </c>
-      <c r="I63" t="s">
+      <c r="J63" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:10">
       <c r="B64" t="s">
         <v>383</v>
       </c>
@@ -6517,17 +6804,21 @@
       <c r="E64">
         <v>77024</v>
       </c>
-      <c r="F64">
+      <c r="F64" s="5">
+        <f t="shared" si="0"/>
+        <v>0.23901641046946406</v>
+      </c>
+      <c r="G64">
         <v>58614</v>
       </c>
-      <c r="G64">
+      <c r="H64">
         <v>1050</v>
       </c>
-      <c r="H64">
+      <c r="I64">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:10">
       <c r="B65" t="s">
         <v>383</v>
       </c>
@@ -6540,28 +6831,35 @@
       <c r="E65">
         <v>21196</v>
       </c>
-      <c r="F65">
+      <c r="F65" s="5">
+        <f t="shared" si="0"/>
+        <v>8.3695036799396119E-2</v>
+      </c>
+      <c r="G65">
         <v>19422</v>
       </c>
-      <c r="G65">
+      <c r="H65">
         <v>396</v>
       </c>
-      <c r="H65">
+      <c r="I65">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:10">
       <c r="B66" t="s">
         <v>383</v>
       </c>
       <c r="C66">
         <v>16</v>
       </c>
-      <c r="I66" s="4" t="s">
+      <c r="F66" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="J66" s="4" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:10">
       <c r="B67" t="s">
         <v>386</v>
       </c>
@@ -6571,8 +6869,11 @@
       <c r="D67" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="68" spans="1:9">
+      <c r="F67" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
       <c r="B68" t="s">
         <v>387</v>
       </c>
@@ -6582,8 +6883,11 @@
       <c r="D68" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="69" spans="1:9">
+      <c r="F68" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
       <c r="B69" t="s">
         <v>388</v>
       </c>
@@ -6596,17 +6900,21 @@
       <c r="E69">
         <v>4302</v>
       </c>
-      <c r="F69">
+      <c r="F69" s="5">
+        <f t="shared" ref="F68:F105" si="1">(E69-G69)/E69</f>
+        <v>0.44932589493258951</v>
+      </c>
+      <c r="G69">
         <v>2369</v>
       </c>
-      <c r="G69">
+      <c r="H69">
         <v>2276</v>
       </c>
-      <c r="H69">
+      <c r="I69">
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:10">
       <c r="B70" t="s">
         <v>389</v>
       </c>
@@ -6619,17 +6927,21 @@
       <c r="E70">
         <v>18483</v>
       </c>
-      <c r="F70">
+      <c r="F70" s="5">
+        <f t="shared" si="1"/>
+        <v>0.53048747497700588</v>
+      </c>
+      <c r="G70">
         <v>8678</v>
       </c>
-      <c r="G70">
+      <c r="H70">
         <v>8444</v>
       </c>
-      <c r="H70">
+      <c r="I70">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:10">
       <c r="A71" t="s">
         <v>390</v>
       </c>
@@ -6639,11 +6951,14 @@
       <c r="C71">
         <v>2</v>
       </c>
-      <c r="I71" t="s">
+      <c r="F71" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="J71" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:10">
       <c r="A72" t="s">
         <v>391</v>
       </c>
@@ -6653,11 +6968,14 @@
       <c r="C72">
         <v>2</v>
       </c>
-      <c r="I72" t="s">
+      <c r="F72" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="J72" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:10">
       <c r="A73" t="s">
         <v>392</v>
       </c>
@@ -6670,11 +6988,14 @@
       <c r="D73" t="s">
         <v>401</v>
       </c>
-      <c r="I73" t="s">
+      <c r="F73" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="J73" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:10">
       <c r="A74" t="s">
         <v>393</v>
       </c>
@@ -6690,20 +7011,24 @@
       <c r="E74">
         <v>17673</v>
       </c>
-      <c r="F74">
+      <c r="F74" s="5">
+        <f t="shared" si="1"/>
+        <v>0.12929327222316528</v>
+      </c>
+      <c r="G74">
         <v>15388</v>
       </c>
-      <c r="G74">
+      <c r="H74">
         <v>10348</v>
       </c>
-      <c r="H74">
+      <c r="I74">
         <v>2</v>
       </c>
-      <c r="I74" t="s">
+      <c r="J74" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:10">
       <c r="B75" t="s">
         <v>403</v>
       </c>
@@ -6714,22 +7039,26 @@
         <v>6</v>
       </c>
       <c r="E75">
-        <v>421238</v>
-      </c>
-      <c r="F75">
+        <v>40086</v>
+      </c>
+      <c r="F75" s="5">
+        <f t="shared" si="1"/>
+        <v>3.6845781569625306E-2</v>
+      </c>
+      <c r="G75">
         <v>38609</v>
       </c>
-      <c r="G75">
+      <c r="H75">
         <v>1315</v>
       </c>
-      <c r="H75">
+      <c r="I75">
         <v>0</v>
       </c>
-      <c r="I75" t="s">
+      <c r="J75" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:10">
       <c r="A76" t="s">
         <v>394</v>
       </c>
@@ -6745,17 +7074,21 @@
       <c r="E76">
         <v>184</v>
       </c>
-      <c r="F76">
+      <c r="F76" s="5">
+        <f t="shared" si="1"/>
+        <v>1.0869565217391304E-2</v>
+      </c>
+      <c r="G76">
         <v>182</v>
       </c>
-      <c r="H76">
+      <c r="I76">
         <v>0</v>
       </c>
-      <c r="I76" t="s">
+      <c r="J76" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:10">
       <c r="B77" t="s">
         <v>407</v>
       </c>
@@ -6768,20 +7101,24 @@
       <c r="E77">
         <v>10593</v>
       </c>
-      <c r="F77">
+      <c r="F77" s="5">
+        <f t="shared" si="1"/>
+        <v>0.37392617766449543</v>
+      </c>
+      <c r="G77">
         <v>6632</v>
       </c>
-      <c r="G77">
+      <c r="H77">
         <v>938</v>
       </c>
-      <c r="H77">
+      <c r="I77">
         <v>0</v>
       </c>
-      <c r="I77" t="s">
+      <c r="J77" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:10">
       <c r="B78" t="s">
         <v>410</v>
       </c>
@@ -6791,8 +7128,11 @@
       <c r="D78" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="79" spans="1:9">
+      <c r="F78" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
       <c r="A79" t="s">
         <v>395</v>
       </c>
@@ -6808,17 +7148,21 @@
       <c r="E79">
         <v>3602</v>
       </c>
-      <c r="F79">
+      <c r="F79" s="5">
+        <f t="shared" si="1"/>
+        <v>0.72820655191560246</v>
+      </c>
+      <c r="G79">
         <v>979</v>
       </c>
-      <c r="G79">
+      <c r="H79">
         <v>738</v>
       </c>
-      <c r="H79">
+      <c r="I79">
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:10">
       <c r="A80" t="s">
         <v>396</v>
       </c>
@@ -6831,8 +7175,11 @@
       <c r="D80" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="81" spans="1:12">
+      <c r="F80" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13">
       <c r="B81" t="s">
         <v>414</v>
       </c>
@@ -6845,39 +7192,49 @@
       <c r="E81">
         <v>62456</v>
       </c>
-      <c r="F81">
+      <c r="F81" s="5">
+        <f t="shared" si="1"/>
+        <v>0.16264250032022542</v>
+      </c>
+      <c r="G81">
         <v>52298</v>
       </c>
-      <c r="G81">
+      <c r="H81">
         <v>49719</v>
       </c>
-      <c r="H81">
+      <c r="I81">
         <v>0</v>
       </c>
-      <c r="I81" t="s">
+      <c r="J81" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="82" spans="1:12">
+    <row r="82" spans="1:13">
       <c r="B82" t="s">
         <v>413</v>
       </c>
       <c r="C82">
         <v>4</v>
       </c>
-      <c r="I82" t="s">
+      <c r="F82" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="J82" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="83" spans="1:12">
+    <row r="83" spans="1:13">
       <c r="C83">
         <v>5</v>
       </c>
       <c r="D83" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="84" spans="1:12">
+      <c r="F83" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13">
       <c r="A84" t="s">
         <v>397</v>
       </c>
@@ -6893,17 +7250,21 @@
       <c r="E84">
         <v>32925</v>
       </c>
-      <c r="F84">
+      <c r="F84" s="5">
+        <f t="shared" si="1"/>
+        <v>0.72151860288534553</v>
+      </c>
+      <c r="G84">
         <v>9169</v>
       </c>
-      <c r="G84">
+      <c r="H84">
         <v>7057</v>
       </c>
-      <c r="H84">
+      <c r="I84">
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:12">
+    <row r="85" spans="1:13">
       <c r="A85" t="s">
         <v>420</v>
       </c>
@@ -6916,8 +7277,11 @@
       <c r="D85" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="86" spans="1:12">
+      <c r="F85" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13">
       <c r="B86" t="s">
         <v>418</v>
       </c>
@@ -6930,26 +7294,30 @@
       <c r="E86">
         <v>18636</v>
       </c>
-      <c r="F86">
+      <c r="F86" s="5">
+        <f t="shared" si="1"/>
+        <v>-1.7385705086928525E-2</v>
+      </c>
+      <c r="G86">
         <v>18960</v>
       </c>
-      <c r="G86">
+      <c r="H86">
         <v>216</v>
       </c>
-      <c r="I86" t="s">
+      <c r="J86" t="s">
         <v>419</v>
       </c>
-      <c r="J86">
+      <c r="K86">
         <v>14366</v>
       </c>
-      <c r="K86">
+      <c r="L86">
         <v>160</v>
       </c>
-      <c r="L86" t="s">
+      <c r="M86" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="87" spans="1:12">
+    <row r="87" spans="1:13">
       <c r="B87" t="s">
         <v>422</v>
       </c>
@@ -6962,20 +7330,24 @@
       <c r="E87">
         <v>31833</v>
       </c>
-      <c r="F87">
+      <c r="F87" s="5">
+        <f t="shared" si="1"/>
+        <v>0.38579461565042567</v>
+      </c>
+      <c r="G87">
         <v>19552</v>
       </c>
-      <c r="G87">
+      <c r="H87">
         <v>6084</v>
       </c>
-      <c r="H87">
+      <c r="I87">
         <v>4</v>
       </c>
-      <c r="I87" t="s">
+      <c r="J87" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="88" spans="1:12">
+    <row r="88" spans="1:13">
       <c r="B88" t="s">
         <v>424</v>
       </c>
@@ -6985,11 +7357,14 @@
       <c r="D88" t="s">
         <v>282</v>
       </c>
-      <c r="I88" t="s">
+      <c r="F88" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="J88" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="89" spans="1:12">
+    <row r="89" spans="1:13">
       <c r="C89">
         <v>7</v>
       </c>
@@ -6999,17 +7374,21 @@
       <c r="E89">
         <v>1105</v>
       </c>
-      <c r="F89">
+      <c r="F89" s="5">
+        <f t="shared" si="1"/>
+        <v>0.151131221719457</v>
+      </c>
+      <c r="G89">
         <v>938</v>
       </c>
-      <c r="G89">
+      <c r="H89">
         <v>268</v>
       </c>
-      <c r="H89">
+      <c r="I89">
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:12">
+    <row r="90" spans="1:13">
       <c r="B90" t="s">
         <v>425</v>
       </c>
@@ -7022,20 +7401,24 @@
       <c r="E90">
         <v>1375</v>
       </c>
-      <c r="F90">
+      <c r="F90" s="5">
+        <f t="shared" si="1"/>
+        <v>0.34836363636363638</v>
+      </c>
+      <c r="G90">
         <v>896</v>
       </c>
-      <c r="G90">
+      <c r="H90">
         <v>462</v>
       </c>
-      <c r="H90">
+      <c r="I90">
         <v>0</v>
       </c>
-      <c r="I90" t="s">
+      <c r="J90" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="91" spans="1:12">
+    <row r="91" spans="1:13">
       <c r="B91" t="s">
         <v>426</v>
       </c>
@@ -7048,17 +7431,21 @@
       <c r="E91">
         <v>1158</v>
       </c>
-      <c r="F91">
+      <c r="F91" s="5">
+        <f t="shared" si="1"/>
+        <v>0.31347150259067358</v>
+      </c>
+      <c r="G91">
         <v>795</v>
       </c>
-      <c r="G91">
+      <c r="H91">
         <v>289</v>
       </c>
-      <c r="H91">
+      <c r="I91">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:12">
+    <row r="92" spans="1:13">
       <c r="B92" t="s">
         <v>427</v>
       </c>
@@ -7071,20 +7458,24 @@
       <c r="E92">
         <v>1298</v>
       </c>
-      <c r="F92">
+      <c r="F92" s="5">
+        <f t="shared" si="1"/>
+        <v>2.6194144838212634E-2</v>
+      </c>
+      <c r="G92">
         <v>1264</v>
       </c>
-      <c r="G92">
+      <c r="H92">
         <v>1155</v>
       </c>
-      <c r="H92">
+      <c r="I92">
         <v>0</v>
       </c>
-      <c r="I92" t="s">
+      <c r="J92" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="93" spans="1:12">
+    <row r="93" spans="1:13">
       <c r="B93" t="s">
         <v>429</v>
       </c>
@@ -7097,77 +7488,290 @@
       <c r="E93">
         <v>2362</v>
       </c>
-      <c r="F93">
+      <c r="F93" s="5">
+        <f t="shared" si="1"/>
+        <v>0.43945808636748518</v>
+      </c>
+      <c r="G93">
         <v>1324</v>
       </c>
-      <c r="G93">
+      <c r="H93">
         <v>217</v>
       </c>
-      <c r="H93">
+      <c r="I93">
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:12">
+    <row r="94" spans="1:13">
+      <c r="B94" t="s">
+        <v>431</v>
+      </c>
       <c r="C94">
         <v>12</v>
       </c>
-    </row>
-    <row r="95" spans="1:12">
+      <c r="D94">
+        <v>5</v>
+      </c>
+      <c r="E94">
+        <v>1430</v>
+      </c>
+      <c r="F94" s="5">
+        <f t="shared" si="1"/>
+        <v>0.27552447552447551</v>
+      </c>
+      <c r="G94">
+        <v>1036</v>
+      </c>
+      <c r="H94">
+        <v>732</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13">
+      <c r="B95" t="s">
+        <v>433</v>
+      </c>
       <c r="C95">
         <v>13</v>
       </c>
-    </row>
-    <row r="96" spans="1:12">
+      <c r="D95" t="s">
+        <v>284</v>
+      </c>
+      <c r="F95" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="J95" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13">
       <c r="C96">
         <v>14</v>
       </c>
-    </row>
-    <row r="97" spans="1:3">
+      <c r="D96" t="s">
+        <v>282</v>
+      </c>
+      <c r="F96" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="J96" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10">
       <c r="A97" t="s">
         <v>417</v>
       </c>
+      <c r="B97" t="s">
+        <v>434</v>
+      </c>
       <c r="C97">
         <v>2</v>
       </c>
-    </row>
-    <row r="98" spans="1:3">
+      <c r="D97">
+        <v>9</v>
+      </c>
+      <c r="E97">
+        <v>2821</v>
+      </c>
+      <c r="F97" s="5">
+        <f t="shared" si="1"/>
+        <v>0.31690889755405882</v>
+      </c>
+      <c r="G97">
+        <v>1927</v>
+      </c>
+      <c r="H97">
+        <v>751</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10">
+      <c r="B98" t="s">
+        <v>435</v>
+      </c>
       <c r="C98">
         <v>4</v>
       </c>
-    </row>
-    <row r="99" spans="1:3">
+      <c r="D98" t="s">
+        <v>284</v>
+      </c>
+      <c r="F98" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10">
+      <c r="B99" t="s">
+        <v>436</v>
+      </c>
       <c r="C99">
         <v>5</v>
       </c>
-    </row>
-    <row r="100" spans="1:3">
+      <c r="D99" t="s">
+        <v>282</v>
+      </c>
+      <c r="F99" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10">
+      <c r="B100" t="s">
+        <v>437</v>
+      </c>
       <c r="C100">
         <v>6</v>
       </c>
-    </row>
-    <row r="101" spans="1:3">
+      <c r="D100">
+        <v>6</v>
+      </c>
+      <c r="E100">
+        <v>1290</v>
+      </c>
+      <c r="F100" s="5">
+        <f t="shared" si="1"/>
+        <v>0.20232558139534884</v>
+      </c>
+      <c r="G100">
+        <v>1029</v>
+      </c>
+      <c r="H100">
+        <v>962</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10">
+      <c r="B101" t="s">
+        <v>438</v>
+      </c>
       <c r="C101">
         <v>7</v>
       </c>
-    </row>
-    <row r="102" spans="1:3">
+      <c r="D101" t="s">
+        <v>284</v>
+      </c>
+      <c r="F101" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10">
+      <c r="B102" t="s">
+        <v>439</v>
+      </c>
       <c r="C102">
         <v>8</v>
       </c>
-    </row>
-    <row r="103" spans="1:3">
+      <c r="D102">
+        <v>2</v>
+      </c>
+      <c r="E102">
+        <v>1305</v>
+      </c>
+      <c r="F102" s="5">
+        <f t="shared" si="1"/>
+        <v>2.681992337164751E-2</v>
+      </c>
+      <c r="G102">
+        <v>1270</v>
+      </c>
+      <c r="H102">
+        <v>1247</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10">
+      <c r="B103" t="s">
+        <v>440</v>
+      </c>
       <c r="C103">
         <v>9</v>
       </c>
-    </row>
-    <row r="104" spans="1:3">
+      <c r="D103" t="s">
+        <v>284</v>
+      </c>
+      <c r="F103" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10">
+      <c r="B104" t="s">
+        <v>441</v>
+      </c>
       <c r="C104">
         <v>10</v>
       </c>
-    </row>
-    <row r="105" spans="1:3">
+      <c r="F104" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="J104" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10">
+      <c r="B105" t="s">
+        <v>443</v>
+      </c>
       <c r="C105">
         <v>11</v>
+      </c>
+      <c r="D105">
+        <v>4</v>
+      </c>
+      <c r="E105">
+        <v>12665</v>
+      </c>
+      <c r="F105" s="5">
+        <f t="shared" si="1"/>
+        <v>6.356099486774576E-2</v>
+      </c>
+      <c r="G105">
+        <v>11860</v>
+      </c>
+      <c r="H105">
+        <v>7897</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10">
+      <c r="E106" t="s">
+        <v>447</v>
+      </c>
+      <c r="F106">
+        <f>COUNT(F2:F105)</f>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10">
+      <c r="F107">
+        <f>COUNTIF(F2:F105, "&lt;=.10")</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10">
+      <c r="F108">
+        <f>COUNTIF(F2:F105, "&lt;=.50")-F107</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10">
+      <c r="F109">
+        <f>COUNTIF(F2:F105,"&gt;.50")</f>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/ScratchData/data.xlsx
+++ b/ScratchData/data.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="28125"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="2880" yWindow="0" windowWidth="19700" windowHeight="16320" tabRatio="500" activeTab="2"/>
+    <workbookView xWindow="4600" yWindow="720" windowWidth="28780" windowHeight="16320" tabRatio="500" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="time" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="4" r:id="rId4"/>
+    <sheet name="cleanedData" sheetId="4" r:id="rId4"/>
+    <sheet name="TestPathData" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="140000" concurrentCalc="0"/>
   <extLst>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1199" uniqueCount="456">
   <si>
     <t>Done in 748</t>
   </si>
@@ -834,9 +835,6 @@
     <t>D = 9 pred</t>
   </si>
   <si>
-    <t>BaloonFactory</t>
-  </si>
-  <si>
     <t>Class</t>
   </si>
   <si>
@@ -912,54 +910,6 @@
     <t>getArrow</t>
   </si>
   <si>
-    <t>1f,2t,3f</t>
-  </si>
-  <si>
-    <t>1f,2f</t>
-  </si>
-  <si>
-    <t>1t,5t,7f,8t,9t,10t,11t</t>
-  </si>
-  <si>
-    <t>1t,5f,6f</t>
-  </si>
-  <si>
-    <t>1t,5t,7f,8t,9t,10t,11f</t>
-  </si>
-  <si>
-    <t>1f,2t,3t,4f</t>
-  </si>
-  <si>
-    <t>1t,5t,7t</t>
-  </si>
-  <si>
-    <t>1t,5t,7f,8f,10t,11f</t>
-  </si>
-  <si>
-    <t>1t,5t,7f,8t,9t,10f</t>
-  </si>
-  <si>
-    <t>1t,5t,7f,8f,10f</t>
-  </si>
-  <si>
-    <t>1t,5t,7f,8t,9f,10t,11f</t>
-  </si>
-  <si>
-    <t>1t,5f,6t</t>
-  </si>
-  <si>
-    <t>1t,5t,7f,8t,9f,10f</t>
-  </si>
-  <si>
-    <t>1t,5t,7f,8f,10t,11t</t>
-  </si>
-  <si>
-    <t>1f,2t,3t,4t</t>
-  </si>
-  <si>
-    <t>1t,5t,7f,8t,9f,10t,11t</t>
-  </si>
-  <si>
     <t>Base64</t>
   </si>
   <si>
@@ -1110,6 +1060,9 @@
     <t>getRegionOffse</t>
   </si>
   <si>
+    <t>no</t>
+  </si>
+  <si>
     <t>getBlock</t>
   </si>
   <si>
@@ -1366,6 +1319,78 @@
   </si>
   <si>
     <t>methods</t>
+  </si>
+  <si>
+    <t>BallonFactory</t>
+  </si>
+  <si>
+    <t>Has cond in loops</t>
+  </si>
+  <si>
+    <t>Prec</t>
+  </si>
+  <si>
+    <t>Diff</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paths </t>
+  </si>
+  <si>
+    <t>Path with loops</t>
+  </si>
+  <si>
+    <t>Prec of code %</t>
+  </si>
+  <si>
+    <t>Diff between branches % of code</t>
+  </si>
+  <si>
+    <t>the same</t>
+  </si>
+  <si>
+    <t>with 3 percent we get 46 and 53 paths</t>
+  </si>
+  <si>
+    <t>22 loops!</t>
+  </si>
+  <si>
+    <t>decodeWhiteCodeWord</t>
+  </si>
+  <si>
+    <t>the same -- takes about 9 min to run without loops</t>
+  </si>
+  <si>
+    <t>Path id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Path </t>
+  </si>
+  <si>
+    <t>Path time</t>
+  </si>
+  <si>
+    <t>1f2t</t>
+  </si>
+  <si>
+    <t>1f2f</t>
+  </si>
+  <si>
+    <t>sat/sat</t>
+  </si>
+  <si>
+    <t>sat/unsat</t>
+  </si>
+  <si>
+    <t>unsat/sat</t>
+  </si>
+  <si>
+    <t>unsat/unsat</t>
+  </si>
+  <si>
+    <t>%</t>
   </si>
 </sst>
 </file>
@@ -1404,18 +1429,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1433,8 +1452,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="61">
+  <cellStyleXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1498,13 +1533,13 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="61">
+  <cellStyles count="77">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
@@ -1535,6 +1570,14 @@
     <cellStyle name="Followed Hyperlink" xfId="56" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="58" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="60" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="62" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="64" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="66" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="68" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="70" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="72" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="74" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="76" builtinId="9" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
@@ -1565,6 +1608,14 @@
     <cellStyle name="Hyperlink" xfId="55" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="57" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="59" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="61" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="63" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="65" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="67" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="69" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="71" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="73" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="75" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -5390,50 +5441,51 @@
   <dimension ref="A1:M109"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
+    <col min="1" max="1" width="21.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B1" t="s">
         <v>271</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>272</v>
       </c>
-      <c r="C1" t="s">
-        <v>273</v>
-      </c>
       <c r="D1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E1" t="s">
         <v>275</v>
       </c>
-      <c r="E1" t="s">
-        <v>276</v>
-      </c>
       <c r="F1" t="s">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="G1" t="s">
+        <v>277</v>
+      </c>
+      <c r="H1" t="s">
         <v>278</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>279</v>
       </c>
-      <c r="I1" t="s">
-        <v>280</v>
-      </c>
       <c r="J1" t="s">
+        <v>286</v>
+      </c>
+      <c r="K1" t="s">
         <v>287</v>
-      </c>
-      <c r="K1" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>270</v>
+        <v>432</v>
       </c>
       <c r="B2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -5444,7 +5496,7 @@
       <c r="E2">
         <v>7590</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="4">
         <f>(E2-G2)/E2</f>
         <v>0.38102766798418974</v>
       </c>
@@ -5461,12 +5513,12 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="B3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -5477,7 +5529,7 @@
       <c r="E3">
         <v>1029</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="4">
         <f>(E3-G3)/E3</f>
         <v>4.1788143828960157E-2</v>
       </c>
@@ -5493,49 +5545,49 @@
     </row>
     <row r="4" spans="1:11">
       <c r="B4" t="s">
+        <v>280</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
         <v>281</v>
       </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4" t="s">
-        <v>282</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>446</v>
+      <c r="F4" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="B5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>284</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>446</v>
+        <v>283</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="B6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>284</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>446</v>
+        <v>283</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="B7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -5546,7 +5598,7 @@
       <c r="E7">
         <v>752</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="4">
         <f t="shared" ref="F4:F67" si="0">(E7-G7)/E7</f>
         <v>6.9148936170212769E-2</v>
       </c>
@@ -5562,7 +5614,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="B8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -5573,7 +5625,7 @@
       <c r="E8">
         <v>4486</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="4">
         <f t="shared" si="0"/>
         <v>4.1462327240303166E-2</v>
       </c>
@@ -5584,29 +5636,29 @@
         <v>4100</v>
       </c>
       <c r="J8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="B9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C9">
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>282</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>446</v>
+        <v>281</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="B10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -5617,7 +5669,7 @@
       <c r="E10">
         <v>1997</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="4">
         <f t="shared" si="0"/>
         <v>0.64947421131697547</v>
       </c>
@@ -5628,15 +5680,15 @@
         <v>18</v>
       </c>
       <c r="J10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="B11" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -5647,7 +5699,7 @@
       <c r="E11">
         <v>1144</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="4">
         <f t="shared" si="0"/>
         <v>4.5454545454545456E-2</v>
       </c>
@@ -5657,7 +5709,7 @@
     </row>
     <row r="12" spans="1:11">
       <c r="B12" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="C12">
         <v>4</v>
@@ -5668,7 +5720,7 @@
       <c r="E12">
         <v>1151</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="4">
         <f t="shared" si="0"/>
         <v>3.4752389226759342E-2</v>
       </c>
@@ -5678,35 +5730,35 @@
     </row>
     <row r="13" spans="1:11">
       <c r="B13" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="C13">
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>284</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>446</v>
+        <v>283</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="B14" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
       <c r="C14">
         <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>284</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>446</v>
+        <v>283</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="B15" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="C15">
         <v>13</v>
@@ -5717,7 +5769,7 @@
       <c r="E15">
         <v>369</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="4">
         <f t="shared" si="0"/>
         <v>-5.9620596205962058E-2</v>
       </c>
@@ -5727,21 +5779,21 @@
     </row>
     <row r="16" spans="1:11">
       <c r="B16" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
       <c r="C16">
         <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>319</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>446</v>
+        <v>302</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="B17" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -5752,7 +5804,7 @@
       <c r="E17">
         <v>20633</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="4">
         <f t="shared" si="0"/>
         <v>5.0065429166868611E-2</v>
       </c>
@@ -5760,12 +5812,12 @@
         <v>19600</v>
       </c>
       <c r="J17" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="B18" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="C18">
         <v>18</v>
@@ -5776,7 +5828,7 @@
       <c r="E18">
         <v>10064</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="4">
         <f t="shared" si="0"/>
         <v>2.3350556438791734E-2</v>
       </c>
@@ -5789,7 +5841,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="B19" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
       <c r="C19">
         <v>19</v>
@@ -5800,7 +5852,7 @@
       <c r="E19">
         <v>8729</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="4">
         <f t="shared" si="0"/>
         <v>8.6378737541528236E-2</v>
       </c>
@@ -5814,26 +5866,26 @@
         <v>0</v>
       </c>
       <c r="J19" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="B20" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="C20">
         <v>21</v>
       </c>
       <c r="D20" t="s">
-        <v>284</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>446</v>
+        <v>283</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="B21" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -5844,7 +5896,7 @@
       <c r="E21">
         <v>6269</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="4">
         <f t="shared" si="0"/>
         <v>-0.15233689583665658</v>
       </c>
@@ -5857,10 +5909,10 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="B22" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -5871,7 +5923,7 @@
       <c r="E22">
         <v>6471</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="4">
         <f t="shared" si="0"/>
         <v>0.31556173698037399</v>
       </c>
@@ -5882,26 +5934,26 @@
         <v>2</v>
       </c>
       <c r="J22" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="B23" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="C23">
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>327</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>446</v>
+        <v>310</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="B24" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="C24">
         <v>3</v>
@@ -5912,7 +5964,7 @@
       <c r="E24">
         <v>1928</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="4">
         <f t="shared" si="0"/>
         <v>2.0746887966804979E-3</v>
       </c>
@@ -5923,40 +5975,40 @@
         <v>0</v>
       </c>
       <c r="J24" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="B25" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="C25">
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>282</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>446</v>
+        <v>281</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="B26" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="C26">
         <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>284</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>446</v>
+        <v>283</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="B27" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="C27">
         <v>7</v>
@@ -5967,7 +6019,7 @@
       <c r="E27">
         <v>1845</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="4">
         <f t="shared" si="0"/>
         <v>-9.7560975609756097E-3</v>
       </c>
@@ -5978,40 +6030,40 @@
         <v>0</v>
       </c>
       <c r="J27" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="B28" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="C28">
         <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>282</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>446</v>
+        <v>281</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="B29" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="C29">
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>282</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>446</v>
+        <v>281</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="B30" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="C30">
         <v>10</v>
@@ -6022,7 +6074,7 @@
       <c r="E30">
         <v>16891</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30" s="4">
         <f t="shared" si="0"/>
         <v>0.59286010301343905</v>
       </c>
@@ -6033,12 +6085,12 @@
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="B31" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="C31">
         <v>11</v>
@@ -6049,7 +6101,7 @@
       <c r="E31">
         <v>7407</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F31" s="4">
         <f t="shared" si="0"/>
         <v>3.4561900904549747E-2</v>
       </c>
@@ -6060,12 +6112,12 @@
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="B32" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="C32">
         <v>12</v>
@@ -6076,7 +6128,7 @@
       <c r="E32">
         <v>4790</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32" s="4">
         <f t="shared" si="0"/>
         <v>2.5678496868475991E-2</v>
       </c>
@@ -6086,10 +6138,10 @@
     </row>
     <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="B33" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -6100,7 +6152,7 @@
       <c r="E33">
         <v>3381</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33" s="4">
         <f t="shared" si="0"/>
         <v>-6.9210292812777283E-2</v>
       </c>
@@ -6110,24 +6162,24 @@
     </row>
     <row r="34" spans="1:10">
       <c r="B34" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="C34">
         <v>2</v>
       </c>
       <c r="D34" t="s">
-        <v>345</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>446</v>
+        <v>328</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="B35" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -6138,7 +6190,7 @@
       <c r="E35">
         <v>16006</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="4">
         <f t="shared" si="0"/>
         <v>3.0738473072597777E-2</v>
       </c>
@@ -6151,35 +6203,35 @@
     </row>
     <row r="36" spans="1:10">
       <c r="B36" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="C36">
         <v>2</v>
       </c>
       <c r="D36" t="s">
-        <v>284</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>446</v>
+        <v>283</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="B37" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="C37">
         <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>354</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>446</v>
+        <v>337</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="B38" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="C38">
         <v>4</v>
@@ -6190,7 +6242,7 @@
       <c r="E38">
         <v>4859</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F38" s="4">
         <f t="shared" si="0"/>
         <v>7.4089318789874459E-2</v>
       </c>
@@ -6201,26 +6253,26 @@
         <v>0</v>
       </c>
       <c r="J38" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="B39" t="s">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="C39">
         <v>5</v>
       </c>
       <c r="D39" t="s">
-        <v>284</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>446</v>
+        <v>283</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="B40" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="C40">
         <v>6</v>
@@ -6231,7 +6283,7 @@
       <c r="E40">
         <v>7696</v>
       </c>
-      <c r="F40" s="5">
+      <c r="F40" s="4">
         <f t="shared" si="0"/>
         <v>0.1645010395010395</v>
       </c>
@@ -6244,41 +6296,41 @@
     </row>
     <row r="41" spans="1:10">
       <c r="B41" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="C41">
         <v>7</v>
       </c>
       <c r="D41" t="s">
-        <v>284</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>446</v>
+        <v>283</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="B42" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="C42">
         <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>284</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>446</v>
+        <v>283</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="B43" t="s">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="C43">
         <v>3</v>
@@ -6289,7 +6341,7 @@
       <c r="E43">
         <v>6341</v>
       </c>
-      <c r="F43" s="5">
+      <c r="F43" s="4">
         <f t="shared" si="0"/>
         <v>0.36035325658413497</v>
       </c>
@@ -6299,55 +6351,55 @@
       <c r="I43">
         <v>0</v>
       </c>
-      <c r="J43" s="2" t="s">
-        <v>360</v>
+      <c r="J43" s="1" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="B44" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="C44">
         <v>4</v>
       </c>
       <c r="D44" t="s">
-        <v>282</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>446</v>
+        <v>281</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="B45" t="s">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="C45">
         <v>5</v>
       </c>
       <c r="D45" t="s">
-        <v>282</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>446</v>
+        <v>281</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="B46" t="s">
-        <v>363</v>
+        <v>347</v>
       </c>
       <c r="C46">
         <v>6</v>
       </c>
       <c r="D46" t="s">
-        <v>282</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>446</v>
+        <v>281</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="B47" t="s">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="C47">
         <v>7</v>
@@ -6358,7 +6410,7 @@
       <c r="E47">
         <v>5794</v>
       </c>
-      <c r="F47" s="5">
+      <c r="F47" s="4">
         <f t="shared" si="0"/>
         <v>5.695547117707974E-3</v>
       </c>
@@ -6366,12 +6418,12 @@
         <v>5761</v>
       </c>
       <c r="J47" t="s">
-        <v>364</v>
+        <v>348</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="B48" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="C48">
         <v>8</v>
@@ -6382,7 +6434,7 @@
       <c r="E48">
         <v>3936</v>
       </c>
-      <c r="F48" s="5">
+      <c r="F48" s="4">
         <f t="shared" si="0"/>
         <v>0.11229674796747967</v>
       </c>
@@ -6393,12 +6445,12 @@
         <v>0</v>
       </c>
       <c r="J48" t="s">
-        <v>364</v>
+        <v>348</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="B49" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="C49">
         <v>9</v>
@@ -6409,7 +6461,7 @@
       <c r="E49">
         <v>2535</v>
       </c>
-      <c r="F49" s="5">
+      <c r="F49" s="4">
         <f t="shared" si="0"/>
         <v>1.0256410256410256E-2</v>
       </c>
@@ -6419,7 +6471,7 @@
     </row>
     <row r="50" spans="1:10">
       <c r="B50" t="s">
-        <v>368</v>
+        <v>352</v>
       </c>
       <c r="C50">
         <v>10</v>
@@ -6430,7 +6482,7 @@
       <c r="E50">
         <v>1242</v>
       </c>
-      <c r="F50" s="5">
+      <c r="F50" s="4">
         <f t="shared" si="0"/>
         <v>5.7165861513687598E-2</v>
       </c>
@@ -6440,10 +6492,10 @@
     </row>
     <row r="51" spans="1:10">
       <c r="A51" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="B51" t="s">
-        <v>370</v>
+        <v>354</v>
       </c>
       <c r="C51">
         <v>3</v>
@@ -6451,10 +6503,10 @@
       <c r="D51">
         <v>2</v>
       </c>
-      <c r="E51" s="3">
+      <c r="E51" s="2">
         <v>41974</v>
       </c>
-      <c r="F51" s="5">
+      <c r="F51" s="4">
         <f t="shared" si="0"/>
         <v>-0.12807928717777672</v>
       </c>
@@ -6470,10 +6522,10 @@
     </row>
     <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="B52" t="s">
-        <v>372</v>
+        <v>356</v>
       </c>
       <c r="C52">
         <v>2</v>
@@ -6484,7 +6536,7 @@
       <c r="E52">
         <v>4089</v>
       </c>
-      <c r="F52" s="5">
+      <c r="F52" s="4">
         <f t="shared" si="0"/>
         <v>0.58840792369772565</v>
       </c>
@@ -6500,7 +6552,7 @@
     </row>
     <row r="53" spans="1:10">
       <c r="B53" t="s">
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="C53">
         <v>3</v>
@@ -6511,7 +6563,7 @@
       <c r="E53">
         <v>12187</v>
       </c>
-      <c r="F53" s="5">
+      <c r="F53" s="4">
         <f t="shared" si="0"/>
         <v>0.51604168376138504</v>
       </c>
@@ -6527,7 +6579,7 @@
     </row>
     <row r="54" spans="1:10">
       <c r="B54" t="s">
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="C54">
         <v>4</v>
@@ -6538,7 +6590,7 @@
       <c r="E54">
         <v>31459</v>
       </c>
-      <c r="F54" s="5">
+      <c r="F54" s="4">
         <f t="shared" si="0"/>
         <v>0.73063352299818807</v>
       </c>
@@ -6554,7 +6606,7 @@
     </row>
     <row r="55" spans="1:10">
       <c r="B55" t="s">
-        <v>374</v>
+        <v>358</v>
       </c>
       <c r="C55">
         <v>5</v>
@@ -6565,7 +6617,7 @@
       <c r="E55">
         <v>1165</v>
       </c>
-      <c r="F55" s="5">
+      <c r="F55" s="4">
         <f t="shared" si="0"/>
         <v>0.12703862660944207</v>
       </c>
@@ -6581,7 +6633,7 @@
     </row>
     <row r="56" spans="1:10">
       <c r="B56" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="C56">
         <v>6</v>
@@ -6592,7 +6644,7 @@
       <c r="E56">
         <v>1229</v>
       </c>
-      <c r="F56" s="5">
+      <c r="F56" s="4">
         <f t="shared" si="0"/>
         <v>0.15134255492270138</v>
       </c>
@@ -6608,7 +6660,7 @@
     </row>
     <row r="57" spans="1:10">
       <c r="B57" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="C57">
         <v>7</v>
@@ -6619,7 +6671,7 @@
       <c r="E57">
         <v>4187</v>
       </c>
-      <c r="F57" s="5">
+      <c r="F57" s="4">
         <f t="shared" si="0"/>
         <v>0.14974922378791497</v>
       </c>
@@ -6635,7 +6687,7 @@
     </row>
     <row r="58" spans="1:10">
       <c r="B58" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="C58">
         <v>8</v>
@@ -6646,7 +6698,7 @@
       <c r="E58">
         <v>13469</v>
       </c>
-      <c r="F58" s="5">
+      <c r="F58" s="4">
         <f t="shared" si="0"/>
         <v>0.5471081743262306</v>
       </c>
@@ -6662,7 +6714,7 @@
     </row>
     <row r="59" spans="1:10">
       <c r="B59" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="C59">
         <v>9</v>
@@ -6673,7 +6725,7 @@
       <c r="E59">
         <v>33821</v>
       </c>
-      <c r="F59" s="5">
+      <c r="F59" s="4">
         <f t="shared" si="0"/>
         <v>0.71902072676739304</v>
       </c>
@@ -6689,7 +6741,7 @@
     </row>
     <row r="60" spans="1:10">
       <c r="B60" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="C60">
         <v>10</v>
@@ -6700,7 +6752,7 @@
       <c r="E60">
         <v>1224</v>
       </c>
-      <c r="F60" s="5">
+      <c r="F60" s="4">
         <f t="shared" si="0"/>
         <v>4.7385620915032678E-2</v>
       </c>
@@ -6714,12 +6766,12 @@
         <v>1</v>
       </c>
       <c r="J60" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="B61" t="s">
-        <v>381</v>
+        <v>365</v>
       </c>
       <c r="C61">
         <v>11</v>
@@ -6730,7 +6782,7 @@
       <c r="E61">
         <v>10849</v>
       </c>
-      <c r="F61" s="5">
+      <c r="F61" s="4">
         <f t="shared" si="0"/>
         <v>0.20591759609180571</v>
       </c>
@@ -6744,26 +6796,26 @@
         <v>0</v>
       </c>
       <c r="J61" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="B62" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C62">
         <v>12</v>
       </c>
       <c r="D62" t="s">
-        <v>284</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>446</v>
+        <v>283</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="B63" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="C63">
         <v>13</v>
@@ -6774,7 +6826,7 @@
       <c r="E63">
         <v>28623</v>
       </c>
-      <c r="F63" s="5">
+      <c r="F63" s="4">
         <f t="shared" si="0"/>
         <v>7.1760472347412924E-2</v>
       </c>
@@ -6788,12 +6840,12 @@
         <v>0</v>
       </c>
       <c r="J63" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="B64" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="C64">
         <v>14</v>
@@ -6804,7 +6856,7 @@
       <c r="E64">
         <v>77024</v>
       </c>
-      <c r="F64" s="5">
+      <c r="F64" s="4">
         <f t="shared" si="0"/>
         <v>0.23901641046946406</v>
       </c>
@@ -6820,7 +6872,7 @@
     </row>
     <row r="65" spans="1:10">
       <c r="B65" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="C65">
         <v>15</v>
@@ -6831,7 +6883,7 @@
       <c r="E65">
         <v>21196</v>
       </c>
-      <c r="F65" s="5">
+      <c r="F65" s="4">
         <f t="shared" si="0"/>
         <v>8.3695036799396119E-2</v>
       </c>
@@ -6847,49 +6899,49 @@
     </row>
     <row r="66" spans="1:10">
       <c r="B66" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="C66">
         <v>16</v>
       </c>
-      <c r="F66" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="J66" s="4" t="s">
-        <v>385</v>
+      <c r="F66" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="B67" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
       <c r="C67">
         <v>17</v>
       </c>
       <c r="D67" t="s">
-        <v>284</v>
-      </c>
-      <c r="F67" s="5" t="s">
-        <v>446</v>
+        <v>283</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="B68" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="C68">
         <v>18</v>
       </c>
       <c r="D68" t="s">
-        <v>284</v>
-      </c>
-      <c r="F68" s="5" t="s">
-        <v>446</v>
+        <v>283</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="B69" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="C69">
         <v>20</v>
@@ -6900,7 +6952,7 @@
       <c r="E69">
         <v>4302</v>
       </c>
-      <c r="F69" s="5">
+      <c r="F69" s="4">
         <f t="shared" ref="F68:F105" si="1">(E69-G69)/E69</f>
         <v>0.44932589493258951</v>
       </c>
@@ -6916,7 +6968,7 @@
     </row>
     <row r="70" spans="1:10">
       <c r="B70" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="C70">
         <v>21</v>
@@ -6927,7 +6979,7 @@
       <c r="E70">
         <v>18483</v>
       </c>
-      <c r="F70" s="5">
+      <c r="F70" s="4">
         <f t="shared" si="1"/>
         <v>0.53048747497700588</v>
       </c>
@@ -6941,66 +6993,66 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
-      <c r="A71" t="s">
-        <v>390</v>
-      </c>
-      <c r="B71" t="s">
-        <v>398</v>
-      </c>
-      <c r="C71">
+    <row r="71" spans="1:10" s="3" customFormat="1">
+      <c r="A71" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="C71" s="3">
         <v>2</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="J71" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10">
-      <c r="A72" t="s">
-        <v>391</v>
-      </c>
-      <c r="B72" t="s">
-        <v>398</v>
-      </c>
-      <c r="C72">
+        <v>430</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" s="3" customFormat="1">
+      <c r="A72" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="C72" s="3">
         <v>2</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="J72" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10">
-      <c r="A73" t="s">
-        <v>392</v>
-      </c>
-      <c r="B73" t="s">
-        <v>400</v>
-      </c>
-      <c r="C73">
+        <v>430</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" s="3" customFormat="1">
+      <c r="A73" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C73" s="3">
         <v>2</v>
       </c>
-      <c r="D73" t="s">
-        <v>401</v>
+      <c r="D73" s="3" t="s">
+        <v>385</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="J73" t="s">
-        <v>402</v>
+        <v>430</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="B74" t="s">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="C74">
         <v>2</v>
@@ -7011,7 +7063,7 @@
       <c r="E74">
         <v>17673</v>
       </c>
-      <c r="F74" s="5">
+      <c r="F74" s="4">
         <f t="shared" si="1"/>
         <v>0.12929327222316528</v>
       </c>
@@ -7025,12 +7077,12 @@
         <v>2</v>
       </c>
       <c r="J74" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="B75" t="s">
-        <v>403</v>
+        <v>387</v>
       </c>
       <c r="C75">
         <v>3</v>
@@ -7041,7 +7093,7 @@
       <c r="E75">
         <v>40086</v>
       </c>
-      <c r="F75" s="5">
+      <c r="F75" s="4">
         <f t="shared" si="1"/>
         <v>3.6845781569625306E-2</v>
       </c>
@@ -7055,15 +7107,15 @@
         <v>0</v>
       </c>
       <c r="J75" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="B76" t="s">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -7074,7 +7126,7 @@
       <c r="E76">
         <v>184</v>
       </c>
-      <c r="F76" s="5">
+      <c r="F76" s="4">
         <f t="shared" si="1"/>
         <v>1.0869565217391304E-2</v>
       </c>
@@ -7085,12 +7137,12 @@
         <v>0</v>
       </c>
       <c r="J76" t="s">
-        <v>406</v>
+        <v>390</v>
       </c>
     </row>
     <row r="77" spans="1:10">
       <c r="B77" t="s">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -7101,7 +7153,7 @@
       <c r="E77">
         <v>10593</v>
       </c>
-      <c r="F77" s="5">
+      <c r="F77" s="4">
         <f t="shared" si="1"/>
         <v>0.37392617766449543</v>
       </c>
@@ -7115,29 +7167,29 @@
         <v>0</v>
       </c>
       <c r="J77" t="s">
-        <v>408</v>
+        <v>392</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="B78" t="s">
-        <v>410</v>
+        <v>394</v>
       </c>
       <c r="C78">
         <v>2</v>
       </c>
       <c r="D78" t="s">
-        <v>409</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>446</v>
+        <v>393</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" t="s">
+        <v>379</v>
+      </c>
+      <c r="B79" t="s">
         <v>395</v>
-      </c>
-      <c r="B79" t="s">
-        <v>411</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -7148,7 +7200,7 @@
       <c r="E79">
         <v>3602</v>
       </c>
-      <c r="F79" s="5">
+      <c r="F79" s="4">
         <f t="shared" si="1"/>
         <v>0.72820655191560246</v>
       </c>
@@ -7164,24 +7216,24 @@
     </row>
     <row r="80" spans="1:10">
       <c r="A80" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="B80" t="s">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="C80">
         <v>1</v>
       </c>
       <c r="D80" t="s">
-        <v>282</v>
-      </c>
-      <c r="F80" s="5" t="s">
-        <v>446</v>
+        <v>281</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="81" spans="1:13">
       <c r="B81" t="s">
-        <v>414</v>
+        <v>398</v>
       </c>
       <c r="C81">
         <v>3</v>
@@ -7192,7 +7244,7 @@
       <c r="E81">
         <v>62456</v>
       </c>
-      <c r="F81" s="5">
+      <c r="F81" s="4">
         <f t="shared" si="1"/>
         <v>0.16264250032022542</v>
       </c>
@@ -7206,21 +7258,21 @@
         <v>0</v>
       </c>
       <c r="J81" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13">
-      <c r="B82" t="s">
-        <v>413</v>
-      </c>
-      <c r="C82">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" s="3" customFormat="1">
+      <c r="B82" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="C82" s="3">
         <v>4</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="J82" t="s">
-        <v>415</v>
+        <v>430</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -7228,18 +7280,18 @@
         <v>5</v>
       </c>
       <c r="D83" t="s">
-        <v>282</v>
-      </c>
-      <c r="F83" s="5" t="s">
-        <v>446</v>
+        <v>281</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="84" spans="1:13">
       <c r="A84" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="B84" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="C84">
         <v>1</v>
@@ -7250,7 +7302,7 @@
       <c r="E84">
         <v>32925</v>
       </c>
-      <c r="F84" s="5">
+      <c r="F84" s="4">
         <f t="shared" si="1"/>
         <v>0.72151860288534553</v>
       </c>
@@ -7266,24 +7318,24 @@
     </row>
     <row r="85" spans="1:13">
       <c r="A85" t="s">
-        <v>420</v>
+        <v>404</v>
       </c>
       <c r="B85" t="s">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="C85">
         <v>2</v>
       </c>
       <c r="D85" t="s">
-        <v>282</v>
-      </c>
-      <c r="F85" s="5" t="s">
-        <v>446</v>
+        <v>281</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="86" spans="1:13">
       <c r="B86" t="s">
-        <v>418</v>
+        <v>402</v>
       </c>
       <c r="C86">
         <v>4</v>
@@ -7294,7 +7346,7 @@
       <c r="E86">
         <v>18636</v>
       </c>
-      <c r="F86" s="5">
+      <c r="F86" s="4">
         <f t="shared" si="1"/>
         <v>-1.7385705086928525E-2</v>
       </c>
@@ -7305,7 +7357,7 @@
         <v>216</v>
       </c>
       <c r="J86" t="s">
-        <v>419</v>
+        <v>403</v>
       </c>
       <c r="K86">
         <v>14366</v>
@@ -7314,12 +7366,12 @@
         <v>160</v>
       </c>
       <c r="M86" t="s">
-        <v>421</v>
+        <v>405</v>
       </c>
     </row>
     <row r="87" spans="1:13">
       <c r="B87" t="s">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="C87">
         <v>5</v>
@@ -7330,7 +7382,7 @@
       <c r="E87">
         <v>31833</v>
       </c>
-      <c r="F87" s="5">
+      <c r="F87" s="4">
         <f t="shared" si="1"/>
         <v>0.38579461565042567</v>
       </c>
@@ -7344,24 +7396,24 @@
         <v>4</v>
       </c>
       <c r="J87" t="s">
-        <v>423</v>
+        <v>407</v>
       </c>
     </row>
     <row r="88" spans="1:13">
       <c r="B88" t="s">
-        <v>424</v>
+        <v>408</v>
       </c>
       <c r="C88">
         <v>6</v>
       </c>
       <c r="D88" t="s">
-        <v>282</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>446</v>
+        <v>281</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>430</v>
       </c>
       <c r="J88" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -7374,7 +7426,7 @@
       <c r="E89">
         <v>1105</v>
       </c>
-      <c r="F89" s="5">
+      <c r="F89" s="4">
         <f t="shared" si="1"/>
         <v>0.151131221719457</v>
       </c>
@@ -7390,7 +7442,7 @@
     </row>
     <row r="90" spans="1:13">
       <c r="B90" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="C90">
         <v>8</v>
@@ -7401,7 +7453,7 @@
       <c r="E90">
         <v>1375</v>
       </c>
-      <c r="F90" s="5">
+      <c r="F90" s="4">
         <f t="shared" si="1"/>
         <v>0.34836363636363638</v>
       </c>
@@ -7415,12 +7467,12 @@
         <v>0</v>
       </c>
       <c r="J90" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
     </row>
     <row r="91" spans="1:13">
       <c r="B91" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="C91">
         <v>9</v>
@@ -7431,7 +7483,7 @@
       <c r="E91">
         <v>1158</v>
       </c>
-      <c r="F91" s="5">
+      <c r="F91" s="4">
         <f t="shared" si="1"/>
         <v>0.31347150259067358</v>
       </c>
@@ -7447,7 +7499,7 @@
     </row>
     <row r="92" spans="1:13">
       <c r="B92" t="s">
-        <v>427</v>
+        <v>411</v>
       </c>
       <c r="C92">
         <v>10</v>
@@ -7458,7 +7510,7 @@
       <c r="E92">
         <v>1298</v>
       </c>
-      <c r="F92" s="5">
+      <c r="F92" s="4">
         <f t="shared" si="1"/>
         <v>2.6194144838212634E-2</v>
       </c>
@@ -7472,12 +7524,12 @@
         <v>0</v>
       </c>
       <c r="J92" t="s">
-        <v>428</v>
+        <v>412</v>
       </c>
     </row>
     <row r="93" spans="1:13">
       <c r="B93" t="s">
-        <v>429</v>
+        <v>413</v>
       </c>
       <c r="C93">
         <v>11</v>
@@ -7488,7 +7540,7 @@
       <c r="E93">
         <v>2362</v>
       </c>
-      <c r="F93" s="5">
+      <c r="F93" s="4">
         <f t="shared" si="1"/>
         <v>0.43945808636748518</v>
       </c>
@@ -7504,7 +7556,7 @@
     </row>
     <row r="94" spans="1:13">
       <c r="B94" t="s">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="C94">
         <v>12</v>
@@ -7515,7 +7567,7 @@
       <c r="E94">
         <v>1430</v>
       </c>
-      <c r="F94" s="5">
+      <c r="F94" s="4">
         <f t="shared" si="1"/>
         <v>0.27552447552447551</v>
       </c>
@@ -7529,24 +7581,24 @@
         <v>0</v>
       </c>
       <c r="J94" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
     </row>
     <row r="95" spans="1:13">
       <c r="B95" t="s">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="C95">
         <v>13</v>
       </c>
       <c r="D95" t="s">
-        <v>284</v>
-      </c>
-      <c r="F95" s="5" t="s">
-        <v>446</v>
+        <v>283</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>430</v>
       </c>
       <c r="J95" t="s">
-        <v>432</v>
+        <v>416</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -7554,21 +7606,21 @@
         <v>14</v>
       </c>
       <c r="D96" t="s">
-        <v>282</v>
-      </c>
-      <c r="F96" s="5" t="s">
-        <v>446</v>
+        <v>281</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>430</v>
       </c>
       <c r="J96" t="s">
-        <v>432</v>
+        <v>416</v>
       </c>
     </row>
     <row r="97" spans="1:10">
       <c r="A97" t="s">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="B97" t="s">
-        <v>434</v>
+        <v>418</v>
       </c>
       <c r="C97">
         <v>2</v>
@@ -7579,7 +7631,7 @@
       <c r="E97">
         <v>2821</v>
       </c>
-      <c r="F97" s="5">
+      <c r="F97" s="4">
         <f t="shared" si="1"/>
         <v>0.31690889755405882</v>
       </c>
@@ -7595,35 +7647,35 @@
     </row>
     <row r="98" spans="1:10">
       <c r="B98" t="s">
-        <v>435</v>
+        <v>419</v>
       </c>
       <c r="C98">
         <v>4</v>
       </c>
       <c r="D98" t="s">
-        <v>284</v>
-      </c>
-      <c r="F98" s="5" t="s">
-        <v>446</v>
+        <v>283</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="99" spans="1:10">
       <c r="B99" t="s">
-        <v>436</v>
+        <v>420</v>
       </c>
       <c r="C99">
         <v>5</v>
       </c>
       <c r="D99" t="s">
-        <v>282</v>
-      </c>
-      <c r="F99" s="5" t="s">
-        <v>446</v>
+        <v>281</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="100" spans="1:10">
       <c r="B100" t="s">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="C100">
         <v>6</v>
@@ -7634,7 +7686,7 @@
       <c r="E100">
         <v>1290</v>
       </c>
-      <c r="F100" s="5">
+      <c r="F100" s="4">
         <f t="shared" si="1"/>
         <v>0.20232558139534884</v>
       </c>
@@ -7650,21 +7702,21 @@
     </row>
     <row r="101" spans="1:10">
       <c r="B101" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="C101">
         <v>7</v>
       </c>
       <c r="D101" t="s">
-        <v>284</v>
-      </c>
-      <c r="F101" s="5" t="s">
-        <v>446</v>
+        <v>283</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="102" spans="1:10">
       <c r="B102" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="C102">
         <v>8</v>
@@ -7675,7 +7727,7 @@
       <c r="E102">
         <v>1305</v>
       </c>
-      <c r="F102" s="5">
+      <c r="F102" s="4">
         <f t="shared" si="1"/>
         <v>2.681992337164751E-2</v>
       </c>
@@ -7691,35 +7743,35 @@
     </row>
     <row r="103" spans="1:10">
       <c r="B103" t="s">
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="C103">
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>284</v>
-      </c>
-      <c r="F103" s="5" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10">
-      <c r="B104" t="s">
-        <v>441</v>
-      </c>
-      <c r="C104">
+        <v>283</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" s="3" customFormat="1">
+      <c r="B104" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="C104" s="3">
         <v>10</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="J104" t="s">
-        <v>442</v>
+        <v>430</v>
+      </c>
+      <c r="J104" s="3" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="105" spans="1:10">
       <c r="B105" t="s">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="C105">
         <v>11</v>
@@ -7730,7 +7782,7 @@
       <c r="E105">
         <v>12665</v>
       </c>
-      <c r="F105" s="5">
+      <c r="F105" s="4">
         <f t="shared" si="1"/>
         <v>6.356099486774576E-2</v>
       </c>
@@ -7744,12 +7796,12 @@
         <v>0</v>
       </c>
       <c r="J105" t="s">
-        <v>444</v>
+        <v>428</v>
       </c>
     </row>
     <row r="106" spans="1:10">
       <c r="E106" t="s">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="F106">
         <f>COUNT(F2:F105)</f>
@@ -7787,97 +7839,2171 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:L71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1640625" customWidth="1"/>
+    <col min="5" max="5" width="9.5" customWidth="1"/>
+    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="7" max="7" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2">
+        <v>60</v>
+      </c>
+      <c r="F2" s="2">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H2" s="2">
+        <v>3</v>
+      </c>
+      <c r="I2" s="2">
+        <v>60</v>
+      </c>
+      <c r="J2" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2">
+        <v>60</v>
+      </c>
+      <c r="F3" s="2">
+        <v>15</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C4" s="2">
+        <v>6</v>
+      </c>
+      <c r="D4" s="2">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2">
+        <v>60</v>
+      </c>
+      <c r="F4" s="2">
+        <v>5</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C5" s="2">
+        <v>7</v>
+      </c>
+      <c r="D5" s="2">
+        <v>3</v>
+      </c>
+      <c r="E5" s="2">
+        <v>60</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H5" s="2">
+        <v>3</v>
+      </c>
+      <c r="I5" s="2">
+        <v>60</v>
+      </c>
+      <c r="J5" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C6" s="2">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2">
+        <v>60</v>
+      </c>
+      <c r="F6" s="2">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>3</v>
+      </c>
+      <c r="E7" s="2">
+        <v>60</v>
+      </c>
+      <c r="F7" s="2">
+        <v>4</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="1" t="s">
+      <c r="C8" s="2">
+        <v>4</v>
+      </c>
+      <c r="D8" s="2">
+        <v>3</v>
+      </c>
+      <c r="E8" s="2">
+        <v>60</v>
+      </c>
+      <c r="F8" s="2">
+        <v>4</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C9" s="2">
+        <v>13</v>
+      </c>
+      <c r="D9" s="2">
+        <v>3</v>
+      </c>
+      <c r="E9" s="2">
+        <v>60</v>
+      </c>
+      <c r="F9" s="2">
+        <v>5</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C10" s="2">
+        <v>16</v>
+      </c>
+      <c r="D10" s="2">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2">
+        <v>60</v>
+      </c>
+      <c r="F10" s="2">
+        <v>4</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H10" s="2">
+        <v>3</v>
+      </c>
+      <c r="I10" s="2">
+        <v>60</v>
+      </c>
+      <c r="J10" s="2">
+        <v>4</v>
+      </c>
+      <c r="K10" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C11" s="2">
+        <v>18</v>
+      </c>
+      <c r="D11" s="2">
+        <v>15</v>
+      </c>
+      <c r="E11" s="2">
+        <v>60</v>
+      </c>
+      <c r="F11" s="2">
+        <v>24</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H11" s="2">
+        <v>15</v>
+      </c>
+      <c r="I11" s="2">
+        <v>60</v>
+      </c>
+      <c r="J11" s="2">
+        <v>27</v>
+      </c>
+      <c r="K11" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
+      <c r="C12" s="2">
+        <v>19</v>
+      </c>
+      <c r="D12" s="2">
+        <v>3</v>
+      </c>
+      <c r="E12" s="2">
+        <v>60</v>
+      </c>
+      <c r="F12" s="2">
+        <v>28</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H12" s="2">
+        <v>3</v>
+      </c>
+      <c r="I12" s="2">
+        <v>60</v>
+      </c>
+      <c r="J12" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C13" s="2">
+        <v>20</v>
+      </c>
+      <c r="D13" s="2">
+        <v>15</v>
+      </c>
+      <c r="E13" s="2">
+        <v>60</v>
+      </c>
+      <c r="F13" s="2">
+        <v>33</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H13" s="2">
+        <v>15</v>
+      </c>
+      <c r="I13" s="2">
+        <v>60</v>
+      </c>
+      <c r="J13" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="2" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
+      <c r="B14" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2">
+        <v>3</v>
+      </c>
+      <c r="E14" s="2">
+        <v>60</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H14" s="2">
+        <v>3</v>
+      </c>
+      <c r="I14" s="2">
+        <v>60</v>
+      </c>
+      <c r="J14" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
+      <c r="C15" s="2">
+        <v>2</v>
+      </c>
+      <c r="D15" s="2">
+        <v>3</v>
+      </c>
+      <c r="E15" s="2">
+        <v>60</v>
+      </c>
+      <c r="F15" s="2">
+        <v>3</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>302</v>
-      </c>
+      <c r="C16" s="2">
+        <v>3</v>
+      </c>
+      <c r="D16" s="2">
+        <v>3</v>
+      </c>
+      <c r="E16" s="2">
+        <v>60</v>
+      </c>
+      <c r="F16" s="2">
+        <v>2</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H16" s="2">
+        <v>3</v>
+      </c>
+      <c r="I16" s="2">
+        <v>60</v>
+      </c>
+      <c r="J16" s="2">
+        <v>2</v>
+      </c>
+      <c r="K16" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C17" s="2">
+        <v>6</v>
+      </c>
+      <c r="D17" s="2">
+        <v>3</v>
+      </c>
+      <c r="E17" s="2">
+        <v>60</v>
+      </c>
+      <c r="F17" s="2">
+        <v>3</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C18" s="2">
+        <v>7</v>
+      </c>
+      <c r="D18" s="2">
+        <v>3</v>
+      </c>
+      <c r="E18" s="2">
+        <v>60</v>
+      </c>
+      <c r="F18" s="2">
+        <v>2</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H18" s="2">
+        <v>3</v>
+      </c>
+      <c r="I18" s="2">
+        <v>60</v>
+      </c>
+      <c r="J18" s="2">
+        <v>2</v>
+      </c>
+      <c r="K18" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C19" s="2">
+        <v>10</v>
+      </c>
+      <c r="D19" s="2">
+        <v>15</v>
+      </c>
+      <c r="E19" s="2">
+        <v>30</v>
+      </c>
+      <c r="F19" s="2">
+        <v>32</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C20" s="2">
+        <v>11</v>
+      </c>
+      <c r="D20" s="2">
+        <v>20</v>
+      </c>
+      <c r="E20" s="2">
+        <v>15</v>
+      </c>
+      <c r="F20" s="2">
+        <v>13</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C21" s="2">
+        <v>12</v>
+      </c>
+      <c r="D21" s="2">
+        <v>20</v>
+      </c>
+      <c r="E21" s="2">
+        <v>30</v>
+      </c>
+      <c r="F21" s="2">
+        <v>17</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2">
+        <v>3</v>
+      </c>
+      <c r="E22" s="2">
+        <v>60</v>
+      </c>
+      <c r="F22" s="2">
+        <v>7</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2">
+        <v>3</v>
+      </c>
+      <c r="E23" s="2">
+        <v>60</v>
+      </c>
+      <c r="F23" s="2">
+        <v>16</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H23" s="2">
+        <v>3</v>
+      </c>
+      <c r="I23" s="2">
+        <v>60</v>
+      </c>
+      <c r="J23" s="2">
+        <v>16</v>
+      </c>
+      <c r="K23" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C24" s="2">
+        <v>3</v>
+      </c>
+      <c r="D24" s="2">
+        <v>3</v>
+      </c>
+      <c r="E24" s="2">
+        <v>60</v>
+      </c>
+      <c r="F24" s="2">
+        <v>3</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H24" s="2">
+        <v>3</v>
+      </c>
+      <c r="I24" s="2">
+        <v>60</v>
+      </c>
+      <c r="J24" s="2">
+        <v>3</v>
+      </c>
+      <c r="K24" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="C25" s="2">
+        <v>4</v>
+      </c>
+      <c r="D25" s="2">
+        <v>3</v>
+      </c>
+      <c r="E25" s="2">
+        <v>60</v>
+      </c>
+      <c r="F25" s="2">
+        <v>9</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H25" s="2">
+        <v>3</v>
+      </c>
+      <c r="I25" s="2">
+        <v>60</v>
+      </c>
+      <c r="J25" s="2">
+        <v>9</v>
+      </c>
+      <c r="K25" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C26" s="2">
+        <v>6</v>
+      </c>
+      <c r="D26" s="2">
+        <v>3</v>
+      </c>
+      <c r="E26" s="2">
+        <v>60</v>
+      </c>
+      <c r="F26" s="2">
+        <v>2</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H26" s="2">
+        <v>3</v>
+      </c>
+      <c r="I26" s="2">
+        <v>60</v>
+      </c>
+      <c r="J26" s="2">
+        <v>2</v>
+      </c>
+      <c r="K26" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C27" s="2">
+        <v>7</v>
+      </c>
+      <c r="D27" s="2">
+        <v>3</v>
+      </c>
+      <c r="E27" s="2">
+        <v>60</v>
+      </c>
+      <c r="F27" s="2">
+        <v>7</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C28" s="2">
+        <v>3</v>
+      </c>
+      <c r="D28" s="2">
+        <v>3</v>
+      </c>
+      <c r="E28" s="2">
+        <v>60</v>
+      </c>
+      <c r="F28" s="2">
+        <v>3</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H28" s="2">
+        <v>3</v>
+      </c>
+      <c r="I28" s="2">
+        <v>60</v>
+      </c>
+      <c r="J28" s="2">
+        <v>3</v>
+      </c>
+      <c r="K28" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C29" s="2">
+        <v>7</v>
+      </c>
+      <c r="D29" s="2">
+        <v>3</v>
+      </c>
+      <c r="E29" s="2">
+        <v>60</v>
+      </c>
+      <c r="F29" s="2">
+        <v>6</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H29" s="2">
+        <v>3</v>
+      </c>
+      <c r="I29" s="2">
+        <v>60</v>
+      </c>
+      <c r="J29" s="2">
+        <v>6</v>
+      </c>
+      <c r="K29" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C30" s="2">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2">
+        <v>3</v>
+      </c>
+      <c r="E30" s="2">
+        <v>60</v>
+      </c>
+      <c r="F30" s="2">
+        <v>11</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H30" s="2">
+        <v>3</v>
+      </c>
+      <c r="I30" s="2">
+        <v>60</v>
+      </c>
+      <c r="J30" s="2">
+        <v>11</v>
+      </c>
+      <c r="K30" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C31" s="2">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2">
+        <v>3</v>
+      </c>
+      <c r="E31" s="2">
+        <v>60</v>
+      </c>
+      <c r="F31" s="2">
+        <v>5</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H31" s="2">
+        <v>3</v>
+      </c>
+      <c r="I31" s="2">
+        <v>60</v>
+      </c>
+      <c r="J31" s="2">
+        <v>5</v>
+      </c>
+      <c r="K31" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C32" s="2">
+        <v>10</v>
+      </c>
+      <c r="D32" s="2">
+        <v>3</v>
+      </c>
+      <c r="E32" s="2">
+        <v>60</v>
+      </c>
+      <c r="F32" s="2">
+        <v>32</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C33" s="2">
+        <v>3</v>
+      </c>
+      <c r="D33" s="2">
+        <v>3</v>
+      </c>
+      <c r="E33" s="2">
+        <v>60</v>
+      </c>
+      <c r="F33" s="2">
+        <v>2</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H33" s="2">
+        <v>3</v>
+      </c>
+      <c r="I33" s="2">
+        <v>60</v>
+      </c>
+      <c r="J33" s="2">
+        <v>2</v>
+      </c>
+      <c r="K33" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C34" s="2">
+        <v>2</v>
+      </c>
+      <c r="D34" s="2">
+        <v>3</v>
+      </c>
+      <c r="E34" s="2">
+        <v>60</v>
+      </c>
+      <c r="F34" s="2">
+        <v>8</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C35" s="2">
+        <v>3</v>
+      </c>
+      <c r="D35" s="2">
+        <v>3</v>
+      </c>
+      <c r="E35" s="2">
+        <v>60</v>
+      </c>
+      <c r="F35" s="2">
+        <v>6</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H35" s="2">
+        <v>3</v>
+      </c>
+      <c r="I35" s="2">
+        <v>60</v>
+      </c>
+      <c r="J35" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C36" s="2">
+        <v>4</v>
+      </c>
+      <c r="D36" s="2">
+        <v>3</v>
+      </c>
+      <c r="E36" s="2">
+        <v>60</v>
+      </c>
+      <c r="F36" s="2">
+        <v>9</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H36" s="2">
+        <v>3</v>
+      </c>
+      <c r="I36" s="2">
+        <v>60</v>
+      </c>
+      <c r="J36" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C37" s="2">
+        <v>5</v>
+      </c>
+      <c r="D37" s="2">
+        <v>3</v>
+      </c>
+      <c r="E37" s="2">
+        <v>60</v>
+      </c>
+      <c r="F37" s="2">
+        <v>6</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C38" s="2">
+        <v>6</v>
+      </c>
+      <c r="D38" s="2">
+        <v>3</v>
+      </c>
+      <c r="E38" s="2">
+        <v>60</v>
+      </c>
+      <c r="F38" s="2">
+        <v>10</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C39" s="2">
+        <v>7</v>
+      </c>
+      <c r="D39" s="2">
+        <v>3</v>
+      </c>
+      <c r="E39" s="2">
+        <v>60</v>
+      </c>
+      <c r="F39" s="2">
+        <v>10</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C40" s="2">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2">
+        <v>3</v>
+      </c>
+      <c r="E40" s="2">
+        <v>60</v>
+      </c>
+      <c r="F40" s="2">
+        <v>6</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H40" s="2">
+        <v>3</v>
+      </c>
+      <c r="I40" s="2">
+        <v>60</v>
+      </c>
+      <c r="J40" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C41" s="2">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2">
+        <v>3</v>
+      </c>
+      <c r="E41" s="2">
+        <v>60</v>
+      </c>
+      <c r="F41" s="2">
+        <v>9</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H41" s="2">
+        <v>3</v>
+      </c>
+      <c r="I41" s="2">
+        <v>60</v>
+      </c>
+      <c r="J41" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C42" s="2">
+        <v>10</v>
+      </c>
+      <c r="D42" s="2">
+        <v>3</v>
+      </c>
+      <c r="E42" s="2">
+        <v>60</v>
+      </c>
+      <c r="F42" s="2">
+        <v>0</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H42" s="2">
+        <v>3</v>
+      </c>
+      <c r="I42" s="2">
+        <v>60</v>
+      </c>
+      <c r="J42" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C43" s="2">
+        <v>11</v>
+      </c>
+      <c r="D43" s="2">
+        <v>3</v>
+      </c>
+      <c r="E43" s="2">
+        <v>60</v>
+      </c>
+      <c r="F43" s="2">
+        <v>2</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H43" s="2">
+        <v>3</v>
+      </c>
+      <c r="I43" s="2">
+        <v>60</v>
+      </c>
+      <c r="J43" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C44" s="2">
+        <v>13</v>
+      </c>
+      <c r="D44" s="2">
+        <v>3</v>
+      </c>
+      <c r="E44" s="2">
+        <v>60</v>
+      </c>
+      <c r="F44" s="2">
+        <v>4</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H44" s="2">
+        <v>3</v>
+      </c>
+      <c r="I44" s="2">
+        <v>60</v>
+      </c>
+      <c r="J44" s="2">
+        <v>11</v>
+      </c>
+      <c r="K44" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C45" s="2">
+        <v>14</v>
+      </c>
+      <c r="D45" s="2">
+        <v>3</v>
+      </c>
+      <c r="E45" s="2">
+        <v>60</v>
+      </c>
+      <c r="F45" s="2">
+        <v>11</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H45" s="2">
+        <v>3</v>
+      </c>
+      <c r="I45" s="2">
+        <v>60</v>
+      </c>
+      <c r="J45" s="2">
+        <v>15</v>
+      </c>
+      <c r="K45" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C46" s="2">
+        <v>15</v>
+      </c>
+      <c r="D46" s="2">
+        <v>3</v>
+      </c>
+      <c r="E46" s="2">
+        <v>60</v>
+      </c>
+      <c r="F46" s="2">
+        <v>4</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H46" s="2">
+        <v>3</v>
+      </c>
+      <c r="I46" s="2">
+        <v>60</v>
+      </c>
+      <c r="J46" s="2">
+        <v>4</v>
+      </c>
+      <c r="K46" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C47" s="2">
+        <v>16</v>
+      </c>
+      <c r="D47" s="2">
+        <v>3</v>
+      </c>
+      <c r="E47" s="2">
+        <v>60</v>
+      </c>
+      <c r="F47" s="2">
+        <v>4</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H47" s="2">
+        <v>3</v>
+      </c>
+      <c r="I47" s="2">
+        <v>60</v>
+      </c>
+      <c r="J47" s="2">
+        <v>4</v>
+      </c>
+      <c r="K47" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="C48" s="2">
+        <v>20</v>
+      </c>
+      <c r="D48" s="2">
+        <v>3</v>
+      </c>
+      <c r="E48" s="2">
+        <v>60</v>
+      </c>
+      <c r="F48" s="2">
+        <v>2</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H48" s="2">
+        <v>3</v>
+      </c>
+      <c r="I48" s="2">
+        <v>60</v>
+      </c>
+      <c r="J48" s="2">
+        <v>2</v>
+      </c>
+      <c r="K48" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C49" s="2">
+        <v>21</v>
+      </c>
+      <c r="D49" s="2">
+        <v>3</v>
+      </c>
+      <c r="E49" s="2">
+        <v>60</v>
+      </c>
+      <c r="F49" s="2">
+        <v>2</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H49" s="2">
+        <v>3</v>
+      </c>
+      <c r="I49" s="2">
+        <v>60</v>
+      </c>
+      <c r="J49" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C50" s="2">
+        <v>2</v>
+      </c>
+      <c r="D50" s="2">
+        <v>3</v>
+      </c>
+      <c r="E50" s="2">
+        <v>60</v>
+      </c>
+      <c r="F50" s="2">
+        <v>0</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H50" s="2">
+        <v>3</v>
+      </c>
+      <c r="I50" s="2">
+        <v>60</v>
+      </c>
+      <c r="J50" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C51" s="2">
+        <v>3</v>
+      </c>
+      <c r="D51" s="2">
+        <v>3</v>
+      </c>
+      <c r="E51" s="2">
+        <v>60</v>
+      </c>
+      <c r="F51" s="2">
+        <v>0</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H51" s="2">
+        <v>3</v>
+      </c>
+      <c r="I51" s="2">
+        <v>60</v>
+      </c>
+      <c r="J51" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C52" s="2">
+        <v>0</v>
+      </c>
+      <c r="D52" s="2">
+        <v>3</v>
+      </c>
+      <c r="E52" s="2">
+        <v>60</v>
+      </c>
+      <c r="F52" s="2">
+        <v>4</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53" s="2"/>
+      <c r="B53" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C53" s="2">
+        <v>1</v>
+      </c>
+      <c r="D53" s="2">
+        <v>3</v>
+      </c>
+      <c r="E53" s="2">
+        <v>60</v>
+      </c>
+      <c r="F53" s="2">
+        <v>4</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H53" s="2">
+        <v>3</v>
+      </c>
+      <c r="I53" s="2">
+        <v>60</v>
+      </c>
+      <c r="J53" s="2">
+        <v>4</v>
+      </c>
+      <c r="K53" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="A54" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C54" s="2">
+        <v>1</v>
+      </c>
+      <c r="D54" s="2">
+        <v>3</v>
+      </c>
+      <c r="E54" s="2">
+        <v>60</v>
+      </c>
+      <c r="F54" s="2">
+        <v>8</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="A55" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C55" s="2">
+        <v>3</v>
+      </c>
+      <c r="D55" s="2">
+        <v>3</v>
+      </c>
+      <c r="E55" s="2">
+        <v>60</v>
+      </c>
+      <c r="F55" s="2">
+        <v>0</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H55" s="2">
+        <v>3</v>
+      </c>
+      <c r="I55" s="2">
+        <v>60</v>
+      </c>
+      <c r="J55" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
+      <c r="A56" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C56" s="2">
+        <v>1</v>
+      </c>
+      <c r="D56" s="2">
+        <v>3</v>
+      </c>
+      <c r="E56" s="2">
+        <v>60</v>
+      </c>
+      <c r="F56" s="2">
+        <v>5</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H56" s="2">
+        <v>3</v>
+      </c>
+      <c r="I56" s="2">
+        <v>60</v>
+      </c>
+      <c r="J56" s="2">
+        <v>16</v>
+      </c>
+      <c r="L56">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
+      <c r="A57" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C57" s="2">
+        <v>4</v>
+      </c>
+      <c r="D57" s="2">
+        <v>3</v>
+      </c>
+      <c r="E57" s="2">
+        <v>60</v>
+      </c>
+      <c r="F57" s="2">
+        <v>0</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H57" s="2">
+        <v>3</v>
+      </c>
+      <c r="I57" s="2">
+        <v>60</v>
+      </c>
+      <c r="J57" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12">
+      <c r="A58" s="2"/>
+      <c r="B58" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C58" s="2">
+        <v>5</v>
+      </c>
+      <c r="D58" s="2">
+        <v>3</v>
+      </c>
+      <c r="E58" s="2">
+        <v>60</v>
+      </c>
+      <c r="F58" s="2">
+        <v>5</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H58" s="2">
+        <v>3</v>
+      </c>
+      <c r="I58" s="2">
+        <v>60</v>
+      </c>
+      <c r="J58" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="C59" s="2">
+        <v>7</v>
+      </c>
+      <c r="D59" s="2">
+        <v>3</v>
+      </c>
+      <c r="E59" s="2">
+        <v>60</v>
+      </c>
+      <c r="F59" s="2">
+        <v>3</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H59" s="2">
+        <v>3</v>
+      </c>
+      <c r="I59" s="2">
+        <v>60</v>
+      </c>
+      <c r="J59" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C60" s="2">
+        <v>8</v>
+      </c>
+      <c r="D60" s="2">
+        <v>3</v>
+      </c>
+      <c r="E60" s="2">
+        <v>60</v>
+      </c>
+      <c r="F60" s="2">
+        <v>0</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H60" s="2">
+        <v>3</v>
+      </c>
+      <c r="I60" s="2">
+        <v>60</v>
+      </c>
+      <c r="J60" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C61" s="2">
+        <v>9</v>
+      </c>
+      <c r="D61" s="2">
+        <v>3</v>
+      </c>
+      <c r="E61" s="2">
+        <v>60</v>
+      </c>
+      <c r="F61" s="2">
+        <v>18</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H61" s="2">
+        <v>3</v>
+      </c>
+      <c r="I61" s="2">
+        <v>60</v>
+      </c>
+      <c r="J61" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12">
+      <c r="A62" s="2"/>
+      <c r="B62" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C62" s="2">
+        <v>10</v>
+      </c>
+      <c r="D62" s="2">
+        <v>3</v>
+      </c>
+      <c r="E62" s="2">
+        <v>60</v>
+      </c>
+      <c r="F62" s="2">
+        <v>4</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H62" s="2">
+        <v>3</v>
+      </c>
+      <c r="I62" s="2">
+        <v>60</v>
+      </c>
+      <c r="J62" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12">
+      <c r="A63" s="2"/>
+      <c r="B63" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C63" s="2">
+        <v>11</v>
+      </c>
+      <c r="D63" s="2">
+        <v>3</v>
+      </c>
+      <c r="E63" s="2">
+        <v>60</v>
+      </c>
+      <c r="F63" s="2">
+        <v>19</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+    </row>
+    <row r="64" spans="1:12">
+      <c r="A64" s="2"/>
+      <c r="B64" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C64" s="2">
+        <v>12</v>
+      </c>
+      <c r="D64" s="2">
+        <v>3</v>
+      </c>
+      <c r="E64" s="2">
+        <v>60</v>
+      </c>
+      <c r="F64" s="2">
+        <v>9</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="C65" s="2">
+        <v>13</v>
+      </c>
+      <c r="D65" s="2">
+        <v>3</v>
+      </c>
+      <c r="E65" s="2">
+        <v>60</v>
+      </c>
+      <c r="F65" s="2">
+        <v>2</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C66" s="2">
+        <v>2</v>
+      </c>
+      <c r="D66" s="2">
+        <v>3</v>
+      </c>
+      <c r="E66" s="2">
+        <v>60</v>
+      </c>
+      <c r="F66" s="2">
+        <v>4</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H66" s="2">
+        <v>3</v>
+      </c>
+      <c r="I66" s="2">
+        <v>60</v>
+      </c>
+      <c r="J66" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67" s="2"/>
+      <c r="B67" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C67" s="2">
+        <v>6</v>
+      </c>
+      <c r="D67" s="2">
+        <v>3</v>
+      </c>
+      <c r="E67" s="2">
+        <v>60</v>
+      </c>
+      <c r="F67" s="2">
+        <v>6</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H67" s="2">
+        <v>3</v>
+      </c>
+      <c r="I67" s="2">
+        <v>60</v>
+      </c>
+      <c r="J67" s="2">
+        <v>6</v>
+      </c>
+      <c r="K67" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68" s="2"/>
+      <c r="B68" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="C68" s="2">
+        <v>8</v>
+      </c>
+      <c r="D68" s="2">
+        <v>3</v>
+      </c>
+      <c r="E68" s="2">
+        <v>60</v>
+      </c>
+      <c r="F68" s="2">
+        <v>2</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H68" s="2">
+        <v>3</v>
+      </c>
+      <c r="I68" s="2">
+        <v>60</v>
+      </c>
+      <c r="J68" s="2">
+        <v>2</v>
+      </c>
+      <c r="K68" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C69" s="2">
+        <v>11</v>
+      </c>
+      <c r="D69" s="2">
+        <v>3</v>
+      </c>
+      <c r="E69" s="2">
+        <v>60</v>
+      </c>
+      <c r="F69" s="2">
+        <v>0</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H69" s="2">
+        <v>3</v>
+      </c>
+      <c r="I69" s="2">
+        <v>60</v>
+      </c>
+      <c r="J69" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
     </row>
   </sheetData>
   <sortState ref="A1:A16">
     <sortCondition ref="A1"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
+        <f>AVERAGE(7641,7431,7353)</f>
+        <v>7475</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>210</v>
+      </c>
+      <c r="G2">
+        <v>7169</v>
+      </c>
+      <c r="H2" s="4">
+        <f>G2/$D$2</f>
+        <v>0.95906354515050163</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>449</v>
+      </c>
+      <c r="G3">
+        <v>7283</v>
+      </c>
+      <c r="H3" s="4">
+        <f t="shared" ref="H3:H5" si="0">G3/$D$2</f>
+        <v>0.97431438127090297</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
+        <v>450</v>
+      </c>
+      <c r="G4">
+        <v>7367</v>
+      </c>
+      <c r="H4" s="4">
+        <f t="shared" si="0"/>
+        <v>0.9855518394648829</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5" t="s">
+        <v>211</v>
+      </c>
+      <c r="G5">
+        <v>7902</v>
+      </c>
+      <c r="H5" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0571237458193981</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
       <mx:PLV Mode="0" OnePage="0" WScale="0"/>

--- a/ScratchData/data.xlsx
+++ b/ScratchData/data.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="28125"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="27729"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="4600" yWindow="720" windowWidth="28780" windowHeight="16320" tabRatio="500" activeTab="4"/>
+    <workbookView xWindow="240" yWindow="240" windowWidth="25360" windowHeight="14740" tabRatio="500" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1366,9 +1366,6 @@
     <t>Path id</t>
   </si>
   <si>
-    <t xml:space="preserve">Path </t>
-  </si>
-  <si>
     <t>Path time</t>
   </si>
   <si>
@@ -1391,6 +1388,9 @@
   </si>
   <si>
     <t>%</t>
+  </si>
+  <si>
+    <t>Paths</t>
   </si>
 </sst>
 </file>
@@ -1452,8 +1452,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="77">
+  <cellStyleXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1539,7 +1541,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="77">
+  <cellStyles count="79">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
@@ -1578,6 +1580,7 @@
     <cellStyle name="Followed Hyperlink" xfId="72" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="74" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="76" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="78" builtinId="9" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
@@ -1616,6 +1619,7 @@
     <cellStyle name="Hyperlink" xfId="71" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="73" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="75" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="77" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -5599,7 +5603,7 @@
         <v>752</v>
       </c>
       <c r="F7" s="4">
-        <f t="shared" ref="F4:F67" si="0">(E7-G7)/E7</f>
+        <f t="shared" ref="F7:F65" si="0">(E7-G7)/E7</f>
         <v>6.9148936170212769E-2</v>
       </c>
       <c r="G7">
@@ -6953,7 +6957,7 @@
         <v>4302</v>
       </c>
       <c r="F69" s="4">
-        <f t="shared" ref="F68:F105" si="1">(E69-G69)/E69</f>
+        <f t="shared" ref="F69:F105" si="1">(E69-G69)/E69</f>
         <v>0.44932589493258951</v>
       </c>
       <c r="G69">
@@ -9901,31 +9905,31 @@
         <v>272</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>448</v>
-      </c>
       <c r="H1" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>452</v>
       </c>
       <c r="K1" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -9938,67 +9942,127 @@
       <c r="C2" s="2">
         <v>1</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F2" s="2">
         <f>AVERAGE(7641,7431,7353)</f>
         <v>7475</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>210</v>
-      </c>
       <c r="G2">
         <v>7169</v>
       </c>
       <c r="H2" s="4">
-        <f>G2/$D$2</f>
+        <f>G2/F2</f>
         <v>0.95906354515050163</v>
       </c>
+      <c r="I2">
+        <v>45</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="E3">
+      <c r="D3">
         <v>2</v>
       </c>
-      <c r="F3" t="s">
-        <v>449</v>
+      <c r="E3" t="s">
+        <v>448</v>
+      </c>
+      <c r="F3" s="2">
+        <f t="shared" ref="F3:F5" si="0">AVERAGE(7641,7431,7353)</f>
+        <v>7475</v>
       </c>
       <c r="G3">
         <v>7283</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" ref="H3:H5" si="0">G3/$D$2</f>
+        <f t="shared" ref="H3:H5" si="1">G3/F3</f>
         <v>0.97431438127090297</v>
       </c>
+      <c r="I3">
+        <v>47</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="F4" t="s">
-        <v>450</v>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>449</v>
+      </c>
+      <c r="F4" s="2">
+        <f t="shared" si="0"/>
+        <v>7475</v>
       </c>
       <c r="G4">
         <v>7367</v>
       </c>
       <c r="H4" s="4">
+        <f t="shared" si="1"/>
+        <v>0.9855518394648829</v>
+      </c>
+      <c r="I4">
+        <v>49</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>211</v>
+      </c>
+      <c r="F5" s="2">
         <f t="shared" si="0"/>
-        <v>0.9855518394648829</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5" t="s">
-        <v>211</v>
+        <v>7475</v>
       </c>
       <c r="G5">
         <v>7902</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0571237458193981</v>
+      </c>
+      <c r="I5">
+        <v>49</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/ScratchData/data.xlsx
+++ b/ScratchData/data.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="27729"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="28125"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="240" windowWidth="25360" windowHeight="14740" tabRatio="500" activeTab="4"/>
+    <workbookView xWindow="5260" yWindow="0" windowWidth="25440" windowHeight="14740" tabRatio="500" firstSheet="1" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12,6 +12,9 @@
     <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
     <sheet name="cleanedData" sheetId="4" r:id="rId4"/>
     <sheet name="TestPathData" sheetId="5" r:id="rId5"/>
+    <sheet name="Time Data" sheetId="6" r:id="rId6"/>
+    <sheet name="SatUnsatData" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet5" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="140000" concurrentCalc="0"/>
   <extLst>
@@ -23,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1199" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="486">
   <si>
     <t>Done in 748</t>
   </si>
@@ -1391,6 +1394,96 @@
   </si>
   <si>
     <t>Paths</t>
+  </si>
+  <si>
+    <t>Path Id</t>
+  </si>
+  <si>
+    <t>Path Time</t>
+  </si>
+  <si>
+    <t>test.BallonFactory</t>
+  </si>
+  <si>
+    <t>1t3f4f</t>
+  </si>
+  <si>
+    <t>1f2t3f4f</t>
+  </si>
+  <si>
+    <t>1t3t5f6f</t>
+  </si>
+  <si>
+    <t>1t3f4t5f6f</t>
+  </si>
+  <si>
+    <t>1f2t3t5f6f</t>
+  </si>
+  <si>
+    <t>1t3t5t</t>
+  </si>
+  <si>
+    <t>1f2t3f4t5f6f</t>
+  </si>
+  <si>
+    <t>1t3t5f6t</t>
+  </si>
+  <si>
+    <t>1t3f4t5t</t>
+  </si>
+  <si>
+    <t>1f2t3t5t</t>
+  </si>
+  <si>
+    <t>1f2t3t5f6t</t>
+  </si>
+  <si>
+    <t>1f2t3f4t5t</t>
+  </si>
+  <si>
+    <t>1t3f4t5f6t</t>
+  </si>
+  <si>
+    <t>1f2t3f4t5f6t</t>
+  </si>
+  <si>
+    <t>1t</t>
+  </si>
+  <si>
+    <t>1f2f3t</t>
+  </si>
+  <si>
+    <t>1f2f3f4f</t>
+  </si>
+  <si>
+    <t>1t5t7t</t>
+  </si>
+  <si>
+    <t>1f2t3t4t</t>
+  </si>
+  <si>
+    <t>1f2t3t4f</t>
+  </si>
+  <si>
+    <t>1f2t3f</t>
+  </si>
+  <si>
+    <t>1t5t7f8f10t</t>
+  </si>
+  <si>
+    <t>1t5f</t>
+  </si>
+  <si>
+    <t>1t5t7f8f10f</t>
+  </si>
+  <si>
+    <t>1t5t7f8t10t</t>
+  </si>
+  <si>
+    <t>1t5t7f8t10f</t>
+  </si>
+  <si>
+    <t>1f2f3f4t</t>
   </si>
 </sst>
 </file>
@@ -1452,8 +1545,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="79">
+  <cellStyleXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1541,7 +1642,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="79">
+  <cellStyles count="87">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
@@ -1581,6 +1682,10 @@
     <cellStyle name="Followed Hyperlink" xfId="74" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="76" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="78" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="80" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="82" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="84" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="86" builtinId="9" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
@@ -1620,6 +1725,10 @@
     <cellStyle name="Hyperlink" xfId="73" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="75" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="77" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="79" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="81" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="83" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="85" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -10074,4 +10183,955 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C1" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1" t="s">
+        <v>456</v>
+      </c>
+      <c r="E1" t="s">
+        <v>275</v>
+      </c>
+      <c r="F1" t="s">
+        <v>457</v>
+      </c>
+      <c r="G1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>7586</v>
+      </c>
+      <c r="F2">
+        <v>7421</v>
+      </c>
+      <c r="G2" s="4">
+        <f>F2/E2</f>
+        <v>0.97824940680200367</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>458</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>448</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>7586</v>
+      </c>
+      <c r="F3">
+        <v>7469</v>
+      </c>
+      <c r="G3" s="4">
+        <f t="shared" ref="G3:G35" si="0">F3/E3</f>
+        <v>0.98457685209596624</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>458</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>449</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>7586</v>
+      </c>
+      <c r="F4">
+        <v>7493</v>
+      </c>
+      <c r="G4" s="4">
+        <f t="shared" si="0"/>
+        <v>0.98774057474294752</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>458</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>211</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>7586</v>
+      </c>
+      <c r="F5">
+        <v>7510</v>
+      </c>
+      <c r="G5" s="4">
+        <f t="shared" si="0"/>
+        <v>0.98998154495122592</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>458</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>449</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1188</v>
+      </c>
+      <c r="F6">
+        <v>503</v>
+      </c>
+      <c r="G6" s="4">
+        <f t="shared" si="0"/>
+        <v>0.42340067340067339</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>458</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>459</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>1188</v>
+      </c>
+      <c r="F7">
+        <v>672</v>
+      </c>
+      <c r="G7" s="4">
+        <f t="shared" si="0"/>
+        <v>0.56565656565656564</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>458</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>460</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>1188</v>
+      </c>
+      <c r="F8">
+        <v>766</v>
+      </c>
+      <c r="G8" s="4">
+        <f t="shared" si="0"/>
+        <v>0.64478114478114479</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>458</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>461</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9">
+        <v>1188</v>
+      </c>
+      <c r="F9">
+        <v>812</v>
+      </c>
+      <c r="G9" s="4">
+        <f t="shared" si="0"/>
+        <v>0.6835016835016835</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>458</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10" t="s">
+        <v>463</v>
+      </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <v>1188</v>
+      </c>
+      <c r="F10">
+        <v>901</v>
+      </c>
+      <c r="G10" s="4">
+        <f t="shared" si="0"/>
+        <v>0.75841750841750843</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>458</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11" t="s">
+        <v>462</v>
+      </c>
+      <c r="D11">
+        <v>6</v>
+      </c>
+      <c r="E11">
+        <v>1188</v>
+      </c>
+      <c r="F11">
+        <v>915</v>
+      </c>
+      <c r="G11" s="4">
+        <f t="shared" si="0"/>
+        <v>0.77020202020202022</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>458</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12" t="s">
+        <v>464</v>
+      </c>
+      <c r="D12">
+        <v>7</v>
+      </c>
+      <c r="E12">
+        <v>1188</v>
+      </c>
+      <c r="F12">
+        <v>916</v>
+      </c>
+      <c r="G12" s="4">
+        <f t="shared" si="0"/>
+        <v>0.77104377104377109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>458</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>465</v>
+      </c>
+      <c r="D13">
+        <v>8</v>
+      </c>
+      <c r="E13">
+        <v>1188</v>
+      </c>
+      <c r="F13">
+        <v>990</v>
+      </c>
+      <c r="G13" s="4">
+        <f t="shared" si="0"/>
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>458</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14" t="s">
+        <v>466</v>
+      </c>
+      <c r="D14">
+        <v>9</v>
+      </c>
+      <c r="E14">
+        <v>1188</v>
+      </c>
+      <c r="F14">
+        <v>997</v>
+      </c>
+      <c r="G14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.83922558922558921</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>458</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" t="s">
+        <v>468</v>
+      </c>
+      <c r="D15">
+        <v>10</v>
+      </c>
+      <c r="E15">
+        <v>1188</v>
+      </c>
+      <c r="F15">
+        <v>1013</v>
+      </c>
+      <c r="G15" s="4">
+        <f t="shared" si="0"/>
+        <v>0.85269360269360273</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>458</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16" t="s">
+        <v>467</v>
+      </c>
+      <c r="D16">
+        <v>11</v>
+      </c>
+      <c r="E16">
+        <v>1188</v>
+      </c>
+      <c r="F16">
+        <v>1014</v>
+      </c>
+      <c r="G16" s="4">
+        <f t="shared" si="0"/>
+        <v>0.85353535353535348</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>458</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17" t="s">
+        <v>469</v>
+      </c>
+      <c r="D17">
+        <v>12</v>
+      </c>
+      <c r="E17">
+        <v>1188</v>
+      </c>
+      <c r="F17">
+        <v>1084</v>
+      </c>
+      <c r="G17" s="4">
+        <f t="shared" si="0"/>
+        <v>0.91245791245791241</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>458</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18" t="s">
+        <v>470</v>
+      </c>
+      <c r="D18">
+        <v>13</v>
+      </c>
+      <c r="E18">
+        <v>1188</v>
+      </c>
+      <c r="F18">
+        <v>1086</v>
+      </c>
+      <c r="G18" s="4">
+        <f t="shared" si="0"/>
+        <v>0.91414141414141414</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>458</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19" t="s">
+        <v>471</v>
+      </c>
+      <c r="D19">
+        <v>14</v>
+      </c>
+      <c r="E19">
+        <v>1188</v>
+      </c>
+      <c r="F19">
+        <v>1094</v>
+      </c>
+      <c r="G19" s="4">
+        <f t="shared" si="0"/>
+        <v>0.92087542087542085</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>458</v>
+      </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
+      <c r="C20" t="s">
+        <v>472</v>
+      </c>
+      <c r="D20">
+        <v>15</v>
+      </c>
+      <c r="E20">
+        <v>1188</v>
+      </c>
+      <c r="F20">
+        <v>1171</v>
+      </c>
+      <c r="G20" s="4">
+        <f t="shared" si="0"/>
+        <v>0.98569023569023573</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>458</v>
+      </c>
+      <c r="B21">
+        <v>6</v>
+      </c>
+      <c r="C21" t="s">
+        <v>473</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>666</v>
+      </c>
+      <c r="F21">
+        <v>104</v>
+      </c>
+      <c r="G21" s="4">
+        <f t="shared" si="0"/>
+        <v>0.15615615615615616</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>458</v>
+      </c>
+      <c r="B22">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>448</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22">
+        <v>666</v>
+      </c>
+      <c r="F22">
+        <v>198</v>
+      </c>
+      <c r="G22" s="4">
+        <f t="shared" si="0"/>
+        <v>0.29729729729729731</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>458</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23" t="s">
+        <v>474</v>
+      </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+      <c r="E23">
+        <v>666</v>
+      </c>
+      <c r="F23">
+        <v>468</v>
+      </c>
+      <c r="G23" s="4">
+        <f t="shared" si="0"/>
+        <v>0.70270270270270274</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>458</v>
+      </c>
+      <c r="B24">
+        <v>6</v>
+      </c>
+      <c r="C24" t="s">
+        <v>485</v>
+      </c>
+      <c r="D24">
+        <v>4</v>
+      </c>
+      <c r="E24">
+        <v>666</v>
+      </c>
+      <c r="F24">
+        <v>1990</v>
+      </c>
+      <c r="G24" s="4">
+        <f t="shared" si="0"/>
+        <v>2.9879879879879878</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>458</v>
+      </c>
+      <c r="B25">
+        <v>6</v>
+      </c>
+      <c r="C25" t="s">
+        <v>475</v>
+      </c>
+      <c r="D25">
+        <v>5</v>
+      </c>
+      <c r="E25">
+        <v>666</v>
+      </c>
+      <c r="F25">
+        <v>2637</v>
+      </c>
+      <c r="G25" s="4">
+        <f t="shared" si="0"/>
+        <v>3.9594594594594597</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>458</v>
+      </c>
+      <c r="B26">
+        <v>9</v>
+      </c>
+      <c r="C26" t="s">
+        <v>477</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>2157</v>
+      </c>
+      <c r="F26">
+        <v>163</v>
+      </c>
+      <c r="G26" s="4">
+        <f t="shared" si="0"/>
+        <v>7.5567918405192391E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>458</v>
+      </c>
+      <c r="B27">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s">
+        <v>478</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27">
+        <v>2157</v>
+      </c>
+      <c r="F27">
+        <v>164</v>
+      </c>
+      <c r="G27" s="4">
+        <f t="shared" si="0"/>
+        <v>7.6031525266573946E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>458</v>
+      </c>
+      <c r="B28">
+        <v>9</v>
+      </c>
+      <c r="C28" t="s">
+        <v>476</v>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28">
+        <v>2157</v>
+      </c>
+      <c r="F28">
+        <v>168</v>
+      </c>
+      <c r="G28" s="4">
+        <f t="shared" si="0"/>
+        <v>7.7885952712100137E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>458</v>
+      </c>
+      <c r="B29">
+        <v>9</v>
+      </c>
+      <c r="C29" t="s">
+        <v>479</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29">
+        <v>2157</v>
+      </c>
+      <c r="F29">
+        <v>351</v>
+      </c>
+      <c r="G29" s="4">
+        <f t="shared" si="0"/>
+        <v>0.16272600834492351</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>458</v>
+      </c>
+      <c r="B30">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s">
+        <v>449</v>
+      </c>
+      <c r="D30">
+        <v>5</v>
+      </c>
+      <c r="E30">
+        <v>2157</v>
+      </c>
+      <c r="F30">
+        <v>354</v>
+      </c>
+      <c r="G30" s="4">
+        <f t="shared" si="0"/>
+        <v>0.16411682892906815</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>458</v>
+      </c>
+      <c r="B31">
+        <v>9</v>
+      </c>
+      <c r="C31" t="s">
+        <v>480</v>
+      </c>
+      <c r="D31">
+        <v>6</v>
+      </c>
+      <c r="E31">
+        <v>2157</v>
+      </c>
+      <c r="F31">
+        <v>731</v>
+      </c>
+      <c r="G31" s="4">
+        <f t="shared" si="0"/>
+        <v>0.33889661566991192</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>458</v>
+      </c>
+      <c r="B32">
+        <v>9</v>
+      </c>
+      <c r="C32" t="s">
+        <v>481</v>
+      </c>
+      <c r="D32">
+        <v>7</v>
+      </c>
+      <c r="E32">
+        <v>2157</v>
+      </c>
+      <c r="F32">
+        <v>736</v>
+      </c>
+      <c r="G32" s="4">
+        <f t="shared" si="0"/>
+        <v>0.34121464997681966</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>458</v>
+      </c>
+      <c r="B33">
+        <v>9</v>
+      </c>
+      <c r="C33" t="s">
+        <v>482</v>
+      </c>
+      <c r="D33">
+        <v>8</v>
+      </c>
+      <c r="E33">
+        <v>2157</v>
+      </c>
+      <c r="F33">
+        <v>752</v>
+      </c>
+      <c r="G33" s="4">
+        <f t="shared" si="0"/>
+        <v>0.34863235975892443</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>458</v>
+      </c>
+      <c r="B34">
+        <v>9</v>
+      </c>
+      <c r="C34" t="s">
+        <v>483</v>
+      </c>
+      <c r="D34">
+        <v>9</v>
+      </c>
+      <c r="E34">
+        <v>2157</v>
+      </c>
+      <c r="F34">
+        <v>883</v>
+      </c>
+      <c r="G34" s="4">
+        <f t="shared" si="0"/>
+        <v>0.40936485859990729</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>458</v>
+      </c>
+      <c r="B35">
+        <v>9</v>
+      </c>
+      <c r="C35" t="s">
+        <v>484</v>
+      </c>
+      <c r="D35">
+        <v>10</v>
+      </c>
+      <c r="E35">
+        <v>2157</v>
+      </c>
+      <c r="F35">
+        <v>886</v>
+      </c>
+      <c r="G35" s="4">
+        <f t="shared" si="0"/>
+        <v>0.41075567918405193</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C1" t="s">
+        <v>446</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <cols>
+    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B1" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B2" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B3" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B4" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B5" s="2">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
+</worksheet>
 </file>
--- a/ScratchData/data.xlsx
+++ b/ScratchData/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="28125"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="5260" yWindow="0" windowWidth="25440" windowHeight="14740" tabRatio="500" firstSheet="1" activeTab="5"/>
+    <workbookView xWindow="5220" yWindow="0" windowWidth="25440" windowHeight="14740" tabRatio="500" firstSheet="1" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="503">
   <si>
     <t>Done in 748</t>
   </si>
@@ -1484,6 +1484,57 @@
   </si>
   <si>
     <t>1f2f3f4t</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>method</t>
+  </si>
+  <si>
+    <t>paths</t>
+  </si>
+  <si>
+    <t>test.Base64</t>
+  </si>
+  <si>
+    <t>test.Class11</t>
+  </si>
+  <si>
+    <t>test.Class13</t>
+  </si>
+  <si>
+    <t>test.client</t>
+  </si>
+  <si>
+    <t>test.GeoEngine</t>
+  </si>
+  <si>
+    <t>test.FastBlurFilter</t>
+  </si>
+  <si>
+    <t>test.ImageData</t>
+  </si>
+  <si>
+    <t>test.MapViewer</t>
+  </si>
+  <si>
+    <t>test.QRCodeDataBlockReader</t>
+  </si>
+  <si>
+    <t>test.StructurePanel</t>
+  </si>
+  <si>
+    <t>test.TileRenderor</t>
+  </si>
+  <si>
+    <t>test.WorldController</t>
+  </si>
+  <si>
+    <t>test.TIFFFaxDecoder</t>
+  </si>
+  <si>
+    <t>test.TIFFaxEncoder</t>
   </si>
 </sst>
 </file>
@@ -1545,8 +1596,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="87">
+  <cellStyleXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1642,7 +1697,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="87">
+  <cellStyles count="91">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
@@ -1686,6 +1741,8 @@
     <cellStyle name="Followed Hyperlink" xfId="82" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="84" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="86" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="88" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="90" builtinId="9" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
@@ -1729,6 +1786,8 @@
     <cellStyle name="Hyperlink" xfId="81" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="83" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="85" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="87" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="89" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -11041,10 +11100,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:AK35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <cols>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:37">
       <c r="A1" t="s">
         <v>270</v>
       </c>
@@ -11065,6 +11127,1523 @@
       </c>
       <c r="G1" s="2" t="s">
         <v>453</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>486</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>487</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>488</v>
+      </c>
+      <c r="AH1" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37">
+      <c r="A2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>47</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>4</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>1</v>
+      </c>
+      <c r="AH2">
+        <v>47</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>4</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37">
+      <c r="A3" t="s">
+        <v>458</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>49</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF3">
+        <v>1</v>
+      </c>
+      <c r="AG3">
+        <v>2</v>
+      </c>
+      <c r="AH3">
+        <v>49</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>2</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37">
+      <c r="A4" t="s">
+        <v>458</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>51</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF4">
+        <v>1</v>
+      </c>
+      <c r="AG4">
+        <v>3</v>
+      </c>
+      <c r="AH4">
+        <v>51</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37">
+      <c r="A5" t="s">
+        <v>458</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>51</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF5">
+        <v>1</v>
+      </c>
+      <c r="AG5">
+        <v>4</v>
+      </c>
+      <c r="AH5">
+        <v>51</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37">
+      <c r="A6" t="s">
+        <v>458</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>11</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF6">
+        <v>2</v>
+      </c>
+      <c r="AG6">
+        <v>1</v>
+      </c>
+      <c r="AH6">
+        <v>11</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>2</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37">
+      <c r="A7" t="s">
+        <v>458</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>19</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF7">
+        <v>2</v>
+      </c>
+      <c r="AG7">
+        <v>2</v>
+      </c>
+      <c r="AH7">
+        <v>19</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>3</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37">
+      <c r="A8" t="s">
+        <v>458</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <v>20</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF8">
+        <v>2</v>
+      </c>
+      <c r="AG8">
+        <v>3</v>
+      </c>
+      <c r="AH8">
+        <v>20</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>2</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37">
+      <c r="A9" t="s">
+        <v>458</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9">
+        <v>26</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF9">
+        <v>2</v>
+      </c>
+      <c r="AG9">
+        <v>4</v>
+      </c>
+      <c r="AH9">
+        <v>26</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>3</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37">
+      <c r="A10" t="s">
+        <v>458</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>5</v>
+      </c>
+      <c r="D10">
+        <v>26</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF10">
+        <v>2</v>
+      </c>
+      <c r="AG10">
+        <v>5</v>
+      </c>
+      <c r="AH10">
+        <v>26</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>3</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37">
+      <c r="A11" t="s">
+        <v>458</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>6</v>
+      </c>
+      <c r="D11">
+        <v>27</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF11">
+        <v>2</v>
+      </c>
+      <c r="AG11">
+        <v>6</v>
+      </c>
+      <c r="AH11">
+        <v>27</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>2</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37">
+      <c r="A12" t="s">
+        <v>458</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>7</v>
+      </c>
+      <c r="D12">
+        <v>32</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF12">
+        <v>2</v>
+      </c>
+      <c r="AG12">
+        <v>7</v>
+      </c>
+      <c r="AH12">
+        <v>32</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>1</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37">
+      <c r="A13" t="s">
+        <v>458</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>8</v>
+      </c>
+      <c r="D13">
+        <v>32</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF13">
+        <v>2</v>
+      </c>
+      <c r="AG13">
+        <v>8</v>
+      </c>
+      <c r="AH13">
+        <v>32</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>1</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37">
+      <c r="A14" t="s">
+        <v>458</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>9</v>
+      </c>
+      <c r="D14">
+        <v>33</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF14">
+        <v>2</v>
+      </c>
+      <c r="AG14">
+        <v>9</v>
+      </c>
+      <c r="AH14">
+        <v>33</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37">
+      <c r="A15" t="s">
+        <v>458</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>10</v>
+      </c>
+      <c r="D15">
+        <v>33</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF15">
+        <v>2</v>
+      </c>
+      <c r="AG15">
+        <v>10</v>
+      </c>
+      <c r="AH15">
+        <v>33</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37">
+      <c r="A16" t="s">
+        <v>458</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16">
+        <v>11</v>
+      </c>
+      <c r="D16">
+        <v>33</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF16">
+        <v>2</v>
+      </c>
+      <c r="AG16">
+        <v>11</v>
+      </c>
+      <c r="AH16">
+        <v>33</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:37">
+      <c r="A17" t="s">
+        <v>458</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <v>12</v>
+      </c>
+      <c r="D17">
+        <v>33</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF17">
+        <v>2</v>
+      </c>
+      <c r="AG17">
+        <v>12</v>
+      </c>
+      <c r="AH17">
+        <v>33</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:37">
+      <c r="A18" t="s">
+        <v>458</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18">
+        <v>13</v>
+      </c>
+      <c r="D18">
+        <v>33</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF18">
+        <v>2</v>
+      </c>
+      <c r="AG18">
+        <v>13</v>
+      </c>
+      <c r="AH18">
+        <v>33</v>
+      </c>
+      <c r="AI18">
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37">
+      <c r="A19" t="s">
+        <v>458</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>14</v>
+      </c>
+      <c r="D19">
+        <v>33</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF19">
+        <v>2</v>
+      </c>
+      <c r="AG19">
+        <v>14</v>
+      </c>
+      <c r="AH19">
+        <v>33</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:37">
+      <c r="A20" t="s">
+        <v>458</v>
+      </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
+      <c r="C20">
+        <v>15</v>
+      </c>
+      <c r="D20">
+        <v>33</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF20">
+        <v>2</v>
+      </c>
+      <c r="AG20">
+        <v>15</v>
+      </c>
+      <c r="AH20">
+        <v>33</v>
+      </c>
+      <c r="AI20">
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:37">
+      <c r="A21" t="s">
+        <v>458</v>
+      </c>
+      <c r="B21">
+        <v>6</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF21">
+        <v>6</v>
+      </c>
+      <c r="AG21">
+        <v>1</v>
+      </c>
+      <c r="AH21">
+        <v>2</v>
+      </c>
+      <c r="AI21">
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <v>1</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:37">
+      <c r="A22" t="s">
+        <v>458</v>
+      </c>
+      <c r="B22">
+        <v>6</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22">
+        <v>5</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF22">
+        <v>6</v>
+      </c>
+      <c r="AG22">
+        <v>2</v>
+      </c>
+      <c r="AH22">
+        <v>5</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>1</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:37">
+      <c r="A23" t="s">
+        <v>458</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>3</v>
+      </c>
+      <c r="D23">
+        <v>11</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF23">
+        <v>6</v>
+      </c>
+      <c r="AG23">
+        <v>3</v>
+      </c>
+      <c r="AH23">
+        <v>11</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <v>2</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:37">
+      <c r="A24" t="s">
+        <v>458</v>
+      </c>
+      <c r="B24">
+        <v>6</v>
+      </c>
+      <c r="C24">
+        <v>4</v>
+      </c>
+      <c r="D24">
+        <v>16</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>2</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF24">
+        <v>6</v>
+      </c>
+      <c r="AG24">
+        <v>4</v>
+      </c>
+      <c r="AH24">
+        <v>16</v>
+      </c>
+      <c r="AI24">
+        <v>0</v>
+      </c>
+      <c r="AJ24">
+        <v>2</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:37">
+      <c r="A25" t="s">
+        <v>458</v>
+      </c>
+      <c r="B25">
+        <v>6</v>
+      </c>
+      <c r="C25">
+        <v>5</v>
+      </c>
+      <c r="D25">
+        <v>18</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF25">
+        <v>6</v>
+      </c>
+      <c r="AG25">
+        <v>5</v>
+      </c>
+      <c r="AH25">
+        <v>18</v>
+      </c>
+      <c r="AI25">
+        <v>0</v>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:37">
+      <c r="A26" t="s">
+        <v>458</v>
+      </c>
+      <c r="B26">
+        <v>9</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF26">
+        <v>9</v>
+      </c>
+      <c r="AG26">
+        <v>1</v>
+      </c>
+      <c r="AH26">
+        <v>3</v>
+      </c>
+      <c r="AI26">
+        <v>0</v>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:37">
+      <c r="A27" t="s">
+        <v>458</v>
+      </c>
+      <c r="B27">
+        <v>9</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27">
+        <v>3</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF27">
+        <v>9</v>
+      </c>
+      <c r="AG27">
+        <v>2</v>
+      </c>
+      <c r="AH27">
+        <v>3</v>
+      </c>
+      <c r="AI27">
+        <v>0</v>
+      </c>
+      <c r="AJ27">
+        <v>0</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:37">
+      <c r="A28" t="s">
+        <v>458</v>
+      </c>
+      <c r="B28">
+        <v>9</v>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF28">
+        <v>9</v>
+      </c>
+      <c r="AG28">
+        <v>3</v>
+      </c>
+      <c r="AH28">
+        <v>3</v>
+      </c>
+      <c r="AI28">
+        <v>0</v>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:37">
+      <c r="A29" t="s">
+        <v>458</v>
+      </c>
+      <c r="B29">
+        <v>9</v>
+      </c>
+      <c r="C29">
+        <v>4</v>
+      </c>
+      <c r="D29">
+        <v>7</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF29">
+        <v>9</v>
+      </c>
+      <c r="AG29">
+        <v>4</v>
+      </c>
+      <c r="AH29">
+        <v>7</v>
+      </c>
+      <c r="AI29">
+        <v>0</v>
+      </c>
+      <c r="AJ29">
+        <v>1</v>
+      </c>
+      <c r="AK29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:37">
+      <c r="A30" t="s">
+        <v>458</v>
+      </c>
+      <c r="B30">
+        <v>9</v>
+      </c>
+      <c r="C30">
+        <v>5</v>
+      </c>
+      <c r="D30">
+        <v>11</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF30">
+        <v>9</v>
+      </c>
+      <c r="AG30">
+        <v>5</v>
+      </c>
+      <c r="AH30">
+        <v>11</v>
+      </c>
+      <c r="AI30">
+        <v>0</v>
+      </c>
+      <c r="AJ30">
+        <v>0</v>
+      </c>
+      <c r="AK30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:37">
+      <c r="A31" t="s">
+        <v>458</v>
+      </c>
+      <c r="B31">
+        <v>9</v>
+      </c>
+      <c r="C31">
+        <v>6</v>
+      </c>
+      <c r="D31">
+        <v>23</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF31">
+        <v>9</v>
+      </c>
+      <c r="AG31">
+        <v>6</v>
+      </c>
+      <c r="AH31">
+        <v>23</v>
+      </c>
+      <c r="AI31">
+        <v>0</v>
+      </c>
+      <c r="AJ31">
+        <v>2</v>
+      </c>
+      <c r="AK31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:37">
+      <c r="A32" t="s">
+        <v>458</v>
+      </c>
+      <c r="B32">
+        <v>9</v>
+      </c>
+      <c r="C32">
+        <v>7</v>
+      </c>
+      <c r="D32">
+        <v>35</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF32">
+        <v>9</v>
+      </c>
+      <c r="AG32">
+        <v>7</v>
+      </c>
+      <c r="AH32">
+        <v>35</v>
+      </c>
+      <c r="AI32">
+        <v>0</v>
+      </c>
+      <c r="AJ32">
+        <v>1</v>
+      </c>
+      <c r="AK32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:37">
+      <c r="A33" t="s">
+        <v>458</v>
+      </c>
+      <c r="B33">
+        <v>9</v>
+      </c>
+      <c r="C33">
+        <v>8</v>
+      </c>
+      <c r="D33">
+        <v>42</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF33">
+        <v>9</v>
+      </c>
+      <c r="AG33">
+        <v>8</v>
+      </c>
+      <c r="AH33">
+        <v>42</v>
+      </c>
+      <c r="AI33">
+        <v>0</v>
+      </c>
+      <c r="AJ33">
+        <v>1</v>
+      </c>
+      <c r="AK33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:37">
+      <c r="A34" t="s">
+        <v>458</v>
+      </c>
+      <c r="B34">
+        <v>9</v>
+      </c>
+      <c r="C34">
+        <v>9</v>
+      </c>
+      <c r="D34">
+        <v>46</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF34">
+        <v>9</v>
+      </c>
+      <c r="AG34">
+        <v>9</v>
+      </c>
+      <c r="AH34">
+        <v>46</v>
+      </c>
+      <c r="AI34">
+        <v>0</v>
+      </c>
+      <c r="AJ34">
+        <v>0</v>
+      </c>
+      <c r="AK34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:37">
+      <c r="A35" t="s">
+        <v>458</v>
+      </c>
+      <c r="B35">
+        <v>9</v>
+      </c>
+      <c r="C35">
+        <v>10</v>
+      </c>
+      <c r="D35">
+        <v>46</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="s">
+        <v>458</v>
+      </c>
+      <c r="AF35">
+        <v>9</v>
+      </c>
+      <c r="AG35">
+        <v>10</v>
+      </c>
+      <c r="AH35">
+        <v>46</v>
+      </c>
+      <c r="AI35">
+        <v>0</v>
+      </c>
+      <c r="AJ35">
+        <v>0</v>
+      </c>
+      <c r="AK35">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -11079,7 +12658,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
@@ -11087,7 +12666,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="B1" s="2">
         <v>1</v>
@@ -11095,7 +12674,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="B2" s="2">
         <v>2</v>
@@ -11103,7 +12682,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="B3" s="2">
         <v>6</v>
@@ -11111,7 +12690,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="B4" s="2">
         <v>7</v>
@@ -11119,10 +12698,514 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="B5" s="2">
         <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B6" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B7" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B8" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B9" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B10" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B11" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B12" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B13" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B14" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B15" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B16" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B17" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B18" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B19" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B20" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="B21" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B22" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B23" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B24" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B25" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B26" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B27" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B28" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B29" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B30" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B31" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B32" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B33" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B34" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B35" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B36" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B37" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B38" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B39" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B40" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B41" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B42" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B43" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B44" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B45" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B46" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B47" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B48" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B49" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B50" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="B51" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="B52" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B53" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B54" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B55" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B56" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B57" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B58" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B59" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B60" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B61" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B62" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B63" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B64" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B65" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B66" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B67" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B68" s="2">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/ScratchData/data.xlsx
+++ b/ScratchData/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="28125"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="2800" yWindow="0" windowWidth="28420" windowHeight="17740" tabRatio="680" firstSheet="2" activeTab="3"/>
+    <workbookView xWindow="9580" yWindow="100" windowWidth="28420" windowHeight="17740" tabRatio="680" firstSheet="2" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3820" uniqueCount="970">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3816" uniqueCount="972">
   <si>
     <t>Done in 748</t>
   </si>
@@ -2940,6 +2940,12 @@
   </si>
   <si>
     <t>over 50% info</t>
+  </si>
+  <si>
+    <t>test.Class11_7_</t>
+  </si>
+  <si>
+    <t>there need to collect it</t>
   </si>
 </sst>
 </file>
@@ -3007,8 +3013,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="173">
+  <cellStyleXfs count="177">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3195,7 +3205,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="173">
+  <cellStyles count="177">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
@@ -3282,6 +3292,8 @@
     <cellStyle name="Followed Hyperlink" xfId="168" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="170" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="172" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="174" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="176" builtinId="9" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
@@ -3368,6 +3380,8 @@
     <cellStyle name="Hyperlink" xfId="167" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="169" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="171" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="173" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="175" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3860,16 +3874,16 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>30.0</c:v>
+                  <c:v>31.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>19.0</c:v>
+                  <c:v>20.0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>13.0</c:v>
+                  <c:v>14.0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.0</c:v>
+                  <c:v>10.0</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>1.0</c:v>
@@ -4217,10 +4231,10 @@
                   <c:v>25.0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>60.0</c:v>
+                  <c:v>61.0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>62.0</c:v>
+                  <c:v>63.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11966,28 +11980,28 @@
       </c>
     </row>
     <row r="159" spans="1:9">
-      <c r="A159" t="s">
+      <c r="A159" s="6" t="s">
         <v>489</v>
       </c>
-      <c r="B159">
+      <c r="B159" s="6">
         <v>20</v>
       </c>
-      <c r="C159">
+      <c r="C159" s="6">
         <v>33</v>
       </c>
-      <c r="D159">
+      <c r="D159" s="6">
         <v>101</v>
       </c>
-      <c r="E159">
-        <v>0</v>
-      </c>
-      <c r="F159">
+      <c r="E159" s="6">
+        <v>0</v>
+      </c>
+      <c r="F159" s="6">
         <v>4</v>
       </c>
-      <c r="G159">
-        <v>0</v>
-      </c>
-      <c r="H159">
+      <c r="G159" s="6">
+        <v>0</v>
+      </c>
+      <c r="H159" s="6">
         <v>101</v>
       </c>
       <c r="I159" s="4">
@@ -23897,7 +23911,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CI540"/>
+  <dimension ref="A1:CJ540"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
     <col min="3" max="3" width="28.5" bestFit="1" customWidth="1"/>
@@ -23906,7 +23920,7 @@
     <col min="35" max="35" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:87">
+    <row r="1" spans="1:88">
       <c r="A1" t="s">
         <v>486</v>
       </c>
@@ -24149,8 +24163,11 @@
       <c r="CI1" t="s">
         <v>894</v>
       </c>
-    </row>
-    <row r="2" spans="1:87">
+      <c r="CJ1" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="2" spans="1:88">
       <c r="A2" t="s">
         <v>458</v>
       </c>
@@ -24223,8 +24240,8 @@
         <v>895</v>
       </c>
       <c r="W2">
-        <f>COUNTA(X2:CI2)</f>
-        <v>64</v>
+        <f>COUNTA(X2:CJ2)</f>
+        <v>65</v>
       </c>
       <c r="X2" t="s">
         <v>905</v>
@@ -24269,157 +24286,160 @@
         <v>902</v>
       </c>
       <c r="AL2" t="s">
+        <v>970</v>
+      </c>
+      <c r="AM2" t="s">
         <v>904</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AN2" t="s">
         <v>916</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AO2" t="s">
         <v>917</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AP2" t="s">
         <v>918</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AQ2" t="s">
         <v>919</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AR2" t="s">
         <v>920</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AS2" t="s">
         <v>921</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AT2" t="s">
         <v>922</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AU2" t="s">
         <v>923</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AV2" t="s">
         <v>924</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AW2" t="s">
         <v>925</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AX2" t="s">
         <v>926</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AY2" t="s">
         <v>927</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AZ2" t="s">
         <v>928</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BA2" t="s">
         <v>929</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BB2" t="s">
         <v>930</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BC2" t="s">
         <v>931</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BD2" t="s">
         <v>932</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BE2" t="s">
         <v>933</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BF2" t="s">
         <v>934</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BG2" t="s">
         <v>935</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BH2" t="s">
         <v>936</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BI2" t="s">
         <v>937</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BJ2" t="s">
         <v>938</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BK2" t="s">
         <v>939</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BL2" t="s">
         <v>940</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BM2" t="s">
         <v>941</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BN2" t="s">
         <v>942</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BO2" t="s">
         <v>943</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BP2" t="s">
         <v>944</v>
       </c>
-      <c r="BP2" t="s">
+      <c r="BQ2" t="s">
         <v>945</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BR2" t="s">
         <v>946</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BS2" t="s">
         <v>947</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BT2" t="s">
         <v>948</v>
       </c>
-      <c r="BT2" t="s">
+      <c r="BU2" t="s">
         <v>949</v>
       </c>
-      <c r="BU2" t="s">
+      <c r="BV2" t="s">
         <v>950</v>
       </c>
-      <c r="BV2" t="s">
+      <c r="BW2" t="s">
         <v>951</v>
       </c>
-      <c r="BW2" t="s">
+      <c r="BX2" t="s">
         <v>952</v>
       </c>
-      <c r="BX2" t="s">
+      <c r="BY2" t="s">
         <v>953</v>
       </c>
-      <c r="BY2" t="s">
+      <c r="BZ2" t="s">
         <v>954</v>
       </c>
-      <c r="BZ2" t="s">
+      <c r="CA2" t="s">
         <v>955</v>
       </c>
-      <c r="CA2" t="s">
+      <c r="CB2" t="s">
         <v>956</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CC2" t="s">
         <v>957</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CD2" t="s">
         <v>958</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CE2" t="s">
         <v>959</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CF2" t="s">
         <v>960</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CG2" t="s">
         <v>961</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CH2" t="s">
         <v>962</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CI2" t="s">
         <v>963</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CJ2" t="s">
         <v>964</v>
       </c>
     </row>
-    <row r="3" spans="1:87">
+    <row r="3" spans="1:88">
       <c r="A3" t="s">
         <v>458</v>
       </c>
@@ -24470,33 +24490,33 @@
       </c>
       <c r="O3" s="4">
         <f>SUM(Q3:V3)</f>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P3" t="s">
         <v>890</v>
       </c>
       <c r="Q3" s="8">
-        <f>COUNTIF($X3:$CI3,"=0")</f>
-        <v>30</v>
+        <f>COUNTIF($X3:$CJ3,"=0")</f>
+        <v>31</v>
       </c>
       <c r="R3" s="8">
-        <f>COUNTIFS($X3:$CI3,"&gt;0",$X3:$CI3,"&lt;0.25")</f>
+        <f>COUNTIFS($X3:$CJ3,"&gt;0",$X3:$CJ3,"&lt;0.25")</f>
         <v>21</v>
       </c>
       <c r="S3" s="8">
-        <f>COUNTIFS($X3:$CI3,"&gt;=0.25",$X3:$CI3,"&lt;0.5")</f>
+        <f>COUNTIFS($X3:$CJ3,"&gt;=0.25",$X3:$CJ3,"&lt;0.5")</f>
         <v>7</v>
       </c>
       <c r="T3" s="8">
-        <f>COUNTIFS($X3:$CI3,"&gt;=0.5",$X3:$CI3,"&lt;0.75")</f>
+        <f>COUNTIFS($X3:$CJ3,"&gt;=0.5",$X3:$CJ3,"&lt;0.75")</f>
         <v>5</v>
       </c>
       <c r="U3" s="8">
-        <f>COUNTIFS($X3:$CI3,"&gt;=0.75",$X3:$CI3,"&lt;1")</f>
+        <f>COUNTIFS($X3:$CJ3,"&gt;=0.75",$X3:$CJ3,"&lt;1")</f>
         <v>1</v>
       </c>
       <c r="V3" s="8">
-        <f>COUNTIF($X3:$CI3,"=1")</f>
+        <f>COUNTIF($X3:$CJ3,"=1")</f>
         <v>0</v>
       </c>
       <c r="W3" t="s">
@@ -24560,27 +24580,27 @@
       </c>
       <c r="AL3">
         <f>DMAX($A$1:$L$540,$W3,AL$1:AL$2)</f>
-        <v>0.58620689655172409</v>
+        <v>0</v>
       </c>
       <c r="AM3">
         <f>DMAX($A$1:$L$540,$W3,AM$1:AM$2)</f>
-        <v>0.11979166666666667</v>
+        <v>0.58620689655172409</v>
       </c>
       <c r="AN3">
         <f>DMAX($A$1:$L$540,$W3,AN$1:AN$2)</f>
-        <v>8.4745762711864406E-3</v>
+        <v>0.11979166666666667</v>
       </c>
       <c r="AO3">
         <f>DMAX($A$1:$L$540,$W3,AO$1:AO$2)</f>
-        <v>0</v>
+        <v>8.4745762711864406E-3</v>
       </c>
       <c r="AP3">
         <f>DMAX($A$1:$L$540,$W3,AP$1:AP$2)</f>
-        <v>0.24848484848484848</v>
+        <v>0</v>
       </c>
       <c r="AQ3">
         <f>DMAX($A$1:$L$540,$W3,AQ$1:AQ$2)</f>
-        <v>0</v>
+        <v>0.24848484848484848</v>
       </c>
       <c r="AR3">
         <f>DMAX($A$1:$L$540,$W3,AR$1:AR$2)</f>
@@ -24592,87 +24612,87 @@
       </c>
       <c r="AT3">
         <f>DMAX($A$1:$L$540,$W3,AT$1:AT$2)</f>
-        <v>7.3170731707317069E-2</v>
+        <v>0</v>
       </c>
       <c r="AU3">
         <f>DMAX($A$1:$L$540,$W3,AU$1:AU$2)</f>
-        <v>9.6774193548387094E-2</v>
+        <v>7.3170731707317069E-2</v>
       </c>
       <c r="AV3">
         <f>DMAX($A$1:$L$540,$W3,AV$1:AV$2)</f>
-        <v>0.5178571428571429</v>
+        <v>9.6774193548387094E-2</v>
       </c>
       <c r="AW3">
         <f>DMAX($A$1:$L$540,$W3,AW$1:AW$2)</f>
-        <v>0.36046511627906974</v>
+        <v>0.5178571428571429</v>
       </c>
       <c r="AX3">
         <f>DMAX($A$1:$L$540,$W3,AX$1:AX$2)</f>
-        <v>0.19565217391304349</v>
+        <v>0.36046511627906974</v>
       </c>
       <c r="AY3">
         <f>DMAX($A$1:$L$540,$W3,AY$1:AY$2)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>0.19565217391304349</v>
       </c>
       <c r="AZ3">
         <f>DMAX($A$1:$L$540,$W3,AZ$1:AZ$2)</f>
-        <v>0</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="BA3">
         <f>DMAX($A$1:$L$540,$W3,BA$1:BA$2)</f>
-        <v>0.23214285714285715</v>
+        <v>0</v>
       </c>
       <c r="BB3">
         <f>DMAX($A$1:$L$540,$W3,BB$1:BB$2)</f>
-        <v>0.2</v>
+        <v>0.23214285714285715</v>
       </c>
       <c r="BC3">
         <f>DMAX($A$1:$L$540,$W3,BC$1:BC$2)</f>
-        <v>0.56617647058823528</v>
+        <v>0.2</v>
       </c>
       <c r="BD3">
         <f>DMAX($A$1:$L$540,$W3,BD$1:BD$2)</f>
-        <v>0</v>
+        <v>0.56617647058823528</v>
       </c>
       <c r="BE3">
         <f>DMAX($A$1:$L$540,$W3,BE$1:BE$2)</f>
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="BF3">
         <f>DMAX($A$1:$L$540,$W3,BF$1:BF$2)</f>
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="BG3">
         <f>DMAX($A$1:$L$540,$W3,BG$1:BG$2)</f>
-        <v>0.3888888888888889</v>
+        <v>0</v>
       </c>
       <c r="BH3">
         <f>DMAX($A$1:$L$540,$W3,BH$1:BH$2)</f>
-        <v>0.63953488372093026</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="BI3">
         <f>DMAX($A$1:$L$540,$W3,BI$1:BI$2)</f>
-        <v>0</v>
+        <v>0.63953488372093026</v>
       </c>
       <c r="BJ3">
         <f>DMAX($A$1:$L$540,$W3,BJ$1:BJ$2)</f>
-        <v>0.33962264150943394</v>
+        <v>0</v>
       </c>
       <c r="BK3">
         <f>DMAX($A$1:$L$540,$W3,BK$1:BK$2)</f>
-        <v>6.7842605156037995E-3</v>
+        <v>0.33962264150943394</v>
       </c>
       <c r="BL3">
         <f>DMAX($A$1:$L$540,$W3,BL$1:BL$2)</f>
-        <v>8.4210526315789472E-3</v>
+        <v>6.7842605156037995E-3</v>
       </c>
       <c r="BM3">
         <f>DMAX($A$1:$L$540,$W3,BM$1:BM$2)</f>
-        <v>8.2372322899505763E-3</v>
+        <v>8.4210526315789472E-3</v>
       </c>
       <c r="BN3">
         <f>DMAX($A$1:$L$540,$W3,BN$1:BN$2)</f>
-        <v>0</v>
+        <v>8.2372322899505763E-3</v>
       </c>
       <c r="BO3">
         <f>DMAX($A$1:$L$540,$W3,BO$1:BO$2)</f>
@@ -24684,23 +24704,23 @@
       </c>
       <c r="BQ3">
         <f>DMAX($A$1:$L$540,$W3,BQ$1:BQ$2)</f>
-        <v>0.20408163265306123</v>
+        <v>0</v>
       </c>
       <c r="BR3">
         <f>DMAX($A$1:$L$540,$W3,BR$1:BR$2)</f>
-        <v>0</v>
+        <v>0.20408163265306123</v>
       </c>
       <c r="BS3">
         <f>DMAX($A$1:$L$540,$W3,BS$1:BS$2)</f>
-        <v>0.26548672566371684</v>
+        <v>0</v>
       </c>
       <c r="BT3">
         <f>DMAX($A$1:$L$540,$W3,BT$1:BT$2)</f>
-        <v>0.18085106382978725</v>
+        <v>0.26548672566371684</v>
       </c>
       <c r="BU3">
         <f>DMAX($A$1:$L$540,$W3,BU$1:BU$2)</f>
-        <v>0</v>
+        <v>0.18085106382978725</v>
       </c>
       <c r="BV3">
         <f>DMAX($A$1:$L$540,$W3,BV$1:BV$2)</f>
@@ -24708,15 +24728,15 @@
       </c>
       <c r="BW3">
         <f>DMAX($A$1:$L$540,$W3,BW$1:BW$2)</f>
-        <v>0.27397260273972601</v>
+        <v>0</v>
       </c>
       <c r="BX3">
         <f>DMAX($A$1:$L$540,$W3,BX$1:BX$2)</f>
-        <v>0.31707317073170732</v>
+        <v>0.27397260273972601</v>
       </c>
       <c r="BY3">
         <f>DMAX($A$1:$L$540,$W3,BY$1:BY$2)</f>
-        <v>0</v>
+        <v>0.31707317073170732</v>
       </c>
       <c r="BZ3">
         <f>DMAX($A$1:$L$540,$W3,BZ$1:BZ$2)</f>
@@ -24732,15 +24752,15 @@
       </c>
       <c r="CC3">
         <f>DMAX($A$1:$L$540,$W3,CC$1:CC$2)</f>
-        <v>7.9545454545454544E-2</v>
+        <v>0</v>
       </c>
       <c r="CD3">
         <f>DMAX($A$1:$L$540,$W3,CD$1:CD$2)</f>
-        <v>0.125</v>
+        <v>7.9545454545454544E-2</v>
       </c>
       <c r="CE3">
         <f>DMAX($A$1:$L$540,$W3,CE$1:CE$2)</f>
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="CF3">
         <f>DMAX($A$1:$L$540,$W3,CF$1:CF$2)</f>
@@ -24758,8 +24778,12 @@
         <f>DMAX($A$1:$L$540,$W3,CI$1:CI$2)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:87">
+      <c r="CJ3">
+        <f>DMAX($A$1:$L$540,$W3,CJ$1:CJ$2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:88">
       <c r="A4" t="s">
         <v>458</v>
       </c>
@@ -24810,33 +24834,33 @@
       </c>
       <c r="O4" s="4">
         <f t="shared" ref="O4:O7" si="8">SUM(Q4:V4)</f>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P4" t="s">
         <v>891</v>
       </c>
       <c r="Q4" s="8">
-        <f t="shared" ref="Q4:Q8" si="9">COUNTIF($X4:$CI4,"=0")</f>
-        <v>19</v>
+        <f t="shared" ref="Q4:Q8" si="9">COUNTIF($X4:$CJ4,"=0")</f>
+        <v>20</v>
       </c>
       <c r="R4" s="8">
-        <f t="shared" ref="R4:R8" si="10">COUNTIFS($X4:$CI4,"&gt;0",$X4:$CI4,"&lt;0.25")</f>
+        <f t="shared" ref="R4:R8" si="10">COUNTIFS($X4:$CJ4,"&gt;0",$X4:$CJ4,"&lt;0.25")</f>
         <v>17</v>
       </c>
       <c r="S4" s="8">
-        <f t="shared" ref="S4:S8" si="11">COUNTIFS($X4:$CI4,"&gt;=0.25",$X4:$CI4,"&lt;0.5")</f>
+        <f t="shared" ref="S4:S8" si="11">COUNTIFS($X4:$CJ4,"&gt;=0.25",$X4:$CJ4,"&lt;0.5")</f>
         <v>9</v>
       </c>
       <c r="T4" s="8">
-        <f t="shared" ref="T4:T8" si="12">COUNTIFS($X4:$CI4,"&gt;=0.5",$X4:$CI4,"&lt;0.75")</f>
+        <f t="shared" ref="T4:T8" si="12">COUNTIFS($X4:$CJ4,"&gt;=0.5",$X4:$CJ4,"&lt;0.75")</f>
         <v>10</v>
       </c>
       <c r="U4" s="8">
-        <f t="shared" ref="U4:U8" si="13">COUNTIFS($X4:$CI4,"&gt;=0.75",$X4:$CI4,"&lt;1")</f>
+        <f t="shared" ref="U4:U8" si="13">COUNTIFS($X4:$CJ4,"&gt;=0.75",$X4:$CJ4,"&lt;1")</f>
         <v>3</v>
       </c>
       <c r="V4" s="8">
-        <f t="shared" ref="V4:V8" si="14">COUNTIF($X4:$CI4,"=1")</f>
+        <f t="shared" ref="V4:V8" si="14">COUNTIF($X4:$CJ4,"=1")</f>
         <v>6</v>
       </c>
       <c r="W4" t="s">
@@ -24900,27 +24924,27 @@
       </c>
       <c r="AL4">
         <f>IF(AL3&lt;DMAX($A$1:$L$540,$W4,AL$1:AL$2),DMAX($A$1:$L$540,$W4,AL$1:AL$2),AL3)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM4">
         <f>IF(AM3&lt;DMAX($A$1:$L$540,$W4,AM$1:AM$2),DMAX($A$1:$L$540,$W4,AM$1:AM$2),AM3)</f>
-        <v>0.68229166666666663</v>
+        <v>1</v>
       </c>
       <c r="AN4">
         <f>IF(AN3&lt;DMAX($A$1:$L$540,$W4,AN$1:AN$2),DMAX($A$1:$L$540,$W4,AN$1:AN$2),AN3)</f>
-        <v>8.4745762711864406E-3</v>
+        <v>0.68229166666666663</v>
       </c>
       <c r="AO4">
         <f>IF(AO3&lt;DMAX($A$1:$L$540,$W4,AO$1:AO$2),DMAX($A$1:$L$540,$W4,AO$1:AO$2),AO3)</f>
-        <v>0.20454545454545456</v>
+        <v>8.4745762711864406E-3</v>
       </c>
       <c r="AP4">
         <f>IF(AP3&lt;DMAX($A$1:$L$540,$W4,AP$1:AP$2),DMAX($A$1:$L$540,$W4,AP$1:AP$2),AP3)</f>
-        <v>0.24848484848484848</v>
+        <v>0.20454545454545456</v>
       </c>
       <c r="AQ4">
         <f>IF(AQ3&lt;DMAX($A$1:$L$540,$W4,AQ$1:AQ$2),DMAX($A$1:$L$540,$W4,AQ$1:AQ$2),AQ3)</f>
-        <v>0</v>
+        <v>0.24848484848484848</v>
       </c>
       <c r="AR4">
         <f>IF(AR3&lt;DMAX($A$1:$L$540,$W4,AR$1:AR$2),DMAX($A$1:$L$540,$W4,AR$1:AR$2),AR3)</f>
@@ -24932,87 +24956,87 @@
       </c>
       <c r="AT4">
         <f>IF(AT3&lt;DMAX($A$1:$L$540,$W4,AT$1:AT$2),DMAX($A$1:$L$540,$W4,AT$1:AT$2),AT3)</f>
-        <v>0.14634146341463414</v>
+        <v>0</v>
       </c>
       <c r="AU4">
         <f>IF(AU3&lt;DMAX($A$1:$L$540,$W4,AU$1:AU$2),DMAX($A$1:$L$540,$W4,AU$1:AU$2),AU3)</f>
-        <v>9.6774193548387094E-2</v>
+        <v>0.14634146341463414</v>
       </c>
       <c r="AV4">
         <f>IF(AV3&lt;DMAX($A$1:$L$540,$W4,AV$1:AV$2),DMAX($A$1:$L$540,$W4,AV$1:AV$2),AV3)</f>
-        <v>0.5178571428571429</v>
+        <v>9.6774193548387094E-2</v>
       </c>
       <c r="AW4">
         <f>IF(AW3&lt;DMAX($A$1:$L$540,$W4,AW$1:AW$2),DMAX($A$1:$L$540,$W4,AW$1:AW$2),AW3)</f>
-        <v>0.36046511627906974</v>
+        <v>0.5178571428571429</v>
       </c>
       <c r="AX4">
         <f>IF(AX3&lt;DMAX($A$1:$L$540,$W4,AX$1:AX$2),DMAX($A$1:$L$540,$W4,AX$1:AX$2),AX3)</f>
-        <v>0.45652173913043476</v>
+        <v>0.36046511627906974</v>
       </c>
       <c r="AY4">
         <f>IF(AY3&lt;DMAX($A$1:$L$540,$W4,AY$1:AY$2),DMAX($A$1:$L$540,$W4,AY$1:AY$2),AY3)</f>
-        <v>0.2</v>
+        <v>0.45652173913043476</v>
       </c>
       <c r="AZ4">
         <f>IF(AZ3&lt;DMAX($A$1:$L$540,$W4,AZ$1:AZ$2),DMAX($A$1:$L$540,$W4,AZ$1:AZ$2),AZ3)</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="BA4">
         <f>IF(BA3&lt;DMAX($A$1:$L$540,$W4,BA$1:BA$2),DMAX($A$1:$L$540,$W4,BA$1:BA$2),BA3)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB4">
         <f>IF(BB3&lt;DMAX($A$1:$L$540,$W4,BB$1:BB$2),DMAX($A$1:$L$540,$W4,BB$1:BB$2),BB3)</f>
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="BC4">
         <f>IF(BC3&lt;DMAX($A$1:$L$540,$W4,BC$1:BC$2),DMAX($A$1:$L$540,$W4,BC$1:BC$2),BC3)</f>
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="BD4">
         <f>IF(BD3&lt;DMAX($A$1:$L$540,$W4,BD$1:BD$2),DMAX($A$1:$L$540,$W4,BD$1:BD$2),BD3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE4">
         <f>IF(BE3&lt;DMAX($A$1:$L$540,$W4,BE$1:BE$2),DMAX($A$1:$L$540,$W4,BE$1:BE$2),BE3)</f>
-        <v>0.47619047619047616</v>
+        <v>0</v>
       </c>
       <c r="BF4">
         <f>IF(BF3&lt;DMAX($A$1:$L$540,$W4,BF$1:BF$2),DMAX($A$1:$L$540,$W4,BF$1:BF$2),BF3)</f>
-        <v>0.73333333333333328</v>
+        <v>0.47619047619047616</v>
       </c>
       <c r="BG4">
         <f>IF(BG3&lt;DMAX($A$1:$L$540,$W4,BG$1:BG$2),DMAX($A$1:$L$540,$W4,BG$1:BG$2),BG3)</f>
-        <v>0.66049382716049387</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="BH4">
         <f>IF(BH3&lt;DMAX($A$1:$L$540,$W4,BH$1:BH$2),DMAX($A$1:$L$540,$W4,BH$1:BH$2),BH3)</f>
-        <v>1</v>
+        <v>0.66049382716049387</v>
       </c>
       <c r="BI4">
         <f>IF(BI3&lt;DMAX($A$1:$L$540,$W4,BI$1:BI$2),DMAX($A$1:$L$540,$W4,BI$1:BI$2),BI3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ4">
         <f>IF(BJ3&lt;DMAX($A$1:$L$540,$W4,BJ$1:BJ$2),DMAX($A$1:$L$540,$W4,BJ$1:BJ$2),BJ3)</f>
-        <v>0.33962264150943394</v>
+        <v>0</v>
       </c>
       <c r="BK4">
         <f>IF(BK3&lt;DMAX($A$1:$L$540,$W4,BK$1:BK$2),DMAX($A$1:$L$540,$W4,BK$1:BK$2),BK3)</f>
-        <v>6.7842605156037995E-3</v>
+        <v>0.33962264150943394</v>
       </c>
       <c r="BL4">
         <f>IF(BL3&lt;DMAX($A$1:$L$540,$W4,BL$1:BL$2),DMAX($A$1:$L$540,$W4,BL$1:BL$2),BL3)</f>
-        <v>8.4210526315789472E-3</v>
+        <v>6.7842605156037995E-3</v>
       </c>
       <c r="BM4">
         <f>IF(BM3&lt;DMAX($A$1:$L$540,$W4,BM$1:BM$2),DMAX($A$1:$L$540,$W4,BM$1:BM$2),BM3)</f>
-        <v>8.2372322899505763E-3</v>
+        <v>8.4210526315789472E-3</v>
       </c>
       <c r="BN4">
         <f>IF(BN3&lt;DMAX($A$1:$L$540,$W4,BN$1:BN$2),DMAX($A$1:$L$540,$W4,BN$1:BN$2),BN3)</f>
-        <v>0</v>
+        <v>8.2372322899505763E-3</v>
       </c>
       <c r="BO4">
         <f>IF(BO3&lt;DMAX($A$1:$L$540,$W4,BO$1:BO$2),DMAX($A$1:$L$540,$W4,BO$1:BO$2),BO3)</f>
@@ -25024,71 +25048,71 @@
       </c>
       <c r="BQ4">
         <f>IF(BQ3&lt;DMAX($A$1:$L$540,$W4,BQ$1:BQ$2),DMAX($A$1:$L$540,$W4,BQ$1:BQ$2),BQ3)</f>
-        <v>0.34693877551020408</v>
+        <v>0</v>
       </c>
       <c r="BR4">
         <f>IF(BR3&lt;DMAX($A$1:$L$540,$W4,BR$1:BR$2),DMAX($A$1:$L$540,$W4,BR$1:BR$2),BR3)</f>
-        <v>0</v>
+        <v>0.34693877551020408</v>
       </c>
       <c r="BS4">
         <f>IF(BS3&lt;DMAX($A$1:$L$540,$W4,BS$1:BS$2),DMAX($A$1:$L$540,$W4,BS$1:BS$2),BS3)</f>
-        <v>0.51327433628318586</v>
+        <v>0</v>
       </c>
       <c r="BT4">
         <f>IF(BT3&lt;DMAX($A$1:$L$540,$W4,BT$1:BT$2),DMAX($A$1:$L$540,$W4,BT$1:BT$2),BT3)</f>
-        <v>1</v>
+        <v>0.51327433628318586</v>
       </c>
       <c r="BU4">
         <f>IF(BU3&lt;DMAX($A$1:$L$540,$W4,BU$1:BU$2),DMAX($A$1:$L$540,$W4,BU$1:BU$2),BU3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV4">
         <f>IF(BV3&lt;DMAX($A$1:$L$540,$W4,BV$1:BV$2),DMAX($A$1:$L$540,$W4,BV$1:BV$2),BV3)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BW4">
         <f>IF(BW3&lt;DMAX($A$1:$L$540,$W4,BW$1:BW$2),DMAX($A$1:$L$540,$W4,BW$1:BW$2),BW3)</f>
-        <v>0.65753424657534243</v>
+        <v>1</v>
       </c>
       <c r="BX4">
         <f>IF(BX3&lt;DMAX($A$1:$L$540,$W4,BX$1:BX$2),DMAX($A$1:$L$540,$W4,BX$1:BX$2),BX3)</f>
-        <v>0.44715447154471544</v>
+        <v>0.65753424657534243</v>
       </c>
       <c r="BY4">
         <f>IF(BY3&lt;DMAX($A$1:$L$540,$W4,BY$1:BY$2),DMAX($A$1:$L$540,$W4,BY$1:BY$2),BY3)</f>
-        <v>0.30303030303030304</v>
+        <v>0.44715447154471544</v>
       </c>
       <c r="BZ4">
         <f>IF(BZ3&lt;DMAX($A$1:$L$540,$W4,BZ$1:BZ$2),DMAX($A$1:$L$540,$W4,BZ$1:BZ$2),BZ3)</f>
-        <v>0.38</v>
+        <v>0.30303030303030304</v>
       </c>
       <c r="CA4">
         <f>IF(CA3&lt;DMAX($A$1:$L$540,$W4,CA$1:CA$2),DMAX($A$1:$L$540,$W4,CA$1:CA$2),CA3)</f>
-        <v>0.66666666666666663</v>
+        <v>0.38</v>
       </c>
       <c r="CB4">
         <f>IF(CB3&lt;DMAX($A$1:$L$540,$W4,CB$1:CB$2),DMAX($A$1:$L$540,$W4,CB$1:CB$2),CB3)</f>
-        <v>0</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="CC4">
         <f>IF(CC3&lt;DMAX($A$1:$L$540,$W4,CC$1:CC$2),DMAX($A$1:$L$540,$W4,CC$1:CC$2),CC3)</f>
-        <v>7.9545454545454544E-2</v>
+        <v>0</v>
       </c>
       <c r="CD4">
         <f>IF(CD3&lt;DMAX($A$1:$L$540,$W4,CD$1:CD$2),DMAX($A$1:$L$540,$W4,CD$1:CD$2),CD3)</f>
-        <v>0.125</v>
+        <v>7.9545454545454544E-2</v>
       </c>
       <c r="CE4">
         <f>IF(CE3&lt;DMAX($A$1:$L$540,$W4,CE$1:CE$2),DMAX($A$1:$L$540,$W4,CE$1:CE$2),CE3)</f>
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="CF4">
         <f>IF(CF3&lt;DMAX($A$1:$L$540,$W4,CF$1:CF$2),DMAX($A$1:$L$540,$W4,CF$1:CF$2),CF3)</f>
-        <v>0.352112676056338</v>
+        <v>0</v>
       </c>
       <c r="CG4">
         <f>IF(CG3&lt;DMAX($A$1:$L$540,$W4,CG$1:CG$2),DMAX($A$1:$L$540,$W4,CG$1:CG$2),CG3)</f>
-        <v>0</v>
+        <v>0.352112676056338</v>
       </c>
       <c r="CH4">
         <f>IF(CH3&lt;DMAX($A$1:$L$540,$W4,CH$1:CH$2),DMAX($A$1:$L$540,$W4,CH$1:CH$2),CH3)</f>
@@ -25098,8 +25122,12 @@
         <f>IF(CI3&lt;DMAX($A$1:$L$540,$W4,CI$1:CI$2),DMAX($A$1:$L$540,$W4,CI$1:CI$2),CI3)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:87">
+      <c r="CJ4">
+        <f>IF(CJ3&lt;DMAX($A$1:$L$540,$W4,CJ$1:CJ$2),DMAX($A$1:$L$540,$W4,CJ$1:CJ$2),CJ3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:88">
       <c r="A5" t="s">
         <v>458</v>
       </c>
@@ -25153,14 +25181,14 @@
       </c>
       <c r="O5" s="4">
         <f t="shared" si="8"/>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P5" t="s">
         <v>892</v>
       </c>
       <c r="Q5" s="8">
         <f t="shared" si="9"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R5" s="8">
         <f t="shared" si="10"/>
@@ -25179,7 +25207,7 @@
         <v>5</v>
       </c>
       <c r="V5" s="8">
-        <f>COUNTIF($X5:$CI5,"=1")</f>
+        <f>COUNTIF($X5:$CJ5,"=1")</f>
         <v>15</v>
       </c>
       <c r="W5" t="s">
@@ -25243,27 +25271,27 @@
       </c>
       <c r="AL5">
         <f>IF(AL4&lt;DMAX($A$1:$L$540,$W5,AL$1:AL$2),DMAX($A$1:$L$540,$W5,AL$1:AL$2),AL4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM5">
         <f>IF(AM4&lt;DMAX($A$1:$L$540,$W5,AM$1:AM$2),DMAX($A$1:$L$540,$W5,AM$1:AM$2),AM4)</f>
-        <v>0.68229166666666663</v>
+        <v>1</v>
       </c>
       <c r="AN5">
         <f>IF(AN4&lt;DMAX($A$1:$L$540,$W5,AN$1:AN$2),DMAX($A$1:$L$540,$W5,AN$1:AN$2),AN4)</f>
-        <v>0.52542372881355937</v>
+        <v>0.68229166666666663</v>
       </c>
       <c r="AO5">
         <f>IF(AO4&lt;DMAX($A$1:$L$540,$W5,AO$1:AO$2),DMAX($A$1:$L$540,$W5,AO$1:AO$2),AO4)</f>
-        <v>0.38636363636363635</v>
+        <v>0.52542372881355937</v>
       </c>
       <c r="AP5">
         <f>IF(AP4&lt;DMAX($A$1:$L$540,$W5,AP$1:AP$2),DMAX($A$1:$L$540,$W5,AP$1:AP$2),AP4)</f>
-        <v>0.24848484848484848</v>
+        <v>0.38636363636363635</v>
       </c>
       <c r="AQ5">
         <f>IF(AQ4&lt;DMAX($A$1:$L$540,$W5,AQ$1:AQ$2),DMAX($A$1:$L$540,$W5,AQ$1:AQ$2),AQ4)</f>
-        <v>0</v>
+        <v>0.24848484848484848</v>
       </c>
       <c r="AR5">
         <f>IF(AR4&lt;DMAX($A$1:$L$540,$W5,AR$1:AR$2),DMAX($A$1:$L$540,$W5,AR$1:AR$2),AR4)</f>
@@ -25275,35 +25303,35 @@
       </c>
       <c r="AT5">
         <f>IF(AT4&lt;DMAX($A$1:$L$540,$W5,AT$1:AT$2),DMAX($A$1:$L$540,$W5,AT$1:AT$2),AT4)</f>
-        <v>0.14634146341463414</v>
+        <v>0</v>
       </c>
       <c r="AU5">
         <f>IF(AU4&lt;DMAX($A$1:$L$540,$W5,AU$1:AU$2),DMAX($A$1:$L$540,$W5,AU$1:AU$2),AU4)</f>
-        <v>1</v>
+        <v>0.14634146341463414</v>
       </c>
       <c r="AV5">
         <f>IF(AV4&lt;DMAX($A$1:$L$540,$W5,AV$1:AV$2),DMAX($A$1:$L$540,$W5,AV$1:AV$2),AV4)</f>
-        <v>0.5178571428571429</v>
+        <v>1</v>
       </c>
       <c r="AW5">
         <f>IF(AW4&lt;DMAX($A$1:$L$540,$W5,AW$1:AW$2),DMAX($A$1:$L$540,$W5,AW$1:AW$2),AW4)</f>
-        <v>0.36046511627906974</v>
+        <v>0.5178571428571429</v>
       </c>
       <c r="AX5">
         <f>IF(AX4&lt;DMAX($A$1:$L$540,$W5,AX$1:AX$2),DMAX($A$1:$L$540,$W5,AX$1:AX$2),AX4)</f>
-        <v>0.45652173913043476</v>
+        <v>0.36046511627906974</v>
       </c>
       <c r="AY5">
         <f>IF(AY4&lt;DMAX($A$1:$L$540,$W5,AY$1:AY$2),DMAX($A$1:$L$540,$W5,AY$1:AY$2),AY4)</f>
-        <v>0.43333333333333335</v>
+        <v>0.45652173913043476</v>
       </c>
       <c r="AZ5">
         <f>IF(AZ4&lt;DMAX($A$1:$L$540,$W5,AZ$1:AZ$2),DMAX($A$1:$L$540,$W5,AZ$1:AZ$2),AZ4)</f>
-        <v>0</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="BA5">
         <f>IF(BA4&lt;DMAX($A$1:$L$540,$W5,BA$1:BA$2),DMAX($A$1:$L$540,$W5,BA$1:BA$2),BA4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB5">
         <f>IF(BB4&lt;DMAX($A$1:$L$540,$W5,BB$1:BB$2),DMAX($A$1:$L$540,$W5,BB$1:BB$2),BB4)</f>
@@ -25315,15 +25343,15 @@
       </c>
       <c r="BD5">
         <f>IF(BD4&lt;DMAX($A$1:$L$540,$W5,BD$1:BD$2),DMAX($A$1:$L$540,$W5,BD$1:BD$2),BD4)</f>
-        <v>0.36363636363636365</v>
+        <v>1</v>
       </c>
       <c r="BE5">
         <f>IF(BE4&lt;DMAX($A$1:$L$540,$W5,BE$1:BE$2),DMAX($A$1:$L$540,$W5,BE$1:BE$2),BE4)</f>
-        <v>0.47619047619047616</v>
+        <v>0.36363636363636365</v>
       </c>
       <c r="BF5">
         <f>IF(BF4&lt;DMAX($A$1:$L$540,$W5,BF$1:BF$2),DMAX($A$1:$L$540,$W5,BF$1:BF$2),BF4)</f>
-        <v>1</v>
+        <v>0.47619047619047616</v>
       </c>
       <c r="BG5">
         <f>IF(BG4&lt;DMAX($A$1:$L$540,$W5,BG$1:BG$2),DMAX($A$1:$L$540,$W5,BG$1:BG$2),BG4)</f>
@@ -25335,27 +25363,27 @@
       </c>
       <c r="BI5">
         <f>IF(BI4&lt;DMAX($A$1:$L$540,$W5,BI$1:BI$2),DMAX($A$1:$L$540,$W5,BI$1:BI$2),BI4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ5">
         <f>IF(BJ4&lt;DMAX($A$1:$L$540,$W5,BJ$1:BJ$2),DMAX($A$1:$L$540,$W5,BJ$1:BJ$2),BJ4)</f>
-        <v>0.33962264150943394</v>
+        <v>0</v>
       </c>
       <c r="BK5">
         <f>IF(BK4&lt;DMAX($A$1:$L$540,$W5,BK$1:BK$2),DMAX($A$1:$L$540,$W5,BK$1:BK$2),BK4)</f>
-        <v>6.7842605156037995E-3</v>
+        <v>0.33962264150943394</v>
       </c>
       <c r="BL5">
         <f>IF(BL4&lt;DMAX($A$1:$L$540,$W5,BL$1:BL$2),DMAX($A$1:$L$540,$W5,BL$1:BL$2),BL4)</f>
-        <v>8.4210526315789472E-3</v>
+        <v>6.7842605156037995E-3</v>
       </c>
       <c r="BM5">
         <f>IF(BM4&lt;DMAX($A$1:$L$540,$W5,BM$1:BM$2),DMAX($A$1:$L$540,$W5,BM$1:BM$2),BM4)</f>
-        <v>8.2372322899505763E-3</v>
+        <v>8.4210526315789472E-3</v>
       </c>
       <c r="BN5">
         <f>IF(BN4&lt;DMAX($A$1:$L$540,$W5,BN$1:BN$2),DMAX($A$1:$L$540,$W5,BN$1:BN$2),BN4)</f>
-        <v>1</v>
+        <v>8.2372322899505763E-3</v>
       </c>
       <c r="BO5">
         <f>IF(BO4&lt;DMAX($A$1:$L$540,$W5,BO$1:BO$2),DMAX($A$1:$L$540,$W5,BO$1:BO$2),BO4)</f>
@@ -25363,19 +25391,19 @@
       </c>
       <c r="BP5">
         <f>IF(BP4&lt;DMAX($A$1:$L$540,$W5,BP$1:BP$2),DMAX($A$1:$L$540,$W5,BP$1:BP$2),BP4)</f>
-        <v>0.74603174603174605</v>
+        <v>1</v>
       </c>
       <c r="BQ5">
         <f>IF(BQ4&lt;DMAX($A$1:$L$540,$W5,BQ$1:BQ$2),DMAX($A$1:$L$540,$W5,BQ$1:BQ$2),BQ4)</f>
-        <v>0.34693877551020408</v>
+        <v>0.74603174603174605</v>
       </c>
       <c r="BR5">
         <f>IF(BR4&lt;DMAX($A$1:$L$540,$W5,BR$1:BR$2),DMAX($A$1:$L$540,$W5,BR$1:BR$2),BR4)</f>
-        <v>0.1</v>
+        <v>0.34693877551020408</v>
       </c>
       <c r="BS5">
         <f>IF(BS4&lt;DMAX($A$1:$L$540,$W5,BS$1:BS$2),DMAX($A$1:$L$540,$W5,BS$1:BS$2),BS4)</f>
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="BT5">
         <f>IF(BT4&lt;DMAX($A$1:$L$540,$W5,BT$1:BT$2),DMAX($A$1:$L$540,$W5,BT$1:BT$2),BT4)</f>
@@ -25383,55 +25411,55 @@
       </c>
       <c r="BU5">
         <f>IF(BU4&lt;DMAX($A$1:$L$540,$W5,BU$1:BU$2),DMAX($A$1:$L$540,$W5,BU$1:BU$2),BU4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV5">
         <f>IF(BV4&lt;DMAX($A$1:$L$540,$W5,BV$1:BV$2),DMAX($A$1:$L$540,$W5,BV$1:BV$2),BV4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BW5">
         <f>IF(BW4&lt;DMAX($A$1:$L$540,$W5,BW$1:BW$2),DMAX($A$1:$L$540,$W5,BW$1:BW$2),BW4)</f>
-        <v>0.78082191780821919</v>
+        <v>1</v>
       </c>
       <c r="BX5">
         <f>IF(BX4&lt;DMAX($A$1:$L$540,$W5,BX$1:BX$2),DMAX($A$1:$L$540,$W5,BX$1:BX$2),BX4)</f>
-        <v>0.57723577235772361</v>
+        <v>0.78082191780821919</v>
       </c>
       <c r="BY5">
         <f>IF(BY4&lt;DMAX($A$1:$L$540,$W5,BY$1:BY$2),DMAX($A$1:$L$540,$W5,BY$1:BY$2),BY4)</f>
-        <v>0.66666666666666663</v>
+        <v>0.57723577235772361</v>
       </c>
       <c r="BZ5">
         <f>IF(BZ4&lt;DMAX($A$1:$L$540,$W5,BZ$1:BZ$2),DMAX($A$1:$L$540,$W5,BZ$1:BZ$2),BZ4)</f>
-        <v>0.88</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="CA5">
         <f>IF(CA4&lt;DMAX($A$1:$L$540,$W5,CA$1:CA$2),DMAX($A$1:$L$540,$W5,CA$1:CA$2),CA4)</f>
-        <v>0.77777777777777779</v>
+        <v>0.88</v>
       </c>
       <c r="CB5">
         <f>IF(CB4&lt;DMAX($A$1:$L$540,$W5,CB$1:CB$2),DMAX($A$1:$L$540,$W5,CB$1:CB$2),CB4)</f>
-        <v>0</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="CC5">
         <f>IF(CC4&lt;DMAX($A$1:$L$540,$W5,CC$1:CC$2),DMAX($A$1:$L$540,$W5,CC$1:CC$2),CC4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD5">
         <f>IF(CD4&lt;DMAX($A$1:$L$540,$W5,CD$1:CD$2),DMAX($A$1:$L$540,$W5,CD$1:CD$2),CD4)</f>
-        <v>0.7678571428571429</v>
+        <v>1</v>
       </c>
       <c r="CE5">
         <f>IF(CE4&lt;DMAX($A$1:$L$540,$W5,CE$1:CE$2),DMAX($A$1:$L$540,$W5,CE$1:CE$2),CE4)</f>
-        <v>0</v>
+        <v>0.7678571428571429</v>
       </c>
       <c r="CF5">
         <f>IF(CF4&lt;DMAX($A$1:$L$540,$W5,CF$1:CF$2),DMAX($A$1:$L$540,$W5,CF$1:CF$2),CF4)</f>
-        <v>0.70422535211267601</v>
+        <v>0</v>
       </c>
       <c r="CG5">
         <f>IF(CG4&lt;DMAX($A$1:$L$540,$W5,CG$1:CG$2),DMAX($A$1:$L$540,$W5,CG$1:CG$2),CG4)</f>
-        <v>0</v>
+        <v>0.70422535211267601</v>
       </c>
       <c r="CH5">
         <f>IF(CH4&lt;DMAX($A$1:$L$540,$W5,CH$1:CH$2),DMAX($A$1:$L$540,$W5,CH$1:CH$2),CH4)</f>
@@ -25441,8 +25469,12 @@
         <f>IF(CI4&lt;DMAX($A$1:$L$540,$W5,CI$1:CI$2),DMAX($A$1:$L$540,$W5,CI$1:CI$2),CI4)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:87">
+      <c r="CJ5">
+        <f>IF(CJ4&lt;DMAX($A$1:$L$540,$W5,CJ$1:CJ$2),DMAX($A$1:$L$540,$W5,CJ$1:CJ$2),CJ4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:88">
       <c r="A6" t="s">
         <v>458</v>
       </c>
@@ -25496,14 +25528,14 @@
       </c>
       <c r="O6" s="4">
         <f t="shared" si="8"/>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P6" t="s">
         <v>967</v>
       </c>
       <c r="Q6" s="8">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R6" s="8">
         <f t="shared" si="10"/>
@@ -25586,67 +25618,67 @@
       </c>
       <c r="AL6">
         <f>IF(AL5&lt;DMAX($A$1:$L$540,$W6,AL$1:AL$2),DMAX($A$1:$L$540,$W6,AL$1:AL$2),AL5)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM6">
         <f>IF(AM5&lt;DMAX($A$1:$L$540,$W6,AM$1:AM$2),DMAX($A$1:$L$540,$W6,AM$1:AM$2),AM5)</f>
-        <v>0.68229166666666663</v>
+        <v>1</v>
       </c>
       <c r="AN6">
         <f>IF(AN5&lt;DMAX($A$1:$L$540,$W6,AN$1:AN$2),DMAX($A$1:$L$540,$W6,AN$1:AN$2),AN5)</f>
-        <v>1</v>
+        <v>0.68229166666666663</v>
       </c>
       <c r="AO6">
         <f>IF(AO5&lt;DMAX($A$1:$L$540,$W6,AO$1:AO$2),DMAX($A$1:$L$540,$W6,AO$1:AO$2),AO5)</f>
-        <v>0.38636363636363635</v>
+        <v>1</v>
       </c>
       <c r="AP6">
         <f>IF(AP5&lt;DMAX($A$1:$L$540,$W6,AP$1:AP$2),DMAX($A$1:$L$540,$W6,AP$1:AP$2),AP5)</f>
-        <v>0.24848484848484848</v>
+        <v>0.38636363636363635</v>
       </c>
       <c r="AQ6">
         <f>IF(AQ5&lt;DMAX($A$1:$L$540,$W6,AQ$1:AQ$2),DMAX($A$1:$L$540,$W6,AQ$1:AQ$2),AQ5)</f>
-        <v>0.84036144578313254</v>
+        <v>0.24848484848484848</v>
       </c>
       <c r="AR6">
         <f>IF(AR5&lt;DMAX($A$1:$L$540,$W6,AR$1:AR$2),DMAX($A$1:$L$540,$W6,AR$1:AR$2),AR5)</f>
-        <v>0</v>
+        <v>0.84036144578313254</v>
       </c>
       <c r="AS6">
         <f>IF(AS5&lt;DMAX($A$1:$L$540,$W6,AS$1:AS$2),DMAX($A$1:$L$540,$W6,AS$1:AS$2),AS5)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT6">
         <f>IF(AT5&lt;DMAX($A$1:$L$540,$W6,AT$1:AT$2),DMAX($A$1:$L$540,$W6,AT$1:AT$2),AT5)</f>
-        <v>0.17073170731707318</v>
+        <v>1</v>
       </c>
       <c r="AU6">
         <f>IF(AU5&lt;DMAX($A$1:$L$540,$W6,AU$1:AU$2),DMAX($A$1:$L$540,$W6,AU$1:AU$2),AU5)</f>
-        <v>1</v>
+        <v>0.17073170731707318</v>
       </c>
       <c r="AV6">
         <f>IF(AV5&lt;DMAX($A$1:$L$540,$W6,AV$1:AV$2),DMAX($A$1:$L$540,$W6,AV$1:AV$2),AV5)</f>
-        <v>0.5178571428571429</v>
+        <v>1</v>
       </c>
       <c r="AW6">
         <f>IF(AW5&lt;DMAX($A$1:$L$540,$W6,AW$1:AW$2),DMAX($A$1:$L$540,$W6,AW$1:AW$2),AW5)</f>
-        <v>0.81395348837209303</v>
+        <v>0.5178571428571429</v>
       </c>
       <c r="AX6">
         <f>IF(AX5&lt;DMAX($A$1:$L$540,$W6,AX$1:AX$2),DMAX($A$1:$L$540,$W6,AX$1:AX$2),AX5)</f>
-        <v>0.45652173913043476</v>
+        <v>0.81395348837209303</v>
       </c>
       <c r="AY6">
         <f>IF(AY5&lt;DMAX($A$1:$L$540,$W6,AY$1:AY$2),DMAX($A$1:$L$540,$W6,AY$1:AY$2),AY5)</f>
-        <v>0.93333333333333335</v>
+        <v>0.45652173913043476</v>
       </c>
       <c r="AZ6">
         <f>IF(AZ5&lt;DMAX($A$1:$L$540,$W6,AZ$1:AZ$2),DMAX($A$1:$L$540,$W6,AZ$1:AZ$2),AZ5)</f>
-        <v>0</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="BA6">
         <f>IF(BA5&lt;DMAX($A$1:$L$540,$W6,BA$1:BA$2),DMAX($A$1:$L$540,$W6,BA$1:BA$2),BA5)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB6">
         <f>IF(BB5&lt;DMAX($A$1:$L$540,$W6,BB$1:BB$2),DMAX($A$1:$L$540,$W6,BB$1:BB$2),BB5)</f>
@@ -25658,11 +25690,11 @@
       </c>
       <c r="BD6">
         <f>IF(BD5&lt;DMAX($A$1:$L$540,$W6,BD$1:BD$2),DMAX($A$1:$L$540,$W6,BD$1:BD$2),BD5)</f>
-        <v>0.54545454545454541</v>
+        <v>1</v>
       </c>
       <c r="BE6">
         <f>IF(BE5&lt;DMAX($A$1:$L$540,$W6,BE$1:BE$2),DMAX($A$1:$L$540,$W6,BE$1:BE$2),BE5)</f>
-        <v>1</v>
+        <v>0.54545454545454541</v>
       </c>
       <c r="BF6">
         <f>IF(BF5&lt;DMAX($A$1:$L$540,$W6,BF$1:BF$2),DMAX($A$1:$L$540,$W6,BF$1:BF$2),BF5)</f>
@@ -25678,27 +25710,27 @@
       </c>
       <c r="BI6">
         <f>IF(BI5&lt;DMAX($A$1:$L$540,$W6,BI$1:BI$2),DMAX($A$1:$L$540,$W6,BI$1:BI$2),BI5)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ6">
         <f>IF(BJ5&lt;DMAX($A$1:$L$540,$W6,BJ$1:BJ$2),DMAX($A$1:$L$540,$W6,BJ$1:BJ$2),BJ5)</f>
-        <v>0.33962264150943394</v>
+        <v>0</v>
       </c>
       <c r="BK6">
         <f>IF(BK5&lt;DMAX($A$1:$L$540,$W6,BK$1:BK$2),DMAX($A$1:$L$540,$W6,BK$1:BK$2),BK5)</f>
-        <v>6.7842605156037995E-3</v>
+        <v>0.33962264150943394</v>
       </c>
       <c r="BL6">
         <f>IF(BL5&lt;DMAX($A$1:$L$540,$W6,BL$1:BL$2),DMAX($A$1:$L$540,$W6,BL$1:BL$2),BL5)</f>
-        <v>8.4210526315789472E-3</v>
+        <v>6.7842605156037995E-3</v>
       </c>
       <c r="BM6">
         <f>IF(BM5&lt;DMAX($A$1:$L$540,$W6,BM$1:BM$2),DMAX($A$1:$L$540,$W6,BM$1:BM$2),BM5)</f>
-        <v>8.2372322899505763E-3</v>
+        <v>8.4210526315789472E-3</v>
       </c>
       <c r="BN6">
         <f>IF(BN5&lt;DMAX($A$1:$L$540,$W6,BN$1:BN$2),DMAX($A$1:$L$540,$W6,BN$1:BN$2),BN5)</f>
-        <v>1</v>
+        <v>8.2372322899505763E-3</v>
       </c>
       <c r="BO6">
         <f>IF(BO5&lt;DMAX($A$1:$L$540,$W6,BO$1:BO$2),DMAX($A$1:$L$540,$W6,BO$1:BO$2),BO5)</f>
@@ -25706,19 +25738,19 @@
       </c>
       <c r="BP6">
         <f>IF(BP5&lt;DMAX($A$1:$L$540,$W6,BP$1:BP$2),DMAX($A$1:$L$540,$W6,BP$1:BP$2),BP5)</f>
-        <v>0.74603174603174605</v>
+        <v>1</v>
       </c>
       <c r="BQ6">
         <f>IF(BQ5&lt;DMAX($A$1:$L$540,$W6,BQ$1:BQ$2),DMAX($A$1:$L$540,$W6,BQ$1:BQ$2),BQ5)</f>
-        <v>0.34693877551020408</v>
+        <v>0.74603174603174605</v>
       </c>
       <c r="BR6">
         <f>IF(BR5&lt;DMAX($A$1:$L$540,$W6,BR$1:BR$2),DMAX($A$1:$L$540,$W6,BR$1:BR$2),BR5)</f>
-        <v>0.6</v>
+        <v>0.34693877551020408</v>
       </c>
       <c r="BS6">
         <f>IF(BS5&lt;DMAX($A$1:$L$540,$W6,BS$1:BS$2),DMAX($A$1:$L$540,$W6,BS$1:BS$2),BS5)</f>
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="BT6">
         <f>IF(BT5&lt;DMAX($A$1:$L$540,$W6,BT$1:BT$2),DMAX($A$1:$L$540,$W6,BT$1:BT$2),BT5)</f>
@@ -25726,11 +25758,11 @@
       </c>
       <c r="BU6">
         <f>IF(BU5&lt;DMAX($A$1:$L$540,$W6,BU$1:BU$2),DMAX($A$1:$L$540,$W6,BU$1:BU$2),BU5)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV6">
         <f>IF(BV5&lt;DMAX($A$1:$L$540,$W6,BV$1:BV$2),DMAX($A$1:$L$540,$W6,BV$1:BV$2),BV5)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BW6">
         <f>IF(BW5&lt;DMAX($A$1:$L$540,$W6,BW$1:BW$2),DMAX($A$1:$L$540,$W6,BW$1:BW$2),BW5)</f>
@@ -25742,11 +25774,11 @@
       </c>
       <c r="BY6">
         <f>IF(BY5&lt;DMAX($A$1:$L$540,$W6,BY$1:BY$2),DMAX($A$1:$L$540,$W6,BY$1:BY$2),BY5)</f>
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="BZ6">
         <f>IF(BZ5&lt;DMAX($A$1:$L$540,$W6,BZ$1:BZ$2),DMAX($A$1:$L$540,$W6,BZ$1:BZ$2),BZ5)</f>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="CA6">
         <f>IF(CA5&lt;DMAX($A$1:$L$540,$W6,CA$1:CA$2),DMAX($A$1:$L$540,$W6,CA$1:CA$2),CA5)</f>
@@ -25754,11 +25786,11 @@
       </c>
       <c r="CB6">
         <f>IF(CB5&lt;DMAX($A$1:$L$540,$W6,CB$1:CB$2),DMAX($A$1:$L$540,$W6,CB$1:CB$2),CB5)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC6">
         <f>IF(CC5&lt;DMAX($A$1:$L$540,$W6,CC$1:CC$2),DMAX($A$1:$L$540,$W6,CC$1:CC$2),CC5)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD6">
         <f>IF(CD5&lt;DMAX($A$1:$L$540,$W6,CD$1:CD$2),DMAX($A$1:$L$540,$W6,CD$1:CD$2),CD5)</f>
@@ -25766,26 +25798,30 @@
       </c>
       <c r="CE6">
         <f>IF(CE5&lt;DMAX($A$1:$L$540,$W6,CE$1:CE$2),DMAX($A$1:$L$540,$W6,CE$1:CE$2),CE5)</f>
-        <v>0.42857142857142855</v>
+        <v>1</v>
       </c>
       <c r="CF6">
         <f>IF(CF5&lt;DMAX($A$1:$L$540,$W6,CF$1:CF$2),DMAX($A$1:$L$540,$W6,CF$1:CF$2),CF5)</f>
-        <v>1</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="CG6">
         <f>IF(CG5&lt;DMAX($A$1:$L$540,$W6,CG$1:CG$2),DMAX($A$1:$L$540,$W6,CG$1:CG$2),CG5)</f>
-        <v>0.74193548387096775</v>
+        <v>1</v>
       </c>
       <c r="CH6">
         <f>IF(CH5&lt;DMAX($A$1:$L$540,$W6,CH$1:CH$2),DMAX($A$1:$L$540,$W6,CH$1:CH$2),CH5)</f>
-        <v>0</v>
+        <v>0.74193548387096775</v>
       </c>
       <c r="CI6">
         <f>IF(CI5&lt;DMAX($A$1:$L$540,$W6,CI$1:CI$2),DMAX($A$1:$L$540,$W6,CI$1:CI$2),CI5)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:87">
+      <c r="CJ6">
+        <f>IF(CJ5&lt;DMAX($A$1:$L$540,$W6,CJ$1:CJ$2),DMAX($A$1:$L$540,$W6,CJ$1:CJ$2),CJ5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:88">
       <c r="A7" t="s">
         <v>458</v>
       </c>
@@ -25832,11 +25868,11 @@
       <c r="M7" s="4"/>
       <c r="N7" s="4">
         <f t="shared" si="7"/>
-        <v>0.96875</v>
+        <v>0.984375</v>
       </c>
       <c r="O7" s="4">
         <f t="shared" si="8"/>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P7" s="7" t="s">
         <v>893</v>
@@ -25863,7 +25899,7 @@
       </c>
       <c r="V7" s="8">
         <f t="shared" si="14"/>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="W7" s="7" t="s">
         <v>893</v>
@@ -25950,19 +25986,19 @@
       </c>
       <c r="AR7">
         <f>IF(AR6&lt;DMAX($A$1:$L$540,$W7,AR$1:AR$2),DMAX($A$1:$L$540,$W7,AR$1:AR$2),AR6)</f>
-        <v>0.99224806201550386</v>
+        <v>1</v>
       </c>
       <c r="AS7">
         <f>IF(AS6&lt;DMAX($A$1:$L$540,$W7,AS$1:AS$2),DMAX($A$1:$L$540,$W7,AS$1:AS$2),AS6)</f>
-        <v>1</v>
+        <v>0.99224806201550386</v>
       </c>
       <c r="AT7">
         <f>IF(AT6&lt;DMAX($A$1:$L$540,$W7,AT$1:AT$2),DMAX($A$1:$L$540,$W7,AT$1:AT$2),AT6)</f>
-        <v>0.26829268292682928</v>
+        <v>1</v>
       </c>
       <c r="AU7">
         <f>IF(AU6&lt;DMAX($A$1:$L$540,$W7,AU$1:AU$2),DMAX($A$1:$L$540,$W7,AU$1:AU$2),AU6)</f>
-        <v>1</v>
+        <v>0.26829268292682928</v>
       </c>
       <c r="AV7">
         <f>IF(AV6&lt;DMAX($A$1:$L$540,$W7,AV$1:AV$2),DMAX($A$1:$L$540,$W7,AV$1:AV$2),AV6)</f>
@@ -26018,11 +26054,11 @@
       </c>
       <c r="BI7">
         <f>IF(BI6&lt;DMAX($A$1:$L$540,$W7,BI$1:BI$2),DMAX($A$1:$L$540,$W7,BI$1:BI$2),BI6)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ7">
         <f>IF(BJ6&lt;DMAX($A$1:$L$540,$W7,BJ$1:BJ$2),DMAX($A$1:$L$540,$W7,BJ$1:BJ$2),BJ6)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK7">
         <f>IF(BK6&lt;DMAX($A$1:$L$540,$W7,BK$1:BK$2),DMAX($A$1:$L$540,$W7,BK$1:BK$2),BK6)</f>
@@ -26046,11 +26082,11 @@
       </c>
       <c r="BP7">
         <f>IF(BP6&lt;DMAX($A$1:$L$540,$W7,BP$1:BP$2),DMAX($A$1:$L$540,$W7,BP$1:BP$2),BP6)</f>
-        <v>0.74603174603174605</v>
+        <v>1</v>
       </c>
       <c r="BQ7">
         <f>IF(BQ6&lt;DMAX($A$1:$L$540,$W7,BQ$1:BQ$2),DMAX($A$1:$L$540,$W7,BQ$1:BQ$2),BQ6)</f>
-        <v>1</v>
+        <v>0.74603174603174605</v>
       </c>
       <c r="BR7">
         <f>IF(BR6&lt;DMAX($A$1:$L$540,$W7,BR$1:BR$2),DMAX($A$1:$L$540,$W7,BR$1:BR$2),BR6)</f>
@@ -26124,8 +26160,12 @@
         <f>IF(CI6&lt;DMAX($A$1:$L$540,$W7,CI$1:CI$2),DMAX($A$1:$L$540,$W7,CI$1:CI$2),CI6)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:87">
+      <c r="CJ7">
+        <f>IF(CJ6&lt;DMAX($A$1:$L$540,$W7,CJ$1:CJ$2),DMAX($A$1:$L$540,$W7,CJ$1:CJ$2),CJ6)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:88">
       <c r="A8" t="s">
         <v>458</v>
       </c>
@@ -26172,7 +26212,7 @@
       <c r="M8" s="4"/>
       <c r="N8" s="4">
         <f>SUM(T8:V8)/64</f>
-        <v>0.984375</v>
+        <v>1</v>
       </c>
       <c r="O8" s="4"/>
       <c r="P8" s="4" t="s">
@@ -26200,7 +26240,7 @@
       </c>
       <c r="V8" s="8">
         <f t="shared" si="14"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="W8" s="7" t="s">
         <v>968</v>
@@ -26355,11 +26395,11 @@
       </c>
       <c r="BI8">
         <f>IF(BI7&lt;DMAX($A$1:$L$540,$W8,BI$1:BI$2),DMAX($A$1:$L$540,$W8,BI$1:BI$2),BI7)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ8">
         <f>IF(BJ7&lt;DMAX($A$1:$L$540,$W8,BJ$1:BJ$2),DMAX($A$1:$L$540,$W8,BJ$1:BJ$2),BJ7)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK8">
         <f>IF(BK7&lt;DMAX($A$1:$L$540,$W8,BK$1:BK$2),DMAX($A$1:$L$540,$W8,BK$1:BK$2),BK7)</f>
@@ -26383,11 +26423,11 @@
       </c>
       <c r="BP8">
         <f>IF(BP7&lt;DMAX($A$1:$L$540,$W8,BP$1:BP$2),DMAX($A$1:$L$540,$W8,BP$1:BP$2),BP7)</f>
-        <v>0.74603174603174605</v>
+        <v>1</v>
       </c>
       <c r="BQ8">
         <f>IF(BQ7&lt;DMAX($A$1:$L$540,$W8,BQ$1:BQ$2),DMAX($A$1:$L$540,$W8,BQ$1:BQ$2),BQ7)</f>
-        <v>1</v>
+        <v>0.74603174603174605</v>
       </c>
       <c r="BR8">
         <f>IF(BR7&lt;DMAX($A$1:$L$540,$W8,BR$1:BR$2),DMAX($A$1:$L$540,$W8,BR$1:BR$2),BR7)</f>
@@ -26461,8 +26501,12 @@
         <f>IF(CI7&lt;DMAX($A$1:$L$540,$W8,CI$1:CI$2),DMAX($A$1:$L$540,$W8,CI$1:CI$2),CI7)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:87">
+      <c r="CJ8">
+        <f>IF(CJ7&lt;DMAX($A$1:$L$540,$W8,CJ$1:CJ$2),DMAX($A$1:$L$540,$W8,CJ$1:CJ$2),CJ7)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:88">
       <c r="A9" t="s">
         <v>458</v>
       </c>
@@ -26516,7 +26560,7 @@
       <c r="T9" s="4"/>
       <c r="U9" s="4"/>
     </row>
-    <row r="10" spans="1:87">
+    <row r="10" spans="1:88">
       <c r="A10" t="s">
         <v>458</v>
       </c>
@@ -26570,7 +26614,7 @@
       <c r="T10" s="4"/>
       <c r="U10" s="4"/>
     </row>
-    <row r="11" spans="1:87">
+    <row r="11" spans="1:88">
       <c r="A11" t="s">
         <v>458</v>
       </c>
@@ -26624,7 +26668,7 @@
       <c r="T11" s="4"/>
       <c r="U11" s="4"/>
     </row>
-    <row r="12" spans="1:87">
+    <row r="12" spans="1:88">
       <c r="A12" t="s">
         <v>458</v>
       </c>
@@ -26678,7 +26722,7 @@
       <c r="T12" s="4"/>
       <c r="U12" s="4"/>
     </row>
-    <row r="13" spans="1:87">
+    <row r="13" spans="1:88">
       <c r="A13" t="s">
         <v>458</v>
       </c>
@@ -26732,7 +26776,7 @@
       <c r="T13" s="4"/>
       <c r="U13" s="4"/>
     </row>
-    <row r="14" spans="1:87">
+    <row r="14" spans="1:88">
       <c r="A14" t="s">
         <v>458</v>
       </c>
@@ -26786,7 +26830,7 @@
       <c r="T14" s="4"/>
       <c r="U14" s="4"/>
     </row>
-    <row r="15" spans="1:87">
+    <row r="15" spans="1:88">
       <c r="A15" t="s">
         <v>458</v>
       </c>
@@ -26840,7 +26884,7 @@
       <c r="T15" s="4"/>
       <c r="U15" s="4"/>
     </row>
-    <row r="16" spans="1:87">
+    <row r="16" spans="1:88">
       <c r="A16" t="s">
         <v>458</v>
       </c>
@@ -59010,10 +59054,8 @@
       <c r="J14" s="2">
         <v>5</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>901</v>
-      </c>
-      <c r="O14" s="3"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="2"/>
@@ -59133,7 +59175,7 @@
         <v>441</v>
       </c>
       <c r="N18" t="s">
-        <v>904</v>
+        <v>970</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -59159,7 +59201,7 @@
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="N19" t="s">
-        <v>916</v>
+        <v>904</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -59185,7 +59227,7 @@
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="N20" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -59211,7 +59253,7 @@
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="N21" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -59239,7 +59281,7 @@
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="N22" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -59277,7 +59319,7 @@
         <v>441</v>
       </c>
       <c r="N23" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -59313,7 +59355,7 @@
         <v>441</v>
       </c>
       <c r="N24" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -59349,7 +59391,7 @@
         <v>441</v>
       </c>
       <c r="N25" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -59385,7 +59427,7 @@
         <v>441</v>
       </c>
       <c r="N26" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -59411,7 +59453,7 @@
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="N27" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -59449,7 +59491,7 @@
         <v>441</v>
       </c>
       <c r="N28" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -59485,7 +59527,7 @@
         <v>441</v>
       </c>
       <c r="N29" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -59521,7 +59563,7 @@
         <v>441</v>
       </c>
       <c r="N30" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -59557,7 +59599,7 @@
         <v>441</v>
       </c>
       <c r="N31" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -59583,7 +59625,7 @@
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="N32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -59621,7 +59663,7 @@
         <v>441</v>
       </c>
       <c r="N33" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -59649,7 +59691,7 @@
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="N34" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -59682,7 +59724,7 @@
         <v>9</v>
       </c>
       <c r="N35" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="36" spans="1:14">
@@ -59715,7 +59757,7 @@
         <v>10</v>
       </c>
       <c r="N36" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="37" spans="1:14">
@@ -59741,7 +59783,7 @@
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="N37" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="38" spans="1:14">
@@ -59767,7 +59809,7 @@
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
       <c r="N38" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="39" spans="1:14">
@@ -59793,7 +59835,7 @@
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="N39" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="40" spans="1:14">
@@ -59826,7 +59868,7 @@
         <v>10</v>
       </c>
       <c r="N40" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="41" spans="1:14">
@@ -59859,7 +59901,7 @@
         <v>10</v>
       </c>
       <c r="N41" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="42" spans="1:14">
@@ -59891,9 +59933,7 @@
       <c r="J42" s="2">
         <v>2</v>
       </c>
-      <c r="N42" t="s">
-        <v>939</v>
-      </c>
+      <c r="N42" s="9"/>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="2"/>
@@ -59925,7 +59965,7 @@
         <v>3</v>
       </c>
       <c r="N43" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="44" spans="1:14">
@@ -59961,7 +60001,7 @@
         <v>441</v>
       </c>
       <c r="N44" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="45" spans="1:14">
@@ -59997,7 +60037,7 @@
         <v>443</v>
       </c>
       <c r="N45" t="s">
-        <v>942</v>
+        <v>971</v>
       </c>
     </row>
     <row r="46" spans="1:14">
@@ -60033,7 +60073,7 @@
         <v>441</v>
       </c>
       <c r="N46" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="47" spans="1:14">
@@ -60069,7 +60109,7 @@
         <v>445</v>
       </c>
       <c r="N47" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
     </row>
     <row r="48" spans="1:14">
@@ -60105,7 +60145,7 @@
         <v>441</v>
       </c>
       <c r="N48" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="49" spans="1:14">
@@ -60138,7 +60178,7 @@
         <v>4</v>
       </c>
       <c r="N49" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="50" spans="1:14">
@@ -60172,9 +60212,7 @@
       <c r="J50" s="2">
         <v>4</v>
       </c>
-      <c r="N50" t="s">
-        <v>947</v>
-      </c>
+      <c r="N50" s="9"/>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="2"/>
@@ -60205,9 +60243,7 @@
       <c r="J51" s="2">
         <v>6</v>
       </c>
-      <c r="N51" t="s">
-        <v>948</v>
-      </c>
+      <c r="N51" s="9"/>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" s="2" t="s">
@@ -60234,7 +60270,7 @@
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
       <c r="N52" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
     </row>
     <row r="53" spans="1:14">
@@ -60270,7 +60306,7 @@
         <v>441</v>
       </c>
       <c r="N53" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="54" spans="1:14">
@@ -60298,7 +60334,7 @@
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
       <c r="N54" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="55" spans="1:14">
@@ -60332,9 +60368,7 @@
       <c r="J55" s="2">
         <v>2</v>
       </c>
-      <c r="N55" t="s">
-        <v>952</v>
-      </c>
+      <c r="N55" s="9"/>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="2" t="s">
@@ -60371,7 +60405,7 @@
         <v>60</v>
       </c>
       <c r="N56" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
     </row>
     <row r="57" spans="1:14">
@@ -60405,9 +60439,7 @@
       <c r="J57" s="2">
         <v>7</v>
       </c>
-      <c r="N57" t="s">
-        <v>954</v>
-      </c>
+      <c r="N57" s="9"/>
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="2"/>
@@ -60439,7 +60471,7 @@
         <v>8</v>
       </c>
       <c r="N58" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="59" spans="1:14">
@@ -60472,7 +60504,7 @@
         <v>4</v>
       </c>
       <c r="N59" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="60" spans="1:14">
@@ -60504,9 +60536,7 @@
       <c r="J60" s="2">
         <v>5</v>
       </c>
-      <c r="N60" t="s">
-        <v>957</v>
-      </c>
+      <c r="N60" s="9"/>
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="2"/>
@@ -60538,7 +60568,7 @@
         <v>20</v>
       </c>
       <c r="N61" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="62" spans="1:14">
@@ -60571,7 +60601,7 @@
         <v>8</v>
       </c>
       <c r="N62" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
     </row>
     <row r="63" spans="1:14">
@@ -60597,7 +60627,7 @@
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
       <c r="N63" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="64" spans="1:14">
@@ -60623,7 +60653,7 @@
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
       <c r="N64" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
     </row>
     <row r="65" spans="1:14">
@@ -60649,7 +60679,7 @@
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
       <c r="N65" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="66" spans="1:14">
@@ -60684,7 +60714,7 @@
         <v>6</v>
       </c>
       <c r="N66" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
     </row>
     <row r="67" spans="1:14">
@@ -60720,7 +60750,7 @@
         <v>441</v>
       </c>
       <c r="N67" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="68" spans="1:14">
@@ -60755,6 +60785,9 @@
       <c r="K68" t="s">
         <v>441</v>
       </c>
+      <c r="N68" t="s">
+        <v>963</v>
+      </c>
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="2"/>
@@ -60785,6 +60818,7 @@
       <c r="J69" s="2">
         <v>24</v>
       </c>
+      <c r="N69" s="9"/>
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="2"/>
@@ -64416,6 +64450,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G545"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <cols>
+    <col min="1" max="1" width="25.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
